--- a/Analise_Assinaturas/assinantes.xlsx
+++ b/Analise_Assinaturas/assinantes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lqr5-my.sharepoint.com/personal/larissa_lqr5_onmicrosoft_com/Documents/01. Portfolio/Excel/Projetos_Excel/Analise_Assinaturas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lqr5-my.sharepoint.com/personal/larissa_lqr5_onmicrosoft_com/Documents/01. Portfolio/Portfolio_Area_Dados/Portfolio/Analise_Assinaturas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2305" documentId="13_ncr:1_{C9D51D4A-6B0B-44FC-A344-1BF84596D16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7D9FA56-2084-44D0-A4E5-27B28D7E3FCD}"/>
+  <xr:revisionPtr revIDLastSave="2349" documentId="13_ncr:1_{C9D51D4A-6B0B-44FC-A344-1BF84596D16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157668F6-ADAD-492C-83EF-9B7B182F518D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A6417F27-DCD0-4E6C-9D29-57B48A9BF817}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{A6417F27-DCD0-4E6C-9D29-57B48A9BF817}"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="9" r:id="rId1"/>
@@ -1598,7 +1598,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1658,6 +1658,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1665,83 +1666,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="380">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1770,20 +1695,36 @@
       <font>
         <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <font>
@@ -1850,6 +1791,2840 @@
           <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2008,30 +4783,30 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="4" xr9:uid="{2A7B9B0E-A5EB-4A22-9746-6F07CAE9650B}">
-      <tableStyleElement type="wholeTable" dxfId="41"/>
-      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="wholeTable" dxfId="379"/>
+      <tableStyleElement type="headerRow" dxfId="378"/>
     </tableStyle>
     <tableStyle name="SlicerStyleLight1 2" pivot="0" table="0" count="10" xr9:uid="{3B5C891F-A385-4F09-8DC8-7D9504388D22}">
-      <tableStyleElement type="wholeTable" dxfId="39"/>
-      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="wholeTable" dxfId="377"/>
+      <tableStyleElement type="headerRow" dxfId="376"/>
     </tableStyle>
     <tableStyle name="SlicerStyleLight1 3" pivot="0" table="0" count="10" xr9:uid="{92A4BD21-9969-4CE2-85E3-C5746F51EF95}">
-      <tableStyleElement type="wholeTable" dxfId="37"/>
-      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="375"/>
+      <tableStyleElement type="headerRow" dxfId="374"/>
     </tableStyle>
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFB69BEF"/>
+      <color rgb="FFBE8FED"/>
       <color rgb="FF12C883"/>
       <color rgb="FFA788EC"/>
       <color rgb="FF7D48C4"/>
-      <color rgb="FFBE8FED"/>
       <color rgb="FFB681EB"/>
       <color rgb="FFA281EB"/>
       <color rgb="FFAE92EE"/>
       <color rgb="FF07BD6B"/>
       <color rgb="FF623CEA"/>
-      <color rgb="FFEB6B89"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2469,7 +5244,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[assinantes - Copia.xlsx]tabelas_dinamicas!faixa_etaria_genero</c:name>
+    <c:name>[assinantes.xlsx]tabelas_dinamicas!faixa_etaria_genero</c:name>
     <c:fmtId val="6"/>
   </c:pivotSource>
   <c:chart>
@@ -2999,16 +5774,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>102</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>109</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3138,16 +5913,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>65</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>132</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>107</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>146</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3359,7 +6134,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.43890274314214461</c:v>
+                  <c:v>0.39285714285714285</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3403,7 +6178,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.56109725685785539</c:v>
+                  <c:v>0.60714285714285721</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3567,7 +6342,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.56109725685785539</c:v>
+                  <c:v>0.6071428571428571</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3632,7 +6407,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.43890274314214461</c:v>
+                  <c:v>0.3928571428571429</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3776,7 +6551,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A98DFF5A-482F-449E-9FF7-16CD3203F4B4}" type="CELLRANGE">
+                    <a:fld id="{6EBFFDF4-E002-4DB0-A288-C81CC185F680}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3810,7 +6585,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D6656877-A377-4472-93DA-48E820F54BAD}" type="CELLRANGE">
+                    <a:fld id="{AAA31242-720F-4B74-BBE9-3F50F28B84A7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3844,7 +6619,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4873A708-BD2C-431A-BCBA-6CCBA1412BC3}" type="CELLRANGE">
+                    <a:fld id="{87A6B7AA-4CCF-452B-A403-37A95B5961E0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3878,7 +6653,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC2C3956-F9E3-4DE4-A703-C2376B66CB70}" type="CELLRANGE">
+                    <a:fld id="{29CC9D05-64C9-4213-8CC7-7694DB739D9D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -3987,16 +6762,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.16957605985037408</c:v>
+                  <c:v>0.17777777777777778</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20947630922693267</c:v>
+                  <c:v>0.22666666666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2892768079800499</c:v>
+                  <c:v>0.28000000000000003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33167082294264338</c:v>
+                  <c:v>0.31555555555555553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4008,16 +6783,16 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="4"/>
                   <c:pt idx="0">
-                    <c:v>136</c:v>
+                    <c:v>80</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>168</c:v>
+                    <c:v>102</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>232</c:v>
+                    <c:v>126</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>266</c:v>
+                    <c:v>142</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -4219,606 +6994,608 @@
           <cx:layoutPr>
             <cx:geography projectionType="miller" viewedRegionType="dataOnly" cultureLanguage="en-US" cultureRegion="BR" attribution="Powered by Bing">
               <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
-                <cx:binary>1HvZctxIluWvyPQ8UDp8gQNlnf3gAGIjgxQXZVJ8gVEShR2Offub/pb5sTmgUlmMIIvRKusxm2Fa
-iozAct3vcu7q//F1/MfX7PGhfjfmWdH84+v4+/uobct//PZb8zV6zB+aD3n8tdaN/t5++Krz3/T3
-7/HXx9++1Q9DXIS/UWLy375GD3X7OL7/z//A28JHfa6/PrSxLq66x3q6fmy6rG3euPbqpXcP3/K4
-8OKmreOvrfn7+48P9UPxv//r/bvHoo3b6XYqH39/f3DT+3e/Hb/qBdl3GVbWdt/wrEHFB84Ilw7h
-zo+f9+8yXYQ/r3PnA7W5ME1h/X39B/GLhxwv+G+s6Gk9D9++1Y9Ngx09/X724MHy8f31+3dfdVe0
-C9dCMPD396p+mOPs/bu40e6PK65eFq9wK3b72yHDX3yB/R/d8kwmx8w6demFSK5j/W4NqXx7fPdN
-v7vpsM7/MeEw8oEwR1DHPhSKMD9Q03IYLpKnH/qT6A+h/NKaXhfPK684EtT1zf9fgrp5KNqHd+5D
-+1DHxcNPhv1PmJD8IBzH5sTEr6efQ2lx+4Pgpk2JYD+kxX4S/yGt//7CXhfV8fNHcrpx/9+W078w
-9udGdHDLryKcST6wpx8CK3kObYJ9oE8CkdarVvQTdv71Sl6Xx8/nDlb9fxvF/jXC/Q3/HlTff/Ib
-z0Du7as/0fHo0bcQ7ge3tt9+f+8wToQkz+S1vOavZ1/1HgdPPT40LRwUrIdQYTuECcK4KR35/t3w
-+HRJ8A+WKYVlO5YjqSUsCLjQdRstfo1+EIs92rBLxihh5vt3je5+XLM+SNOEpdoOM3GDlH977Y86
-m0Jd/M2Vvz6/K7r8o46Ltvn9vWAgU/64b1mwxS1iEttxpGVR25KOjRWWXx+uERrgdvN/Ud1GJqmM
-zjO0pIkSQ9VPfmIW+ZVBa6pVZljGllujHlWli1yrse3GVMnWTh/4KCvqGsMYViqr4gAX5VAGStK4
-DvyekyZUdt4Yo1+kRri1AtoRN7F1ZSpralruFlkyfbVr2QYuybP6c007bbpG3HSVO4iOT2piObkU
-RmiehUPTpe4Y8KBTDTFZ64dDSRKVVs2cubEjmysWU1qroG3qUuV0JqObjwaNVV0T/qdj5WnukdhU
-UZBbdzNpCVGNNoNNYtXWt5aO5VVtBvnDJFoeulPYD1hEHYMHSZiVs5vG1njFh3ZOlalJn6vYNrpB
-9UJiazURvUrrumzcaYh479V5pk011r2oXc36pnEtY44fpqjkoUqDIGzdKBqbaN0NSTupKJ+dB7tl
-TaloHhWpyrLRNlUn+vo+SKcwd4k2pk0opzRTdpgNqYe1NndFkbeD6hpHbu2wSG8CNjS3RFtx7WV5
-TPdcc31e6taIvaqO+azqsJFfdNTad9QOgmnjhLK7FEEJqddW6pj+lMj2jAxDsQ+HWP4xS3MOvC6n
-2WWT1Qlxq7IY7iUv5z94Pjej6kiXfBwqre8LR1fXcT+RSc1x33DXdKK8nVUiUtEqJ9XDrWHZ0TdQ
-FGRrsFh8yopkiFd9MPe2N3SZOa2qqM0SvyIs/iLnsXrUYxWbhQrjrqX+nDm59EaWRIEanYpFLo3T
-qXFHQ3e3FjWFVLp2xODlA03+MGnOm22cOO0uDWT4WU48OavGKXiog0jHLg1kU60yLdtrqyjmh8LI
-xs+RnjpDmTbpL+Jyyi8SntWViuwqoKqXc5CodrY0U13AglDNhR5yFZi2/BIJ0WaubpMg8NKpygwo
-n22fE5KnoZuY83wZpKK7qEyL3uW2tu5N4ohQWUNXn5OCpWc2d0p3ijPRunNTZNdTOQytqvLSlC4d
-neIKUVUVqs7IKewibsWNxe04Vjx1+lUyD2boEa6bFZ9D5zoWRr2xrWa8MuvSWUdBmD8EgZ11LtCq
-aFzS1xFXzRBpex3WaX9txEVTuJlNmvuGDLXl63kcZ2XUQw2acmZcpUUyBSuuzXo/sHD4ald2E6g+
-AVfb2qq4n5njMK3mUARC1TzjhZ/peaaq5Dq1153ISeSNST9Tbw5jcU2CsLuf7YoKl5QDM10ZNKah
-xjDlXNks044/pKT9Vth2U6x4WM/7soMQN8QK02QlSF8yFXRz2q+jSkSzO00TOx8l8pokjZzUbYIg
-+NZFc5ErR9j8gUFEs6oqnZmKmEnuFmZp5m49dLZw63IwSsUZzUev1osq1Uk6dSqMhkR4qeGQ0C2K
-KrRcJ7Ciz4Z2mntuG9n50CfFl66thaU6y6Rsxaeu0K5TGYXww0Ra7VUeN/Im58WcuyBQnyVmG81K
-2nnd+Wbb0V7ZFRZi2NMcuE3KxOck1n3szQPE6E9W0K56aXCq6ojQamPJwfwUJyJvFJnbqVVRMlh/
-5CIjHytOUuF3jl3vA2tMYq8u5+xPLqkBKO/s5nsdZnmn8qwfYr9kVu/ppK1iv6r7Nvf60oi+2k1U
-kxWnRj6rqRrTRwNbaVyajUXlljKdpMfCafxOxhC475C6kmoG5l0HlR1Ovoi1/jZ2gXPT04zZamjq
-9jrI85kDzaiTuIA66AShbDTdcB74FnsNhTKaGIBXzmMyqzQmiaVm2rE/RzPpWkBIRTp37KJMK2mO
-yV055LJVvCuK3cBjOvs60sMjKUz+SSeWUak0NYvaJd1Q3diakMwLJ9FbflgY0Go9EhIp4oSTqdIo
-K2uvKapx3oQ1n5kiRAjLbRIrDb2wC3B/mpN49EIejV9CZtDPtqWrG96wyPJ0YGbc7YVdGz6RwGiV
-i95sldG15Z9NG5FcNUE7j6pJZ8fxtQHLBhz3fFeYGcnX4cSg21mSXzjj2Nde6DD6ORmpYKu4k8as
-eBnE1Trr2gLyaavkW5xV1j0rA5v6VddNjgqpw42Vdkaa7pJiMj85wiD8bJ717GygHxbzTCcuqWc7
-yJRdPU1R65OxjrNtY9dUqCZOnfmqgcP9FJKk1rD0Mu62KRHDvElbM3BUC7X1ilFbqadLmLbbdEWT
-+LqVJHVDYrfam4uh2oSlHKstGdKKXztZk6briLPY2OhorAdVAAjGm3Bsg+sA4DQoZPdiuKSdk5pu
-JHV+H/TmlHhTqw2usrwKkxWJm4arOGitDbU40y6ZnLH2RBvMterNJpC7pjANqvjcWfV60iy57krW
-mKofJitRE5mTTBUZTSdvpnZq+8kgDcuPue6FGpvKqj3a1lnlh208Nn7tDHWxLfhIuxWxzNlRpiFz
-AXElfaumdsxMf4xE0ynBWtwfWXH+tYzn0nClzXTks6SMbKgmm26k7MduZ+u069YxgY+qc1YHmzwt
-xkyNVUJux2IwH7ms7AddmmRYo7pRRyrg0ZCqaYjzARRJ9mWox+A2qIbgmxGFTqiGaRy4y8dBDi5z
-pupMxxX7XGeRmaqcOPxzFY99oerWdNYVgoUY9pAU+WYMx+C6TXXZe1NCm9DLRJr4gzlXpttkaQVV
-pzTL3HQsbO4FQQYAtKmUH5vBaDOlSxbstEFY4bXYMlVxVaSRy5qJfCIkmL5ktZFpN8tkYbkZ8sra
-DepRfywSbgdKD6kolEmbKF1plls38GQI5tqGyo9RIMTsVnaAiMq2rXK4KCXRt2OSlRbiHcvUijZZ
-It0ybR3uxoxUo0dlF62LIqxa38obZvlZPcvLLAr6O1504Q0PdJSfV8YovwUs7VLV0BqKorkwDIVw
-sG39qB7h7vk8dMSPSG9/SvqQAA6MGarDo0l/7pMEEimSAu5+muG912FHKtOXaczitYwlHT2WjtGf
-dmAAMDSeBMDEJUQHPoSD29pT27g1rTRzDccs4EjrObfdsg+Yl1hDemM1Sdutyy5LAiUKsx68hKC2
-pkJRaAQD/TjPcNUUcJ91TWiqEI7CWplplH8yK6dg0PQii3djm08mEuq/i2yvJAj8RXrgWEKYklLi
-EIFk5jA9CPqoyB0+xR4ZGuGZdtasTd0nq7epmEhojrKQhYwtHCQ8KDaYqDI8z0KQ+AFhGYu9pCw3
-rZN1Xh/Ohq9JYriV1ZCLinf5Kqpk6QdjMK4qYjpXQdfyj28vxDmxjoUdz7IhXpKhpZzGXlzXuRqF
-rNeSLWYpc+YBJH1tsVaJfNDIlEjov039NWZb0nRs05TcpjbSz+fUrZnJSeTw+53jxH7LMtujY6NP
-MHsR2WHG51jPqSyyeLbHWsc6TmQXe3YYdjtRWZNPwq5f6bhn3tsbosuKj2hJZluWxSSjtiOOdqQD
-GUTxxGMvHwmUuxth8kDMOqW7WLPqvovEbG61Lsh9QPvRG9oyUzLTublOB5PvyyTgUtEgNVTcJ+nG
-nKnx2OUmuy91itjXQCwmPOCC8zHsgEW/qv0IqQlAHsGILZd0+5BVSd8H4ZA4iUephsTtWPtGHJvb
-t7n0QuwLFdsWlpDgk4WM/kAgjWZDVNpG4pWcwrxslq9i0gj1NpUXYgcVypHmI3oR0rSOVDuckO2x
-yk48o5+0iiLCV/FgJpsxIOPZ26SWBR9IHaQE7ILZRBJkXUvN4UDDTNSs4jj1qqYNv85pl98KEVar
-KhGj19ja2IVO9O/sT9iMcRROFvpH+6tnMDiswMUkjqoVDXgJuC+kGg1zOKEWr7HSYibnjkUF2g/W
-4f5EFvWoN0Athpm1l2Wkc1f3tvmZp6w/YawvdUOaDEUaxJzoYaDcc0iKzFU8lZ2deuUw67XTZN9r
-ZhUncOelvKAPJoemIwBfdOSQSMPMtOVdvCignD51yNm82eDRuW0UzZ5EZbYvZqO2Tijka1t7TvVo
-a4E1acKjIPaY2c+bgRuTG5W5fUIXFxM91EVpSoliGaNyKcEd6aIYpzitUGvwDLuLP+Zph6RGjoWb
-85KemVESoI4zBGzDozZA4f2XfKcJ0rawiaAUyfwxeoxzUxrGOMKpWdboWR1Nz9MWKfC/QcWBvjsm
-jBoJ5qHwRNIhzgpE7Ena9ysGXFyZSzL5NpWXHhqbcYCEDPuQVDhHHlpLkhfIWhMv0IhkvWrQoUQM
-JdtWdRnlrWI6ZudTlBrMbWpSAKArEig+JSlVoV2W1YkVLUp5LFhsm6F2CWfJ7KMF9WHBq2rmWNBc
-8XWI2PWqEHHmJXVpEeV0vbN5mwWvWAlK7o7JmaBLw/HIl0Ut50Yvh8SzZUtV25q096Sh7Q1xJPLz
-pLTPe9k0+QnjfAk2EpBNmARVS5jkCNdaA50Zs+oTL0SVaSWKZN4GcVcIhXottU4o01OgdcRVCgSg
-dHERBEh6qE1OQSbphFXiadlZF8giHNVkjXFTCSK9Ps2CECU3s0c6q+m4N8nsXEDzteEx5LDrtu6C
-FWpVwfqJ9X/V/T/+WMCPuvVXXU51HEZ/NZz//vif+59d7KeG6D+/X1rW//x02T/WbVc/vts/lM27
-VVd8e2pkHz+zUP77IRD+ayVLjf/gw4uWw79oKvzokf+Liwcdh4PGys9e2lKKXyrzf6PLi2bDz77M
-PzsUy/1/tRmo/QGeAdU+OHeLCG4hrP2rzSDZB8dmhMIrQqBwVbj0V5tBfKCLm17sGa1Yk1lQ+J9d
-BsY+SPTN4aclYhNO0bj4ubkDaWFW4K/PB12GA1MVlumwpcVgosyEIApAdahUzAiLhIb1pCqUSJk7
-Y36hXncdqgG7cBZJe8JnHlrMQo5zZpsgRYH4Jj1yLKUhgw4ObVRm2kzi25il5owKQBAb/CbkTj1/
-fSaJV7Z36Mie6AlMIdjYIaqIYuHj83CHxEVaT1mFBolBiutWMuu2iq3khw386P+/RuXJ0v9pmwJd
-IkokE5yZELNl2kvy8iyswlemYUbm1dn2cnW58VYrpVZn+9XK81Z7F5/3Hv71PFdt8Je3P1tt1Rb3
-7Pf4uPM8XNt4O1zzd/gTd6+220tvg6t7PLzFra67xdtWa4VX4vXLLSuN57e3q8vtFm9TeJ3yl8ur
-7cq9xy1YgnKXb/A3PvhKuRt3A7q4F2/8uL7E6888D6+6xzdbX/k+3njn7dV2e6u2votnfN93fdd1
-l9t8PI/3LS9zz/HHHjvBiq4X8uuNu/vD3y23+rut8t0L18Pf2PVmrbF5F6tb+Ztz111t96tloVjb
-Gk9euw946wa37i5uNpubhU1g1PK0t9/naiF74+LrtxWDHmnGscSOXUae1A0niXm1X13eb1e32JTv
-PribnXtzgpJ56A1f6MaxiaHllVF08q5W3tXdl8tQXSr/84VL1Ak67DChe0nnKNpoqqaM5EIHIrrb
-Xl9Dzi74DZFszvbemeueCN+O4o6XBI/cfGCi5DmD4N67v4W2QE5vywg4d4hOL4S0CPGZWTW0lEEf
-g8LV2epsUejV/uk//L68X8E2LqGr+/v96n5/WSkYzv7+HrJU52so1vZ6vV2v1/56fa4uoGE792wD
-df58fv6kjufKvdhA3rA8mIXnXp25Cvbp767cszNo325zIkg5qQgLOD7bDSfIWRPwy7vzbmE34Ngp
-rRZH+PqCYQtDn5GYgeSFAImz1f1l6MMsYe6Xi8GDbdf42ao1/lqsOlTY4e77pnQH9d3bbDbfB3V1
-c0pFxAKwbwDj0mV/vqC8tVmSL0p5ub29XLnfN9tYrdarhen7FTDOu9kvMAnBQBC+Aga6y0fvcnXr
-3W6v996dBrat1d3ZlxVegK1crtX69mMP9nlAkevtGnrn76DnpfIvHhK1u4GoPY8q7woKce+oT/4F
-kGTlqY3nXwGHdvsFYN5WVbHo+lv7PCpHpNoYmQlNBWDv1R0wt1dY9+f1Sl3/QGZsDyB65npnKyzC
-B+6+vQJmLj7mrSUc+aBZTgP622D1HeB9Dy7sF1zb33iXnnu23QKtN/ewFoA1EB9eYu37FeB1tQLP
-4Xo2ixfw7iCc1b23vbwEYENvLq9Dpf6EFq0gE3gJfwcrvANq79QTlm3X28vt9eM2VI/Xy0u/3F7e
-x+p2Vl9CtQXYAYcur/Hx8RHaCMzfuBc3wFj8vtrc+Deb7y4gf3OjbuFFRqVCtYap/nl+cfHnxW7j
-f9ruNt9uruAp3Cu4A9f3bzz1cA5HtLk6825gosrf7c6B2bsNWO+Bq09sxs6/g91wrqAI37LZwy/v
-z9yNfwFTf7rxjxt8vYDCjXd2dXcHRXS/nZDI2+iFBOVQ9+0w0IaEi4GXPMP/0N313oPLg+kr19v9
-cHLuCT3AvMmbeoCK7SHZtEdrQ4MsaIId+0vYP0xtobp470rBitSXxdcDLmEXW4UbgQ6r68UrQ9AQ
-PP66xgNbdYGAYIW/lme32/UFfm9uwDRv5149BTZg62rxmrCoC1ju9ilc2Ox2MMhF1VeLDl6uFjiN
-1AYqBPYDrVce8PhsEaO3udsj0vE2lx6eeVsAi3f4p0FYDCM4jk3NZX4GlTsil+vPwLCfZyck6IWh
-TWKgqdKWvYs6ROu/TeVQyn9RwSSQRC7vUEqPLF8HDfp9DA2AoEgcP+gMNNjRQ7oPx7ny0L0zLt6m
-93JXAnNBhNiYDrY5EoTDXWXmLIUz2rXqagd1QnsYV1HWm+rXqTAhUZ4xkboIcrQrs7PjpCZBrRIe
-0T9JXOXbthznE8r6knfInh3UPJGEIDw/DpvrKiNRK51ajSmPpBs5o+7QghGiU9qZdKPMaohu397Z
-oYtc5IVMXQiU8G3kUXSZ3nuuFejJVGXeT7XSVUF3xKiE1zdpsiedfSplf4UUMj/kOaiFLK75iIm0
-zInOuxSksr5UvVPMKzRvS/Sv82z39q5e4aTFkVxRCTZKZIaHuxKlVaAkmKPtGjfJFgVDa2MhfTvn
-mjmXQ63l5m16r2jhc3rLON5zLqILPGurB726MOdyk5tBafhJb8Un6LzGQkFNdL8ptmctE8vP6QS5
-PU+xFhhmyKqod5NkTiavjbv5noV9dYLYa0xEoR9jNsjLUR1crj8DDKeqLbtJpkqFE029rq/pRWRZ
-gSu4PXnWaPMTAPXq5mz0FdCmRQncOjLlnneB3ca0UmbWcSWchPpxSyUmqubwhD2/RsoinElYMwZk
-6JFTMA0hUmMklZpqDFy0NLMumgRdYicP6xMGdhjyPRmY9ZzUkYH1syzrxsSuxKwvo0iGaxtDV38s
-xfTzgafVH7Xd3f26Nj4n+YKRsTEOqQlGYqjD5XUgVjj8EJ5Aq9d0HlVxy7aQ6BNxrIuNU0b1bES1
-KmOn+4hOfYKxoIJd/ht7gbLDmC0u5HGnMRABryJHVko3eawY5jpWca+tEyWL11TdsjFJiyFT9EOO
-09/akXEdV1aFKTKHWZg8y9JdZuXB97xsolsHeNWeMK5XNdC2AIcO3sj5EWIkRpTVscUq1aJets76
-7rPg/AutqPR/nYGScHS3oOuYgFgW8syKLUGicBCAjCgwpDvkje3xDGM/b1M5yn4XNUdRx0F5e2nZ
-wpEcIW5k2HGXiaJWFauZago2uGKOEr8sy3BdDJhDLC2xDgLM2TDRDoaq+qJTM/oqJ1DkpVpaT30o
-FIbNp3DkcL8O+vN938PLmEWbWVdFw6NmG7Eub05I8LgC/bRlZiHWQc91mTw4MrOxCe3IHHWtojhK
-dySj/aqqSnar+3ofWsa4q5tS+3WK6VoG+u44YQIFMmjN1tl2k1GdCIVeIo0D5wqLdFBFxTGIo/UM
-E+Ijox8rVRJ7YGoIndxStB1C5mECgJYqrnvruunafDwh/Zc8B2VMZXMb7auX4dGECbm8M+EpRqZt
-t9ZJ6s6sK05I9tX9PaNypGJTXzpzWAG0kdb1Xhdm1B2qwFjnmFOenM86GapfhjjsCwIG4zCHQJwj
-7LblUDBElJViEwaEDGfE/BxvixPcewk+oGLh1IqNVi2q4kd+ttCYGmhki0nA0LGutT1VPkubZE0w
-ZvOljet59batvsZHqOyPVi15gQhBqnEOTMAjWcnAS6+vbOOMBhgatTECv6f95LTeGCIKPLHPU3SP
-9ml14YiJVo4J/LzAZOmg9baMunmfdEZ9hsFW7pI0MU/A32vMXaJNgia/kOiIHcLBWNp5ldUFmBub
-4q41urHzqdMn66FwSKmiwmj/fJu9yxsP8yxnaUgwhhQIbvE4FuwwcFyIBgOnfdAUnlVVtcfypFdG
-Mf562IlQGhGMhVMbaLmJI4tI+Tyng4X5gQkj6T5J5241tuLXg2n0bNFURe9lOV7Fj+RWTI3WnE6l
-MmQ5rFnKc5Um8opUqVAZBnDfZt8rWHJAbdGiZ/5qCKnVjBbQisRZYLoslqnlBrSepxOaYb+Uk5Q4
-ObNoB0dbabn+jBDsOM6iaC5V1pNmF9lGjpnGnOx0Lmy/lFZ/Ow6GgSlFlJGGXzcFjOugW4X4Ggk5
-O9qkTEd7Tlt4/9lonZusEvQSoz2dW1JRbXVtzYkqMWh4YsevaKaDugs8BMX8jkWPHARyEqtl5oBQ
-1MQ0Y8mcTJVmEqmY9MavYzWGw56iawtpylNl9hlz7bKZGh6WCKgi3Z9ZXdVtc9aKXcwdumkD2UY4
-h4PJ1Ld15xWRosSBugMCERuzDItuPaNaRxWdceIYeN1ZNFRZHOOwRqybndCsuxi5TlRhO41bxX18
-gvQLtV2cLqZ6qckpXMZT5fcZaREMRVlVQJQwsXEyBuckVqjF9Pu3N/hCgqCC6gOOVBGM3r3AljoY
-WT3M0Nk5bjFo2nTJ7CHFzTaslMX527Re2xHQBeGnLVHLMY8i1JTHPBZlW6rUKcZSVZ0x3/cGzeQJ
-VXl1TxzjULaNyoB1DGLxjHmEgXQltBKDz0058TOSdfm2GrvmBLa8RkpC/wmzFkcrj/CyHYJC6zwH
-qSpsFMoehlfOE07SkOlEcPga8xALwQRMgUkMeQQuVW5H8UjLEqdLSOzXBmLdaIgq/5dFtLgZuEYw
-j0h5lMY2oYycKo4BYQJz+8RqIhx9w8Dur1OBakMHQMOmxx07WJGJc1w4Mzekk+OiVW986Tun+OWc
-HIcPUaHEeBBcDPzMETpJmleREaY42VJhNqNNMYqMKbXERTnkRB/mFeEcUFquP7PVQk9VME9JqRyr
-/8OWBfMLGpQndG3xigdhwNNZSozIorhGljOVh0TMdqxybeIwi2lpcl4lY3WTs0FvnVBwjF0P47h+
-W0xP81MvKJqU4kQoN0H1SLvnKkuyoQJFHjpgYGXiDFOBSdPAwfkWFYkg2hRjH/pTLJx1QSr63ZiM
-XSOKchWxIb1+ezmvMRmCtASmGwgOEx3tPyJovNkjtCaV0b3sDMOvIqs/Ued7jQiOplIuMVAJvTnS
-Gasa5rgpBY5zxjWNcaAxsVqvIU5pnbCB16QpMfMNgMdsGaZRDqUZ8LQgbIJyYrx+dJOIWYoMxsoU
-/aZoMQ/467zDLDKUR3JLwsQPqXVjY415r0scXhXBWdpP1bYEgnr/BhUUOzjiH8SQx0Vtmcma4bxm
-qZImr891F+X+KFj86yIC25BAAQ0hqGPOpYU2UieOlhhVRhfZgDMRZiyiXy0TYfaHoPoA2EBeYz+1
-zp+ZtD33Rmssuo+zDvk+n0bqlUFhn8Dbl1WOhQxmgzBzhqIyN4+QI7dmLUgucdC2C+JzY7IZRhiz
-nR6EoywcxLQHcV0aJICuy+AMte6d5eCcwNtyW6R/ZOewb5OhRYBKi32cYMw4YOa0OOirZqunpt+O
-UVN85CNOGZ6LbhiYOw5OFm/rHhO0JxTzFTNAJrDMVTJLIMQ6MgNDR4J0uaPVlCcsdSNiTd5QxueM
-h9ztmgD/vr3XVwwcjoei/swYppaOPXZH5ZjPBCjCoyhWQ8PqlcznU5awLPuQoyZEiuoYNAjTy8ep
-AOrN4VhLiNWK4hBHS6XeTsUstzxwohMq9JKDIGUzhIjIPTCduVx/pqjASovUAhzUqYgNb9JZZeNs
-ZGR+chomvkVDPgQn7HzB/ePdwfKWKiPgix8PHURpJXDunWlVFrnhcacSf1TdMH+pOpl5plnQLyiB
-jGdlxPQmr2lz/7YIX6qryVA8ochyEEUC1Q53nBcVwQn1TiuS1TjGZclvWS3vRYHiFI4E5arjpyLK
-l0qzUETCik4aKqzsyEqbIU5ialZaFQZFwoqzhxuYyqlZ9BfJBgZsOWq3MAS6+J6jEI8mLSbgdKtx
-+taoZ9cu4viumqece3UZ8I9V2s84zGZHqBf9H96ubLlqXdt+kapsS+5eba8mHSQhBMKLitadJDeS
-Lclff8fa5+GSRYoU+17OA7uo2oBiW5qazWhSIfRrd8QLezYOEqSyyP/QOTrHDs4bCK4Ko+2CCD7t
-47r3BnzfsHkY9Ey7V47hC4EPYxKUySk6/qfod/awNCI9BAUCHPxE3yIu9g/gWvbVymYRVkw38bue
-SpTJjlttwGngPAVPVk/vm5mp8ZVa64U3j1ks8JkZUusTYPT5jooElJw24LqhqNDguK6L+WIT5PIq
-AAhYeN7f6OwxnOrmj68yvASM0GNMCXB8z4kpgcxFPI3YybFnIA+amtPtkK9hq1953S99WxRdwJ+C
-DBCH7PT/fwoSUqmOA3U6FLVe+PvVdzTd+TDnV6ZlS/pK3vjSYoCno1hHgwe/zt6mYVHUEDAtiw3s
-jssxHJY3VqWkWhPIIPw+FLwQ/JLTEgGGiSkGffT5c4WcxT5VeK60S/m3zoT+fWbS9dArIY4YZjYf
-fr/eC4+G/jwQxyDsRRlgAs/XE4y0cvED4vqQZhVpMLyc5xrTdPydP/9kGcbNuBLxaOgUn8WcNpFj
-rU03FLlnc10wtyygSG6KXoQR9Aqq3z/YCzE1Q07FTlEuODUbnz9Y51Qi6oWAoyplV4I8qruCTBj6
-lTzT0Tfj5zU4TLhrXqmcXloXrUYsSf8BkpztlcXYUEQ0xbpWoXvjlpa9iTyGjLNqm/f2JOGRrQ15
-Jbl74TMCnIAUIEXyhd+cHYc1XZk0pEaoM+gQcIVTPvbTUKapfo3q88IOzRDnYoCy0TEGIP35i92o
-XdLVyqHgettKsWzRwSdrdlxmDhKVqskrTZaXHg0l9Wl0gl4xisXn6002rSeX5QrjTZZcRASKE7KO
-h/sta8UrO/S0A8/SgAxZFOYMKaD0uCCfL8WSKTLg1qkiqFvxhs1oHXUsbva/35kvroJ7N45iTALB
-9Hm+SiDHXiYxosnUgag+8SC7akhj/7gPBopjgm5EhgZuHJ1zpXSDsVviR6wiYgfRkSAR/sg6zNQq
-D5rT9EqIfGlXoDt1qmOQVLDs/KGCLZmXFnGLGPNuNdudHCZbJMininTq/pAvBPAPWi2gWQI+hRYx
-6rrnr3CEXEFCRxzu2U/1pWpnutd9nV4Ezo1Xm92WV57uhU+GiIwudB6kWPOc+tqn0WgdCAGFXccR
-M1kod6xVDb2h17KIFzY7ljg1xdCfZSD3P38wN7KwMS3OsVvXVFYSuIEq7YesLdqWz+9+vxFf+GZ4
-iRhLAqAAdtD5YtyFTpk6U0UCBqeq8ONMX9XMYl5wgiYuuv6s+fPoiBsbnVLkJEBvn1/b25BJ17hI
-Fd3a8hJCUhWLeIsubUx2DPIChXOhrX7/mC+9UyTV8an9fOoznV7DT6lCYzoySsKQY2pxGWGSuBOS
-QreJRa81119b6XQ3/LRSMgISBkSQKsbFtOsFQrURO+X7dSzbfsSn/P2DvXDV5GDmotmN3AR3ytmD
-STNnotEQVDJuM4fNx+R2S3heTbGedsTl/jKFkNeHf7FocgorOA6ols4WnWVuwzajCiIGeIktYCDv
-pU/eN4maIbEx0b3VDXtlzRfKsxNf9sTVQ1WPfvvz96qzbdAdnVWBSgmKCY26zEcnPnjedFBJpfIT
-1IigIkKC+SKy7jW65K+59GkihBCKjBqcq/PDDx2m1FEBCYcldeHdEilfiGauPxM+LTdbRvhO80nf
-kFG/cvP9GnVO2xUnBXk0Ggrn15EyLG8N+pMFjwAawjij3nW0i+5+/0F/jQKoOlP0IQEpQx/t/H5d
-U7W0bdSgYcOX5lO9NWtTGUjQQsmGu+GTWeL68+9X/PWFnupctNRScJQxkj0Lco2RpAlmZBASUhG2
-mFoV3+aQfqqLGSOVfUxBiExVHawFH3n3GmLhpdX/yeLDE90befbzzbSSAbpxDGloMI6NAOsTB7Ow
-8dDYMrcCknKt4putRheM/RHN4vD775/+1yBBcYeAo4eRBI3QKX2+foJpBNJkBInI9fQCvz73I7OH
-qMmy/R+vhBYpOkMY4/zTYH++EmqHKN8EbknF81RVasush3Qb5vn7ZI39a+TlX08phBVQRiAvxDdF
-W+H5crojfeeMxnUSiekbLpCqtx2k7XqODpxRw6GWfnoabToeOk/Z4+8f9tfDgtXRSs+QfENUMYue
-r26WJOkXjdWBGuuuwjEJirhT0R8fydMqGYb8mPQAXnpWLuGEZEBoW2SIluSXnWdv1syRi3/xKFl0
-OvVAeubnmBoNnB+UgbBIYrfxFoB07jGADtbXcGAvnPwMOwOtSohZIrk+y6IwO4X4iVqgTQPlpiqf
-QHPMQ1lfAOvnLrPMkD9OSQEIgwAmZmRgkf6CBtN15Ifp9IkI6ehOrJl4E6PvtZO1Y7e/f4Uv7UWg
-LoP/NCyBSX++G2TXBqi3PO781OqLoJtYiWaCrCJvxcUITvvlhFn7XTx34xM4cOMrN/MLMQZpHF4p
-uk4Aw5/jgmPRr4B9IPnmroZI0YSO4i3LRIo+pkvnhygiUJiMWTs9sLb28ysP/2tegAwL9FUMe9AB
-hxzp84eHatEIqQuoq4XbEDzhY7RJoSIcxnJpaqEBc+z7+5q4+F8EHCwMbAE+MsLOee/ftK2e6hVF
-gA8nXRL8hBdrtjUfw3TpX8ldz447Tt5zLaOzO+RvaRmd7aPXtYwwT1SXPSW3/69SRmfBjf3/Shmd
-3Vj/vOufRIbOJ/X/F5Ghlz7rz0udzvXPGfS/U006C3z/PFB+agyfVIxQ+JwdELI2fdy0XVPxdk7t
-JTQ0GaQa/djPF9R3efAuHQ3/w2zutChQ9JjygV9+4uKfXY/Us2mOh7yuLG/qG+OIqRTUuMrfB74X
-Hu2kzhSBAgEuTnqeKi8ginCCBlOVO5/JqyUUtD8aKtPoCKq+Bv8nHRHxf7/oWcD559F+VoY6OyXn
-ylCqG5d2K9NN23Auepe6HMJpzWqhtvZvdJ3AoUITAAVCguc+h79D6zJlhCtWxpOpj8HMfZkA9PrK
-ez2L6CctFgDEkUbhA1LMgs8u/kW0IK8MEVQuW6gJlx6Kpm+7yeU7kjiy0x63tVSj2tNoq18J578c
-PyydYfgMLFyEcQo7C3V5NwS87yQtw2BowtsoHtfpsTUmgqwi8C3avDKNemk9nAvc+cjlAFU/O4PN
-xkTEyRiVvmdrIeyWVZB8EGW8bHP1+43zwlLo3Z/0fABuwjk8e7QRbC7Ih+VhyVF17PikNggCGyi0
-glnzygc8ywhOHxAoCIzY8Ss9yaw8jyxdn0yhWyyeSgfDVcPVeCAcGq4RSet7s2LGz+3SlZ109NrS
-2L7yEX85l6flMRpBUgfkDnbq8+UjkufIgZuoxCbNDmSD6gxLZjSmA0KRHwzB3e/f7C+BFHMRCCTh
-P9gzePizjzjWrufQW+OQeu3ZsRdq3U1tY155qb8+1bNV/pGM+ylc9znNydRTXmKin5Y1pFRL4YC6
-C5v8bl3pa7JgLy2H7uwJmA0SBZ7v+UuMFXqnbZbUFYJYoLr9yGbfNmUTCyqgbamYj9TOG9Gy/Z+/
-TQoWICCwAE+igfV84QatRuD3I1JSiD0/NT3GmIP+QzgQPhKUTnA1oKODCRBO/PNFxOBFk2QBKz0e
-5ykPBlVhijG+0oH7dWM8l8E7e4d/SQbv7Fn+kgzeKbz8tP3+pgzeWfiAiDS+2t+WwTt7vr8pg3e2
-Lf6mDN7Z3vg7Mnhn8fa/JIN3FifOZPDWsTWHQa/R8ffR6NdcBEPNn2Twzvbif1MG7+wB/5IMHn1+
-rv+lDN6vycdzFbyzoup/VfCCZePLYbCjjvZbN/fyOMnImIvff7XTtv5puIjwjuV+0rg7W+6va9yd
-c+X/Wxp3Zx/v/6Zx98JLfSZxd/ZS/1fiThtTD6CeIfUrgT7IkrJNct0ceza08pVy54WNg6YK2lgY
-gkAi7FwLkqXWar0sslIYhpboLfGHxBp63Oiwfv39pvn1tkZPM4faJRrFGOeeI6jMkmIK0KyyAoY+
-LddwjUux5d/+zSLoREOzGTSw83I4CMcaeD5YBgAAbXeNCoJK2Xx7JfH45a2h540pI+Z+GNqegK7P
-D7VD8YbhYjdU4JVPdwJt9yrQsz00Pkw+/P6BfgmQyLDj00AMWSKoPOfoNjWruVZQnK+6IaYPHMgs
-ftFuHgRXSPzPQV5BwNZmTcnsOPWfOrvk9JUtghHqL58O9ROgkkiQT0gQEOmfPy/KuR6Ez37a+Tjo
-wQEnGxWRuF3Fpuu+TGBnAk8G6M3DB6UAd1JD2D7IZJD0ZYjRHZ92eRuEMny3Seqbz20PLAa7sCIb
-yWOTKnQoPnAPHfjumJJVk29KdoRn8NsJOOmKtl8VxOADWweclo1X6xRUZsW4F8KOeTfTh9WNORnK
-pGns6c83GzTnpxQeLz9CAwePD1u0JfTNLNNZfpt6ZpYyWnwb7joCefqugOtFJy+XsWsvg7SDvvqS
-dqv/6BplMCCHYPvcpfuItWopfdivFsr7wB/NN4E4KSV0tBHZI0SxI3aVgEcZfMs1eE/vexSEtCsG
-UKJCVf7HIWYVpFugUb8Ojl+OcydNicmtsu9CTxJQJf/j0iIxJO/Lzpt8fu8Ynbu38xATehR5ziF2
-jmcZ4qcJEvh0q+hkXRof52mrN7oza4deTCkCkbP0ODea2IORgFoVicjWKK3ATGnbtJT5lMvC+5EH
-1dBw6u+HZQvVNzGqJGoPBiqBHyaNcnatxDyM5A3wsgN/Y9p8A9h5CXWLQmXVvJIJkCUfw6UOQGil
-G9xq3o3JCExrXkM2Yud0MJlySWPR3emTBo2sCCVL/iHmPtWfxgXOAEuJJpNa3mkYfkA5e1WdmOGf
-Q3geHhsaGXeftM70qCLqbZkwr+wCwrpCRPOyfUhcKur3bZytE9lDPcCu4kIs69Lcpc0yrmsBykzG
-7qxNB2ELI2rru/I0lYXUdOvhHvVhTsHWR92lxtw8bp5a7iDpHW/kLtO0Fl8ZhGujupSEZLWG8cnc
-RRkm/kG8vBsS0B6+R9vG6h5NaT01QdnUa9o1ZZutcwjLpWUaZgPvjMHWWB4HOX/ouJfArC9jkm0H
-Dyl99ZTFfdD1BfASjYd+qlhS+wmxco2Cwiys326nJQMM8kB07jUtok7NcV32taHLDLenLeLf9ayi
-GFuZJxq0BeJ9GHzMmN80+OrMbfNa1h2Z/NPY5Ft4aaORbe+ZmmFGQHNu1AOYrU5Ucc6JLUGL2NIi
-CwxX1Tq0PriRkHMC2R/N+O1REKBHTDUsCRaf7ZRee98l7NF02bLtMz4gApWA3ekmqDQfwpocJy8w
-eS3UxLx/UkzioO5l4CHRUKR9sAEiojqi5uCKzpEc83Lj0OO0B9WQOBVl0MDBIIPrSo9ZwNVCwOLM
-y3CVy/YtbgimWBVvNFBAcL/ywcD2gAipDGy5kGywUekC+H88AWFJuroAo5yr6yiqCVCq0PgBLLnw
-Q1b3n+NpdmNbpnWwBfcJ9J51BtaO53lXbDBLAbwCATZevsrOd01TkKjO56U84SG0vkxDMTHzph+C
-WMwXsxHNuBxmB1qwLldoY6dJBUsbHl8r2iVygW5R26jmwiBad8BIhzlodxT6NXEZMULGvmwXm43R
-xUYlwtd7LmK/LPeqp1Of77TKUxu+n/mAmTCyuyym3WkmSdIbBz8Xd5UBNKSj3VhvzBY290u409pD
-EqjKie3mW9lNfjpO0PJoOyAKzdB3sCGKbP4tkxFmHnvT+eQHfDRsehUGvQ4+pW2khweZgo0P1B/A
-SgAegkQ6fIsoYnIRrcgWSuvadb0KEqgWPnjoxC+PgRlmcRCiTqIrnUGLqkT4Cr6kRkLcqF38eDHz
-TRxszOGuNNmphv1abesb+LE1b3MwD/aRyPu3mKuNmPfINNfxQ9bGst+h3TQ7+DdB4rx5m4yrBXF3
-pBMjHyOK3vdXPFNLP5qk00DvgoyUH/BjwT0hbPrFl8AhCHoA3DoQV9orHleJ7RZW9l0eTR/pEmUk
-KIiU03hN4j4X91EPb5vrEDcwv51Y6/w14t34cWOhbx5rlU/8a7q1mYS9E8nSOzNBfvgjsEDTsNcD
-adOqCcfVH9BUhyfS6hRAo7uJSP4dXk3hfAvYaiv3roao8Rds2QF7joeAu9zNSaTUt5yzLgGpcMZ7
-gPvVOtPvLVvhW1CQYY6wq7FHAncXU4nxFFHeJO+U36btsiEdA62fOS76R15nJlBHZnWi030Qz7UL
-jw6FAnflZrNu/rFm3gbf155NyhaNCdlCSm3g7vQlmp1bKNjzyiVbBYbGqkUJFaS6dkWeN20MrsbQ
-nFCpc0MnB0s5ryb1PV0kDI6KIZs0mLJNHZn888S6YHxMWyZbXEoDNnpTABm2JVHZD57Ch2UJF2kU
-Amnm5kOWrQL8c8w9ppuWxNC5AFAGckHZ4BDPAT3Qy5MELnQuwKFqF4TGEI49PXAgwFiGA4EnhhtO
-Pm1B37Ls0dUYnD5yS+S3Wo1dhm6lWHt0g8fwMSTomJUUe5GW6VTP8qtetuweAC/c2Dkswtxdoqw7
-1jhf/LpvaKNKRJ/pYxZi8FtouvZPGqCee+GH7lvSxkYex8HRu9Ha5A6kUzjrna6FpzoLZweeo04u
-4UzULO+QKWRoSTdxLg/TBmGLA8RMOKyQUs5cSYd8jo+bDgBrAdxXPg5hio/lN3Ixzz4IK/RGm6Bo
-RqgdlADiQYognoTo9l0S82soeHtZjFJsn1uC+/tiNBEc0cZGW0CwjZG7eQr7fZL5kO1ZoOoDig8o
-hoy+HwOA2vjUVKNUQ1CuAI1XM6YXy8HiOZ4osJiinDjumDLuV3yU1guoAq1AtZrSz3bpL3S7pr5g
-awbsGJTi8hrqQc6uVeuJdpfQpxO+6DqVHns5Gwe5GpuFVUBwDRXhaalyGaIemI9w4aycwyGBnreL
-XAiQXd3cI9xFHzQd1FpEPtfvWZfW72M4Cf1owBqHwRykT/BGCAn2DWzLmipI5wDnYehyW+SZRrIK
-0ZgxuR65dP3dMGxKHyKmu/HCDeDo7BcK98X3PVjmU8WmlLTw+9IWY6ABWzPRuWQ77rNgKDv8nben
-74BOuO+HtTScR1GJHGVIK7YhFwEu0cPfDD+iXItELdHn3Mbyqqaws6uAbG7xDIEz9NCSbQKjfGu7
-TwM+TVu2VpA9Bes7xk+rACmK4xEGdlL2UYliR+7hBIjfog2LHLzuM9UUtAvrx7nvOn5kNbdRkSJT
-AQSjy3L4v4VifNsLGB7uYawJPZtcL4nZ00EHGOnnW58Xw6YHmB6sQPYWJA5hyAe3nSDebYsc722q
-ZfwO5oFdWNqEdKaQLh01/Mom525gOjmCZl3THK50tU3DasD3HN9MWxAdh7qT8cVAheP4SwRulCJd
-wq2gYAathUkNgpneWib2Sq7kbQRo1fAlHHpfkAwxs5gSt9RVU0/4Z2mf5v1uzVdkfEnaxjWQ4iq9
-yuG5wg6ZQAxfCpGr/nu/UWe/JxBd+SjFiPuka9qWVkrn+bw3Wx3gWUJYDCJbYlDjtoB7XHI3x49R
-7HV2qTh4AGVD1/p+S2sVFCOQ91du5UguV2uR5K3bmEdVMrDalRCdyiG52Lj21k9R9EmzvLlu4RvD
-ChPQ2iAY5l1bKr4iMNoNrnBzFPhPZOjhZQbztTa8jxYDuYIYEAf5sZ+nFRYRvTaLeoNj6TcILTrc
-fAlvA3LbIK992BYCWZdgiNoruAMueTlA9Ru+TP1wsomrm4we8anidb8tjdXYqiq/X0E36eBY1BoO
-Mye5NsfWkinZ94Dq9MUKGlO654bDFWUjXDZFM7jwI7PkBIgCm7Pbw4tD73K6Ag3KXcMPW7QG0CCK
-61oeCPLp8UPTUVuMGdyoSl0viF2YbKS9LCwokvI4g+96CwuKSFSYH63hxZSaEAwxgpoF5ytpyXpg
-ceC6o2LZPF4hV0HV1uOzdEc0GfDvBN0S60o7Bio8CCzNB3gHye9RuNXfmnGw3yD90ny2dS+uVQxs
-3p6iSr/duqV/UBx+mlWADfVxoSrQh6Cn6mHuSYCYKcON7lOXCCQFAc9JFSOhoIckdGF/QYXUD5iz
-x/VWot5H9bYZRe9ncOz8DgyksWo4jLMKTXBrlYDxQhuLC5hhIhlUKFBXQZNbTOUhTLGBzJTvgdEP
-5j1J59S971Se9ReG9UiHzRqkMBVdcQ/BBE/BU3aEVl1bJIQ0T10N5nwB0FogH7rFW12tcuL0gFA8
-3MAPioPiS+EFWqRLnsBCrINOABSh8h/BHMEd0ZD8h2YxKtu145Mvl2CJMbSEuyJsNuECCOPOEGZI
-PEZ5DtzLSSzShXL6bO3JcbNuqIRfWb7Rr2AAogYyOazdNkPm9xlPhy9SeUIvKdjphzBIsrbE+HCe
-oMOBLvAezJV+LLuYw0eraabwcR34iuMybPWnRMFbLdkY/5wbT+4WGi13OcltfxiR8QA+aWKwilOJ
-odOu7bppb5nU7S4PHRzcmqX1N3YSLtgLZt2XFHKkfRETb752FBoJUHlRNKm4i9KDCMCWQeOm3j7r
-gK2gyo+Zcse11/SLtSBcgdPjh88jgse2S5esu4m6KPgRLdK+WQn64Hs66eTzWovuoYmhkAFKo9CX
-S1IjRYrhKbTC2i9i61EAhOthSNLKH24KyBelXRchvnn/rh0MJFn0sInmbddODGNTuarvodCzL63P
-+37nCRMCyE2xXBHpxhkFgp9+1Anjnzwd67sFV/htIhrz1Jg4k8WKt/Y1ncx85eQUItdX+OYF9Ffg
-Zil6gjxQiOZE22UaIgEB8wI+BE2zvMlnlOFF5+BfVyKfPZUJWdzehpF0aj8GbQxjmhBqRvtV+3Up
-uqmN0wMml+FTYnp4i4KST96yOcZxj0C7TNGoQg1fOdDa54KlLkVVCiRBBtMl4uGcSh0oHL1zw+WG
-mS/b2wiF/S6aDMaehhlzSDu86yI30sATcokW2LzqFJuMr4y9hZdn8wjkhXiw0YI+EAq/RRd0zKeg
-4FBgSAqZZO6+F3X8fR1ycWN1q+tL1xDKdnmGJGY/O5mZEtaHMBYKeFhfhFMqzN65PH/AnT601Rq3
-6qoDw9tczINIPg0rJTeuI1u8D7Om+VAjYV0u03rO75ucewfuYw+OgaYu5qVvpmmXhS7tj1PIVFfW
-bGTfsok6WKcpLq7YNsOj2C6jKedYJwpyR57ATxFf5iAx8LT7dW22j7x23l0jWsRyn0d9tJMsM7ac
-AJlAOjvWKO44Hh5vx+f+I4pu+hD3tH7XzyD6Fq2ZYvjbEOQAFRwmgx+i7eQV6H6nEI7uVbKf13ZM
-S7BozG1qPCwn8QlDvIDNJiVUdoO30HSjDtZHW6KKNSMJjCiRtsclESy4iFeLx8xBgoAOpLRpWuA8
-s6/1RPj7YGT6AwOc/hOscPxVLZbOlaYR+YfMrsM3dALF7byM8ksXb/RiwGPOJabkKH8deNRQywDm
-H55+NucXVGmRYd3FY0cRbuyOB3SNipDxCW8WMQN9kCjW9wLiHij2I6AiED3T6RaWsb0tIOLbhVej
-J/Gn1ev4Jk26+bNoe/aBwre2KTQT5kuvoTpVOIH+Z6nlkMDwNu4ETG0XnX2G0RqS5KXJ6+stntxc
-eLzEGxh5BC2oVW65HpcaSUoQLmHlOSziQOuaSFJ41B1PBNCsp6xNGH7uaAQlBMCN4cDgHgcXzXWG
-g2sCWimK/60dpgOXxN7w7GQKksCRDB7LTZTWpYYX8rJD1uRVyfTWfQRMn99GS2LXQqI+2kpZn7K2
-ia3DUSXQIyzWMUmHsqYg7F9ms58/Q+aNPSRbzhC7yabuBmWyD3FNQ3+R93X/MJpu+GoAsb6BfMTg
-923S5q6A/R39GDg0UosINzDI/+0U3otV4QrgDWQzEWKT9M6pIP2w0BGlHFDE7LFZV1wddvBg/cBS
-z4lLE3T0SmgUych96bBUFM6oH9tsgCwdagaOgjRjEHLSyFqu5QbL+AJmrtNa4IgnXwixot41k4Xw
-UYeKuBR1379VFPUE+kCwVjuIiXfX8wahhAOHleVFpvv0ew1j40vg15HFiBUpRmgy94DOcjpVgCFz
-W7qMZE2VxSMA9AINMUhlgjd/08JQ6asVJk/2xgzRPk5WZPTKdBusuedZPwWTzW8TWCICa68gSVL0
-MUziyxzaj1dw9BriAoO39l0NI8+xHI2KBARZV+ReGUSjaGFoLd8tOYFFqrQj3UrDQnfN4FGc4yo0
-7X0GFd60kKNp0z3NlnCPbwyf906D6iwjTZ4ALgLdHaT3SFexiPW1ADvOHntMiR5SYufmEqqRuBwb
-pNVNgVhEjnkTuPUQ1GOaVnOcgaUe1wgyDM2ySzgFb2+1EVO+21zTX3nl5xgFWOxpkROv37Y2wa2m
-0hpuXmKZ1bFNMSjabUAefoRF+/Z5yl0wVfiG/fXiTBRWudXY3KLn8oMh/fgllwLe9QkylK8YMvib
-LrWmqVAzqzfGeSJuA0gxmPo+H9EErtxADVx5+NLOTyH1EmlHu7DlDeNRnVSZyib/pd9IoAvVG5wC
-khl8hQCpOipDTXt6OPnggeLczvnXJG5ntZtmvdkny5fwXQZzrKNfAxhzy21dPg7S5l/lMohmn4VK
-PUI4nX1YBtLNpaVEPgUtbt0iQMX9fiNdDtGlJB/24Zxgl+bJYsWOaBhb7+AtPbbHGb1uXUSKhdt1
-LXLkLBvK4ncJ02gvhi6CMgBFA1tU7dhnroBU6eB2WdYNPdocVL7rHYQTIJ2+KTiOz417MqxDGhql
-oUp3UuCHqYZ1wtIum1JdBZt3N0ieJ9SyXviplOjotTuw86VET22cPhO/Jln9VWynloIPpuku60iW
-7aIMxoultZO35dbGCp2pdDFBSbzbBlwq4zyWA6zdfkQ+DSD7i+/QRsc4t+OniS9QOeXpMtESPWaU
-NT6lCzo9JBnGSw2LbgGJTkrRHYKwHrrE89jA1Hzb4tuls/31GhCrKmcsSqF6A2yvhAszROSb2Yx2
-H0XIMWAEWcPRVI5y7jGgceq+m5cowB9fhzch7ZC3+W4L5H5D15eViWqTOylgnlc4v4zouPUyfQNJ
-OpoWZkyWbyDEOzgjBz4YqwSfeazkTBo0rMa8vl09hHEKNEr64LDC69RWsYM6ZxlL+JVj60TsRnCu
-7zFUkajt/aDCU/gWn1vHYAI+gd+Jv94imy4ID9eHaGP521E64w6A63e3WtVhVMXQiLgzOcQboedt
-oPiuEhthXBU2CzKBQEch2S85WkaPsulqWB129RqW8CBtt5ue9SjVYlyDsshAY3K7cSMQ7iRis+Kq
-nbPwOI+jWYsR8/+HBrvKwGBSZA16FWyoEYxbHKgW3Im6cIB7oRBN4vqw1DTbKggTjxhl8s7URQbR
-cV4mcBf/zJQwwaFBlXqBnip9O6Q2+dHQnC2IW7XxJxt7nxaxEFuw77e636oZZqkP8IaXpAjD1mto
-YzCRYgjTprIc5QjvWg9tLJfBe5BuFm1e4GH7Nxb6aXGJOa2dkO3b7AZDovk9B0QugKkdWiHQsrXw
-ac9Cg0FAa6eNlJ5r4EfDFneTCJn4Qpp2Q1OS5f0DhwvduJMpyX1JUB/c5q5D5gR2EQyTg0Bv6DN7
-0V9wGoHXaxzGMkUMZQZVpchc53LBjE/iS8KnfJc6Fs9l3I3sXT6HqKtDkC7vMfIJ0cKYwgWJ0AID
-Z9NnmEn51Iy3S4uUt4Ied38h+wY5xlqTdapW26xfIu4DgXzPjtddL0V4ERlOHuaN0TtgfzdZwD08
-R4f1fzg7k964lWQL/6IEmGRy2pI1aJ4sy5I2hGTLnOeZv/59vG9jlQsquNGN3jTuTSUrMzLinBMn
-tKJptjls3/VSmgBgUWh23/8jGTx3cKsPvW+mW1EE3ZMIyjrbuk2dfJhGynNaMZX5fZxFc2vMRfRR
-l1h4UBwYwW01FxYhKCj1pyFT+PUOoE9ntl7qP4OekMdWOWPwoku/6aeiebULATC/LAOOW70TZbQk
-Y+WCX1tibnnn1C0MWvtAqbpUvhGa8zMiafFawEzwkLnRtI6FliK5xq0UPins6uFbNTvRzOjihbEH
-lW43H42GZwvZuvUhMHHUfIpR50bXxwSkt5na72LKyayjrteus2SNNFMUBfcFz2fnj50cLiFH6L5F
-yGwLL4hbaV1P5qIsqJk8u5/kTL7LksWtPgkLW8OB986xB4JVY1vaQ+0USX3JrHZ9gmDKB3MT2hkw
-JRbajn7W1wqrLBOHFXPTyWL+zRdagxWpZupXwKlPcowAS1P88UZ6YIA9QqxJzDMeQQmunQcQ4fqS
-l/fp6jSwcwt9viLsGQXlB+m9Zzmi/B2IXCm/mKKaUngwyodkctvRhy+P252rCkxf9CmW9w0piOZb
-zLq8a0n/G8KBE0E+MQq7pzN+0hqS7HDC/T3Iq8FLiXW0Jw2xPZ8rOgI/HDNJlJfLXuU+h2R+HvpE
-PIYyaWKo4KZ5K9IAtHZgkFzq9dNQ3VlYk/5seHluQZrlHX69pX5Xo4UPgOzylNEbK0M8JYwG/xGA
-/Gn7xJj7u1yTbX4ZWN2yeDXXy9rRjAj/l4jV8Hj1Gt7mbUsubzixGzOxshWxj8Q2ei9SsFmaKBsK
-WtGkKTRRlUZ3Ot2w/bbphmYbBi0U/8REW77vrJNUNJlm3acyTWs+dUiuUDIU+V1LIaa3RUso9udk
-4sQ6pWb/7gxtflBzP7SXlcNsdkr1sZW+PZjTGzi4rfwWEfLewvY2Oo8V8vj1mcMPs6pKg/SvDMHt
-sKHRAx9Yd3lOpkG+zGnmSG/QU3FJ03v5YdkjwDMmz5itJlDAP/rMHmwv03I4fDO06/O8Ffyb82ao
-SWmVnZl+nTrmb3gPE7YDFcFKFuf0XBWqpczCNF77CXYCLF4Q1AY/hT7Ur+Ym175nQtX6VjCvMPbH
-GJYfHDmAjLcj8N8NXnLlQzoa8/tEg8ULG2JCC8VGVmxtukMsX9VD2+1HvNMvAHy00Ss5Qt/Ilops
-ExqB0PzSWYSxn2VnvGhmET/NRh299mCzL1h5ymgPT50/1UlsfjRLGU0eSY8G5g83986oVXU9uU49
-NltzcOVPhOPVwtjsBBMAJlGo9FxLs/FHwegu80KPiqDZdKhBOMg0dv7mPk416GENTxwP2UyKh/Km
-3lqpiKpt28TqssVtArppKtRHYOQgAbJ0gk3UjNa4s+OlX+AZTU1QMZSiDa9DM8nZM8yA8CfO67wr
-+97I/Jzf7qKQpQaXTEPmR1qN3X1VLCS1ImgD05+Bq42tWZhT4ldaZmiXS5A1gYcxkfki9AlGqAgd
-vdslFLAPdipk5bumEPN53ET6I1NgcAbQZERuYJd4uJSdBJ0J1zzAC4Ogus0Ko8oI7mPxTTTQY7zS
-TPvwFlnZ91prDeFuFF3+aldkR35cAFZ7mQhN3jM9qx67ejJ/0XMBPlOkfWl7TUc/jnpWOBnKa2Oe
-9eUqbVQsPCMNQJuG0LRvaWOo0o3DO7xsos6pCUrC7GmvG3CH2IUMb8n2QVbbyaVO+AB5jupObplT
-GT8maTgD95ijiLcluiQFnKcDK1edtfj6zPR0T6ZL+mRoVA5ejp9FyD/eLBur0BcG88YTHEfPS/PR
-YqCrNjA+8sIa8yDFw9K1LqzUEROA/jh9i/iUT9Wy0GQ8JW5c+iIl9vlDpEfYDRdlXe2AhMK7Nlr9
-ObLRkk9Ci/of9Htw/Yo+QIAy59XUbiLltMoPRYUUQwWOft4m3L83dAIESGUXEF26QbBNSbO4nIXe
-VJ6MgRgwN0EciW9iSxEbW3XHXCBGve+zDt83XgM72KqJIsJTOKbuiqETyZU5j4HlOZM2xV444Ezk
-ZwWA6pkzW+ZHZdbRj4KQEvER7P68lKREGwcNlHpY0qy/mpVWxldkZ9bVWGl2sTeHYoh908wR1ZA5
-gNZIOchmkw+6AIBZQg5PZJrlyzD3bKQ24vA+p+j6MVET0OIjSgwOFqcKvqdOWM10Uy42MiCejmQL
-1dtcVhVpyi4HU0/9jEm4Pe2zRnMj+7H8KTJhxpeTbplndF/3P60hM7eaHvX1DdA9nFdHU+RMUKqt
-3+6Qx79muNWPDPT1SVUW0omgwtHHN9KQ7K2rSc038VCp2w65BwoxOFh8lIZ5gnIYVOrPOhbkmG6O
-zZudlATBPgIt5yXp7MZP0rjlpxhtjn7nVIXyiqhVTy7So7cok9OTVttO7+V6Mb0VGETLTRIN4p58
-YkGhUvPH207+Xam+eUqnUnM9YrVM6IFCd4JyTDUkLXNYxVgeWcVC7ba0nRdjAAPUgHs8MFdlN44n
-+0m9mbJT3w3N7u+VoED1Wmdof+paWJCPUARVmwBa8zxng6R0QW9cxqSklp/FQ1uiWcGzGrNPA2Pa
-oUJkwdXPqz1vYfRuq9HssJaeFwOfpzq2NgolTLwJ+IDSZ/S0zV0NOAd+rBsx07vxDIM/rxBseWtM
-pmmFH1h5DSOlrgoHuBNGLq2eMJjKfqXT0JQMo1+y2yIj89zOQ1hBa0Hv5hs3GdS0mxJo7Xqy8tqf
-7VSxs6DUku0S8MDAjTvTa5Vq6RsFAX3ccS6WR13OGl0roh4fVTgnD/o8SEAjOcLC8XyUlY9eA2Y6
-c7ryduiC+iZXuvG9Kaj074GdDOXXKK9eZzrrXsJyzr+1VkqKzSD0BE1YHBhPkTmXdODPsXEjoLmj
-s7II67doKFcFIjVI6o3YuHX7XitS4Q29y3sh5j6BToJMfLQsRC1JhM2lN9ZF9zHMQfBqUYKG5BsG
-99MgSSCbgONyt6U1xp1ft0v4XXYSMVEFo7NO1IigK8xy5DvHOdbTXt/r8n4yxuk+ZzBZBXSpkjcU
-dRQhczf8mpienXtRu57itlVxebZUafFcQghzoN1sin0BMKB5cAeR6wE6AUUtVhpdR11V2H6j9IZ3
-eOQf2tWR6iNGe0SA45km5uxM5QHCoTacuvuwDZBYJKvQ3lNqjGb0aL14pjbPbg0TqJsvn4jbqunC
-OwxtMM8NZKHOddmBATerRIkLZ5oYRKZl72xsQLUnQMXqRQtH3dzaWgYuOzSxvEEzWVi+zZSUBY+J
-2oKVTqQ9+8RZxBukXsX93DMeZiNqgx886qCSN1wBOfohir1nERnVtDGiWTsbBfQ7MTyc3pzKDB5N
-shi+kyX6d2kssPw4eMaMmJHmTKEuxuhJBrEZXGDJOt4WNY4xO64CgQ1pHm9laTIHGQZ2qEMyd6MB
-b8ori6diLpsroYgtnt2FXbrpMlUvnrDm4JY2xeFh0J3ufVCdas4kniGXRQYVT+ZWBtCSynwDxxsJ
-f3YTnpUGHfZgsXG518YaZc+kRHXJVlukDbYeRf5My9VHzPlhBfzbd62WW78rFWXWVjRD8baGB6o0
-OA98vMkkzu1gyrE1hC99qZ1R5kQhIyx4oYQDPANGcZM1WAcij7GCm8XOmOa3AMShRYiWcti4QRlW
-pEQqvljMAgS7CpjFDoCB+mNXizm9Sd2SxzOv81Hn+DTGRWrCOeF5o5UZNZSVPmjdlPwcy8V+jdCD
-I8iMDO1Hu9QURWaG646aItQ2oa7RYxj2WkBabg3GD05hctVJ/ecUtFntG0VFtmfH5Of24ug4QhaZ
-dpboFXqmaYHkJGAndbRNHFJ2bxBUol4CXYfYyB31c0Q5kbPF6Y65TFYhjLcCMRzRyuAZTopBO4va
-misB8O/etXpl3FUg0MUmGI3xpdZ5NTl8anzXC0YNeUmaWJdDi/bLK9wyfhpn6DIwqdG81qd25IQj
-roy2PcK+Bm+oSlHN2ykshtVI7YIfrkGrkU7iMXWnECHbKkAsTaYN7Yd6iAm4QfHS0ET6PBpteVNo
-8WScJVml7QoxdWpPcK1T3+7KLlKoJoAEGQUEnpANF2kB/ylXJhFNnePZdJQOZ5Nr5vANeWy1RCAd
-sJchKbRV4pMPvT0YKfeJHyFo0DF1pgXxMTjX6Rgzzaw1gMevmfkHelBMqWUzV6ZBnwssAVrBuxF1
-26GyM2PHlCAg7aQ3mucy0cePseANwpELxnmTdHP9zXalyK4Q+saXCdEi9+1xrargmPkjkMvEoWeT
-ez3jQyou6VqExraXMXlTkRo/4PhYtUnb1N2AW2XObaNyAGGmGy7UA/jfwroWjtn8sFy9Mi8js4y/
-IzroOhKuoeqRzMQCzchka3nqNxUKrLMQSK29op22vR4Qmve+A9y1nDEdsYqjW7jWSX9EYbG8k3gN
-6OEnWwXtUxemdttuGyy47HMBlf+Gy/f4PIXG1O/h5J1y41IVo7HoBe6Q1NeA26G9iBcXSzRsuxzL
-vYn61I1Qg0UOyXVZfmuh8RFWabH2LpBHFJslTs1gizjERRpFaZpvVItGCKZ7vQCqnzEr1AtnqH2H
-N8Uiw7ZRmsH0uY9dWTv3S2+MGmTlwjbpUK73KG3H62VoF+C3hciwgRjpH0JE0z38kExrME0nfYpL
-aKpNX5YNrj+oAEky03wGK25NQk4jU4p+B2GIRDLWdR26FBGlUAyCYwN/i41jWi12cFaDLceYFJHg
-+qWmQxlCwRXWDtuxCm8mrNScHch9yttk6FBzChk5nnHNQrlcNIMOaWWI8BvJ4zhsIxxULzCTkSAs
-WiEExXHL8R0nbTA2dZLPgZfOhHd4RACfc1zBKaYRnNhou5ZEvpmpntI/XGCjidvqkE6b3BjUr2gp
-iIEiZhKNJ4wcjNZN0AB7PcH6ocnq7DvCRKPaUtVPT0MY5dG5IPGG24gr494OdRy2JllxIjur6CSs
-oZTXI8nNW50Mzjfsgl3ER0wqCraZu7RUxobe3TROrL9GpW6bmySZtPPFDMvqtnHL5n5kwLSGdsNB
-wV6uqX0eGGnjK61HFUZGLui8Lqz2RxFl1LkJtqAEeUScwQZkXN0TDuCQOp5wuTWKTAjEb6K/I0wt
-g28kKRrHKsHRaKz/ewdU5w5eqZXdNaERnhgdUfBMJ0Z2NuOsOm0QPEAPIvOpX2bFQ7upEbzVF8xM
-0X6HU+EYe02A8fnABJKnRLOYHklwEc5WjgblJ+7n3a881NuRhDoNn/DYHe7nqBl4YSorfKu7ef4d
-2sjsdmnjpu8uj3SztbhYMBF14tRY0CQ2utCZlNPnxEN2q0hwb5IgIPGj9E5/gtEXb2Vlx6MnsYZ/
-gsUFoxnbbr4uy9F9w/sFNQ+MsVnDAiwJkmVDOL+yJF/eY2ordiUzNG19bg/KT+LE7FY6zxx8Lbaz
-1xhvV4b2yIV2ewVSB+sZrz0d7eAiFi3KJUd8omn8+CG03UU7znrnabY+mtwDJSJURknYbJ3KRXbN
-28I4JSdUS+hDyNY3TB3T5o2tWdqVGRYMG4jlmJV78sf0R10SlUnikB71ekXoR/CY/0Rumtzphd2h
-M4z1XGxRhAd3HfEp8knzJWVaXPbfdLTi3yu4m0fTgkdQvI5XeZkZD0lmqOK+TsYeqx03HuYz3Rmm
-b23UttigLo2BDVCVdcF+Lo3koa+MFuRpnGlambUFtJHcBdPURXdSZ0uVJKxtrErKxamtrWajd9ya
-bdjFE/HRHZvivFCT3uPgPCrHBVs1iQ+m0fF/R7Tz/KzipRI+XmsljgaJnJN3p0Q4sQ+ieAiuB2oc
-BF1MqX+Y0M19KEoDfmqpjYxWCsHaAxUhJ5tRwCBv6LTsfWym4DEg0/+FKdQKs87TqAgE5IBbWnGM
-F/pBUHrktAe91PHEQ9500t3X2ZjCstIhlJ9N6DsfqFUqhhoneot83qQ5aJRLLf02S0nsUl3PMhQm
-gCSbIKBNhjzStu/Apsk2TboCLpMG+d0mZrykA3nQ8zwhrjGe9LmO3ycHZa+fZTZZLtYLTe3XmhPc
-FYlCZ0TmT5IL7Rqlu9LIrW8i1xHy9IEd3LVCdotfO0E/erS/oWaqbK18TO14fnV6S36zILS0rQwW
-TWwi14WcYC5UGPtpk5OaZsIo7qXTOQ9MbixfNNGaCJbKMtR94iHwIZPhiita0kSxGTkHb/jJI/hE
-jpufNzReDVuJ73vn8/doj0GE5mlZxhKNCADqrzaNwxcdNA1FbT3lMUwsR8zTjVzMKAWHVXeJwA1x
-ABL4H0ExR2qDImmBhredao/Cnn/SQFtX8u7BvpEcI8n3egOftG3YdPZNl5hiIlRn0gT7S5Lnpkrj
-RzdI3TtoQxCXMQgWsQJcU+k5lqC1ZYoV6f5MZHsjaaDU0FFZel1Js4NHY1XwbkVAFbvWrRO1mdFC
-uOi8uvlCLVaO14W2vjCJVmfxVg0RsGyGosPYytyxb9e60ySo9Mt5W7Zh4wf9ALaHf5N+1Q6L+h6m
-RDEPg8uY6UOUJTunqUhnMG9ufo80/F3Fdd7pm6HR4Mtjh64CvjQH0je7Osy8YZnFMw2I/MbTjCW6
-Ey/y0ZhsrFpqdJc60BgpGhN0Sp3Gm7Rw77s0WEyPYj0iaQik5EJouvg+xsbyPYiHXiIIX3FmzOD6
-N5W0Ru0vIziMvzCBIlh9BWcINzCju3yuQoF8lrLamw1bXtMu1tw4bojg2JY5mX2o7I5BUW41TkR6
-6Hm9naF6lykdgx1CURWeZbJ170UR4aLhujD2l8YwwmZAh7ebgLDf0mLBW3+uJ8oVXtsxR7krGkEt
-2kG7bylWi4Q2xKQs7/VZIgtAM9bSRBNo8F30yPXbeormatNok1S+s0hIxUnr+7fBGMW4HftGJjs3
-clPuVORaZFoIUBfkc2GYbCSQYPxrCgFmtv0i5ODnZQcKMTlziuTCrfX4Av8xN78eh9i5M+M0qzfG
-sGS0aZVo7G5p+YHU7ulT4GPURv5LpoVsd3O0BNNmnoCsdmFEYryRfMVmsxDEyS0SWCo+bFYJCSqk
-Bw9xbZNL1Iy+EAg9B5KQmbv6kRUTw9Rj+j4eym7G4aVmDMA1AxG6ZzSzChKybK3r2oR39o1lrpAW
-O1WCF6MKJMpbIpcnIFJuZCCRvEwgqSjxRmTZm4z+oV9lUM3fy0wmtwpVurYKBsGOQWNtCtGy+u0E
-A8UfuC5YIeghGVdiQth0dqa9kvGNnU+JUpCCDo1zKyujlvtAOctrKEbtmhbTQbukmcz4NZrSWMGZ
-DHkms4TCc4DhaIEf1YpbmgsMiYbf6CNodgYc+IiAuFH2lGj3EUMPUr9UGj/YoGnmY9820Mp1b0Hv
-plrrns8i7Mb9yO/9beEFn84UaMZ5Anpy3xkDGJJ0ADkRRPBKlqhPbsgOeC4yrS0Hb2kBMfZOXDcA
-WDrdBN/AJDNSkHLQ0UsVqXNv5SViWJ6b8LbOUBJ7A1/5Bwr14XYt9JDiaBn9YEKU7R19ksHPtAJB
-9gdjosJQk5MhE2GkyosbzVzmsIpmG31WBlyRJxjrbnHDUz8zwDacYfUqeoxU0VH5am79gs+QlQGy
-FdnPUNYNKoggBVLC+DCr0KQX1aMsUQAQZNFfKBPPYy9uGUi+4RbPr+5sLQN5vIEWZASqNVHhkDai
-k1bZg4rpZfBhoax302nse96g1tiVQQjPzdFttloXNqT4TWVU/hqd552eAO5sk6kDxjadBWFk5OS3
-qwZ13kRTPV2TuRStdRbCaM/bSEmn3suyFtftwKt5lpalce6Aieieg8E8JXw5VfK2pRnwVxNoy60V
-O1nnjQgr+rNuAX+7o/cswNtU2CXfJlJmuWWKV2dfLZ2VVU/UBeJJuACj0ECVhj7fSshyu7GSL1mx
-KI0ckPLopxsmg/Aov9AoBpKmqX1Voxr/YTMx1IVycQuTIGEAjaGzDQHhEQDF83fUpQPzNlxal3ZG
-RS+PV/Yzc2i/7rhefR/+NDdgeADWn5j/aZicgUIeNHdncjbdGuEPhLDSX0VfBl6f1v3eTsfpTogM
-s1cRhPx0Xb/J0l7uv17+sOF7Xd7C7BHjcWxsYcE+91rTw9p0yFZyj9YryqEMKXN/pqESNOjurG7h
-KFxvMVV42UwZsuCvFz+cKsZwOVbXNQ3W0bBcSz+waWFOmGVC3RVeGvDkbhsZcJFyRgJuU6qKGFkT
-KFpIZzb8eUxFRY/oNi1Qm5DEAHjXVvd84i867D0//IsOLFYQPAd1k/NzhKUiDkNhbpLQ1X1Spaea
-VJjAAxfe0I22zbrRxN/LmfdFAQKgjyHS8BnIAT2Je+JLHVoA/PdnMcBwdb2Vxl/OYvVEhO4VJXGR
-h8Ct9M6FCDsy0Mi0La1y8/VXOPSGWFdbHT7s1d0UTcyBTUo1qoIR7yhBkAM77yq2DeRxtEuRFk7m
-9M6QX/2EHdaxY4jlnrTM9QxK88D6AoFkW6YtPDztgPqdhcyENFeixe206Rz1nLuvCnq3S8P6t/EP
-63hDrG8ZcssJZH15cAKdkg5E9C/QfRjh0XIF/BtX33PFW3AOEgS1/fWn/Xujn9c7OF+zJWhMqSoa
-DwttXE1V5+uZdS/RYxhoxetuUzt1/eCaWbj7euW/TzYrM7fUxNTYZh7V+pf9YfnUzmYpY8XJZkKS
-dhGibeXhrcp/9Gr573syJJBjQ0cGIM7nVVg6NtyaG22MsrswV+mbk8sLSPnxm43e+sS5+fte4L5N
-+IA9hhDk1/y8nKPcwM0FJ7XpeM06oGEfxPEHzTXy7OvP9/edUPhs2Ewih+7B33f9vH98Plq5mmaK
-eRuCWq/PyWDoxaJ9OPYReNKV3ADnnhi5fnRFQ5EC4XZt4EX3eUVJhV3nPXe+isT4M5gButwuWZHE
-JkrvcGt0TviMHDshjE5waIRwMFI7dBcfmQihYG6Jxk1PveIuVVttKrsdiv/hKDKCCE94qRS/2sHO
-YsTkZBR8y6W2a7TOnYvmaKpPrHLs+2FXLhFPrYNFD30LRxudbhqxSodCwKK10F3OkkhvthMYKww+
-WNjXR+TYYXQ1F/UAaRnR7OCGWWVjhrOzHhE5uPdjgTGIP4WhLbZ9RlJzIpKsLiifEwdk1Yat8RUV
-rhGHY0pKt8/Igek8bmSYv8UQeuhDU6QrS3XltMU6jlh0w9PXWzwSvngYpLGO7OYd0vXPZ3IJnMUw
-EYl6eArQ0SntYN/O4K1GnuzqLHBAIQy1VwaCxxPbPfJrYgIL28wsA4KLOkhUBj0uI6fmprdB77zo
-NF4nvMVyOGNYWb8L6Y/efr3VI7dhTcgYzWJInqTD0NKObofGLoPLQh66MXG23PXCODWR/MivaOsW
-t03iUoT188G2sKsJk2K9c4GeygnVe9ome6NtpbaT3VpLyJaWqEj2iXtif0dX5iGghY1hgfilf/4p
-A3T/U8c0MMiSQXum2yoF30mD+HZmMsY7oR2t60gnZ3AikB65JSynkVzgdY28bf27/gikDR3vNg2m
-fNe0mi7aQhu2GMGKexcA5URAO7JFhgIazC/hpqyTwj8vVWeavoxmzhZp/duIBmXZZDb03cbwR/cV
-KuXnVLqn7IqPbNBdreEZH2QCoGgHPyn90r3rDtyRmN9uozWokehsCfahRpPCP59RF8mHy5ANpt7g
-gfl5gwk958BJbDDAD2jjdsiYxto8Ncbj75uwDlzQmLFqumCJhw6s2uAwxKNmDIzAP+A2HVPkfFEy
-nMjEjqxCdiL5D8ETB/2D6NnTrpIXpgsXbSMRrWRhItaJrBOn/sgqjDPEWp6hRLqmmwenb9KiYSJ7
-R2OBZiS/bfDWKTdlI7roxDE/thAJJWb2Gm8cJ+HzTwOhpMIC+NRbRoxJ41xvfPSKJwyH/w6K/00U
-xS6L6fBkPwe70clXxqkA42S76QWxM563cYv8o5po+t/SYF3NL/965PDiZVYjCnVznaxyEDZiVN3A
-ByTMhlFRsUVOtavmadp8vcqRjdkOYVFpvG2MB1+/7h9BYsS+NWzSmkrcrWEMs8i+YpZMu3PsPvKr
-KTw1m+f4elQAzDElvTucsDfoWm/bwDooEEQL/cc0UcjVIKTRJtGS8r6fGuPn11s8ckDYIlPMeGSw
-/P+r8s61mKYVPuQcFTGNuyXkQtkt/37eseQBFzONNeq6B+7bbmvR4k7PgddnWnDnTPQ7tUk6nxhe
-+XdaABJl8pIwOJPpAu7B3Q2sCLepJMg9g8l2CLUxZaFpZvyGYt/du6NDC24aTjB4bZfvv/6MR345
-si3sAk1GFUqglM8nZYi1uK6ZV+KVlgqf6QAyn+nMU+0uK3Ht8KwURdHu6yX/flaYS8GnXIkcHs/D
-Nzsa9cIdGaLtBUax7E1EWa+ZgJC8EjrV+V1AA6/0yjoCzv164SNHxsEF2+ECOty/w2G7jL0kf8Vu
-0BuiTtwkpsq9tqrGf05j2Z6LK7xOvxWO3wfvV1lNtPI76L7czCn2tDUGeLyJwuYqZFlunjigx44O
-TzNg4PpF0cx9/v16g4lYyFQpS50p3mPthbQuiwWm9IGdXGNHOF+bYHZ7g9z68d8/p81nZNiIw/Ex
-16P1R5CxY6Dr0DIR/6NlupNYPm1LLBVPlKjHDqitUxKTQppUqgcpM5ZPlYHhPMJkK7W9Fr3CqzEV
-Jui+qs9oE2nPvt7V3+kHcZlKGp9bqh5C9eddLbiplHQI0t2TRybSSBVCSVqws0i9MMo6cSSP7o5K
-f81A+F/noN7HnQppKC4NuLgE9BEwHRjSpC3dKTtLc1NrHxa6f06hYUcWXQelUPvwRXnHD16HRUeq
-XC302sxMbYOnoo1rRgtf4m0T5vnmn78n0gTsSqlVeRqMgwCTjymdtljr0BbV0WDkx8tUZ8/0f9n1
-RJf4POqnKju55gafSzvSOY3qyuG7kkIc/IRT7kahBT3hudy9fBsPnXY9TriIuXFXnAUO9JGM63Yf
-oY5kDqCAovLC2YYUzPHJO3F+jwQdF/MT4rphEeAPc8xoRJ3JhKgSfU0Tbhmmi4wvxC3+6698fM9/
-LLMe6z8uY2J12aAFTMAJlmWyvKZfDbYYF6lMPzfc7pbTLM61EY7NyepkU2XQ0WKYHSbzJNqJWVXH
-zhe/+P8PVyA8HFzZEkO5wFZsOUQ/7isUqx9GU6fIwrTwYmip077e/LFPDADOg8LzuQ52+7x3ZS3M
-p8Ca0bNNo8Z7jS4ie87HE7s6EhhI26BDMMg3+C3XXf/xhVEHq2zqKRaw0atfgiSES6z18I3h26fy
-gaMbovBiOKaDvlc7+IBDQu/lIsk6GgaJb4IGVSBkTXQi6zi6Co0lBB7wD4L45w3R2xRUOqNTGRUc
-xs4OqyLVbyi36IL++vc59uUcHkN+IyYYGIe5fEOG79DYykKi03YCdfrGLgf7vqJr+Nv/shQDE9w1
-u2YO+Oc95e3Udq7gR6qmrrp1gi6C5XSQ8qIoGpPv/8NiTLwChiPPloelOJY2ETM3yHoHSJhd33cM
-v0Qlvhm6LN99vdSx34o8jVcQS2ae+YN9oWNSVpsD3xiGmd9jZ+HcWM7gnIhV67/lMHBilGyvEBEv
-xKEfc5EN1hwvnLuiRTvp9ehFzwmO41MESrWrejp+vt7WsZMB4IdMEcUSPNbB82d0NI7nFvQZnlqF
-nyy0yDUJg8JI7qMTP9bfewMyYa6dzcMHnHG4t1FJN2vRVa8d1c0+Cur70mkukMtZZ1oTDyc2dmQ1
-B+9l5loy92WVnH0+h2NvCCaOQ7Gbo7AuwtwVj4x3on1H9ssdNn3BiaTz7/MBui4ZnkMeodPtenCX
-Y81CtC9KGtvh2V8quczgbvr48PXPdXQVJh1yjcEz4D0/70qIwZoWHJpQteHCqoawuUHGmf7zKfwP
-mIVsoUIAeD4460D2dEg5aOuLYR7upAxW2QSdvxcqH60feh1kv/95WxxBkCadSa+wPAfbMqysicOI
-ugCXMTL2XP8VF/Y/zqkGXaAoUIQlAjqPx2FeqQsMJ4ploMYrDZx0W/xjQJhV4SPHoElN4zc78R3/
-/rWI6yYjOCksSTEPScF6qOjCGVw0fVndX9lLElxr/WiM/xzdaavQbKaX20R33TlAapwczQ8ikBR3
-jK7c5mn+saxys8ZKTo3C+mtDTN6hDLc16mSdCeYHlwq330b0Gs2Isp7jl7wU1Tbton/G6FmF+pR0
-wnVhcA+vEmJQFN82lsNNOhq1lxYOdjjjPKbG9dBXSPeS1kVIR688lx+3y/okV3Zsn2vYoCwngsA6
-fr5mGeXO2vSLgqnJ0MvEjRFdqdjM//X95zlZ52zxMPMyExo/L6NhEd+rFcujNczZuMb4USA0PlFO
-rbn2pycF2HMdGbLy4e7638+LNHHRNl1rvfb0CVeluLfis1yzd6XUPSbVk+DQ+FUPyYkz+RfEsK5K
-wxHYrlpNgw7CIXpCHHsn63XqL9zIucqHrV4GfmYlm2V5/jp4HC4FgKzBQJhsznbpgj4IHjHeEgvy
-UDqDrSm8wfEk8PsxHy4FnutbJw8QlPGabr5e9PCE/LcoPD+8pk6KcYjvJTgPmWM5RR4eHuk9PQLZ
-dnFm58Qqh6/z/6/ikPMaBon14eg5iOgQS2C2FtHqNCIsESsei5OST2/5KdHEkcUYQ2XSiwbrzZiM
-g6jflCWjysxVkRgFrDVWzgMPGi/m1AX/ePDZ16elDg6+aQWBvdQsRX/iSCNDHuwxWPnXlG1dBfiH
-+RiAa0SSg7jY9zJCfY9DI0HG3I8wxxBui73715MAQ0snBHEKyAmQ5PP9outgSUyLBsUgriqq2DbC
-ZTH718gL/fNplYNbTEGCL8BE8YgpaODhnfWipfLl6538fQCAI7BndbB2AVSyD36VKROdHi7YqTG4
-yPolJzwdMpp0V28J2zoRH/47un+GJWoeFgMigDKBZDqcUjfik/B/7J1Zb9zImm3/ilHvdHMeLvqc
-B5KZGixZkjVYpRdClmXO88xff1fQrtvKlEtZLjQuqoFWvZShIZJTMGJ/+1tbnwdKWVTSIcmwZpRo
-2Lbas0bK648YcMttZ/b9MQBY1ZviRD2BlJsdmBtfPcXskck9UXBw2aKPc++I8xrKeh5Z905MF0AN
-atGbzPTQauqng+Dy4JxStjHl/UFAv4ASDn9P5zp3NlqtGacFeXXO0S9dPeGK0dkIUUdhIDJQ9t7N
-fZZNTmROo0sgXoR7ubJvYafQRqon0fXbQ+0d0fehWOUS10odm0jD3VteC6w4LVjcumZOA3jLAfp9
-Jim/Nkmso1D/WQ+GGMx9N8JSlqCkiohum4gojoau6DNNXg5V7fYtfN+HocQgAvjYrhp75w12zkAR
-TcJKPxjNcTLV8xkkuf6j0YfGUcSGme6uyaAZkx6uMSVIhWbpPjwxYLd4XNJDD/reQ7h+HJN6gHgE
-WRC/0iPtQgWjBy6inKfMbfU0+zCBNNjG9LcdCOVevWEvnsF1LKxyKjcOBXzWxrvXUddz8M8z1zFK
-mpueBh/wWdrREqTHYIuPjbJ56OPxoVeI0NGD68Lo7yfK0DOrvrpLT2DTH9IpxFy594F4kdu80B0V
-K92+Y4g2CzpzbTD5stI42nMOAzY9LVpKnZfwM4t0m8ZLrn6CCxc/LTFE6gOOpZ+cfNM0NRm7EqYJ
-AHy7JyRoFrUHATq42MPg+Jpl6eMhrvw6SjL/l5+hnaHER3khZtXKrEazuO2izpROUm6IMxaj/a8/
-qYzi8IziZhPvwt1RGlpbgyLjGeqXMNqqziRtKxXe1N84FrZVCnVAKhHm3n3kkLSQgV/jPiqT5IHO
-6PajNEjmp7dH+dnNgd2DRwJ9hALu3qyD6yKshpzO6jRWkiNiWyOLrhAl3IR62J3JFWQHta+qU21I
-httfH5p3FM4yDB+vHxTaqwtlzGkv1BDnzifFGB/JRpBOaPc2LnPIcuDTTPOSuf+QP/D1VIt5nv0W
-liUW00wJuxdQGqnvSE0Cw8PW6/MkLcrjyGkPlVxen1qbMiCXTrZlNnj7en0k14MpV/ns0pr3STaN
-x0G3b4LFPB2guMBt7Y4tvfk1bwuTD4qkCjEAmVXFprv3WqQHaWTbXcx0nwIsuHcq4ODHlaLFpgdm
-torgNrYhRRgwncnd25dT3Cm704yt8N7C1ED5BV/N3tA4aGgoSxnaNjFla1OQbMoqqjfkHdHw0DWH
-lIefnF7G0ymF4EvGwLp3587KEuihChMHEHLqTUVpHjt5L/lTlVbHNHzeAPyrjmESO8dvH+jr+UzU
-BfEqYS/l7tlXzKOF1qhFcBYBG0leKpeSn+qts63gbB2Yz346FPt2mkFhGvLW3r1RwQmNVi7Byiky
-6vNeBOMgvYirAU5aJ4Afbx/Yq8eC6D1MFabOXStq9nsvbWmihdo2aMQwJhAeUgPmqkrJT3t7lFf3
-iTCsMwQTKLZgNpe7x+QE+M4WUFTw8nK73cxjlBR+ZkbGV1rEbJBoVXIobvjVadwbcu80ahl9gDbB
-Bh4dn5Wv6OlzYimdn9fZcODgXp3C1Y2P1YEFFvVrc+/VEC1zJENGAik61/0JyJLco0WoOHBbvB4F
-aYNqPLVO3qog3HdPIXDRIbFqmpWdtDU2dTQsgJvM5cDaV/yVlw80yxceLB4tbnLVBki6OwoNWgrR
-Tzhe+iCQP03OQHZS2J/MmjW45BBNn4byUIXo1ZCcMfYuwr0tzNv7275MsbRJa+mniNtG8Scw5obn
-lJ10qQBYunDsTmDr5m7z9h0pLv/OgbI3Y6Um7IcMiudy90CzaewHOSUPqtvGbu+Nm/JIO1f96MAw
-+8VM5ozdcfZeOywYe7POGKfyH+4KnwgO9+vp5ePbB7NuSd46Gm33aCazjWgAZBT1CGOBS6THRvkI
-7cUnBsUzNlTf3A+NewpF350/vz32/v7z1RGKG/fF+osddKY3IllLOta90cML7z5Z59bpr75a98+k
-eOBfjDNlBViIgnH0q+Coprv+Dl/zaXDggu2/YfZH2XvD0JWfZJI4mmVLRIgHP9ArvOrAs/xqq7Q/
-ingmXhyLFjeKnojrdV5vvqTezbNx9Hh3fShAUxGX/a3bYm/axc+czUrMMPUG+6kHhsC9g7l5sXjW
-LRjPkwN3griX3xpub8p1CK5k+mC40fsC+9V9KtzTb9713YFhfjJhvHx09/fneVu0FkRQcVSAsDz0
-Io/oIM/2Tf/x6PfWvwUZdOiCHZgu9vugOlurnEiMOfjs7XjA4s3nxX26/Ri5l63/yLbAhbl54MVy
-6Prte+w1WB1qJq7f7H1ZtvIRwVibdht9jE8CNzvq3QMnVrzr37h+6t4skuq0UtJlKA4y8nL+013A
-nx6MtgOnUzyqbw20N2XoEolEEcVLVykgfA8BHRFl058OqXXomA7dK3uThm0lrV2IB8027vvgOAaZ
-XKlknhUpRJJDNedVanvruPYmj8SWVAPu2PcTmF0Q1+BbW6LgvNvYj/1v9N4zEcvut0NHuS4/3xp4
-bz4Zw5xIgZqBtWv1tL0rP9an2pfgEsUR+nb1ON8Up/GFdmncHLhjDp3evQkm7KbYLMUdo3HPAGDg
-/hyOWeV5gWt51abYhL7t2d4h6/YrvWVv/lT3ZppZLdKsFQ8GNchtfKz4N7m3uM+BW3F6y63qHnyP
-/2wCoCaImV80zdFnwy39YsZuUzsvZHHLkkW8UXg+NN9h5aB7zofcI8nvqr0EbH3UHOlnzsmBs/yz
-efXl2HtnGazMnFEjYa3ijxvzLttG23E7++m2PVGPD8lmP7uklBSoW+Croy6+tyFI4FUnc1O1bgME
-XlZowoVSpc/PfdH4yXL19qHtTwQs+5E+0Ts0DbM/voXds2p2sRpEmb54ktZpWzBJwJWVJiZqbV4O
-zDliTnn5iDAUDk9q/bQi2RZ4rN2hMls1J3UgQCugWf1D6RQFvmAtOzCH7p89MYpOEYvdgGia3ZdW
-dMKqiYWEetTRnHsBe9I6bYas9eRZzS+SKs9v6WhSLn/5LCLisK1i0U4d1BT3z4t7s4SX0LQVkY3k
-TlYb8KzMqXqXX0Gtzw7di/s7OQ6QPRzaDYZ8gy6sveeAUJ5mcSxp9qxiKBwPBEZ7CwMOlFJjlFp6
-kylDB/c1t8DXIm63kgsiMb/Mkjm4M7qiK+EIDMNwUuemeoWhpCZqqIkr261k4pPePi+vFt+UXSmP
-mQpqE9Ywyle7J0YnS6PoLIssS2UYiB6RsnBmNgRdG/lTS9wrNGhjmJItQafDY0Px8SlsndD2FQqE
-yzapNPNQo/v++lJ8JI37gwoXxFfijHY/kgSrKSYsfvJIWkjhDWuqSyZF/jvaP0yCsRrs07lSee3G
-w3Rgafv6YdO4aDjUkIQR6bW9txNAV2mc6RLxms5+qPFv3HYwiC4Abx4yiv5kJNFRY1KJR1XAzrN7
-kGErku8cdYGql5i4Keh58ss5ARpKqer57Yv8+rlGxUT2gh5Az4a8X5UPLXnKS4hWngURZ9M1EzlP
-dXiggvJqk8Nlo7lSw5VJDZlXgDjiF49YSH1CS5Z+8AIpCtyJYFE3yUPN5YbKT+N+KTdWFmQbVU70
-cwr62bORz8qBGez1o8dnwHojupZwmu2LbfMyjGFZ83TZIJ3NTVgG0rWeytgCnQ4kzgkUY4guv3x2
-xTxGow9uHwWxfve4cyPKtTIL6LdvS0A4s55u89zSjn99FPzNol6A7YCG2d1RwnGgPDUnA7QXYj0B
-IgEbJlP7l8+fLmsciIKwRrlyvcYvrmE6a6nV4Q3x4rEqzjO9VfxYAkIzAhH1834Ktr96VMK2gamS
-Igh3jr53z6iz3GZE0oKJX+LwNCml5SQgmuXAJuH1hGKrBq2bHBRVt1e+Q5p/qerNdusRE1v4sgwG
-J4PVfizbhoRpwxgBxE7tcBJI7Q9X1n88Tf8nfC4vv78923//J/9+KmE+CefY3j//fR4/NVz7b91/
-il/7fz+2+0v/vhiem65vnt+dP1btu21ffH3s4rLY/52dP8FIPz6J/9g97vxjU3RxN1/1z8386bnt
-s24djs8sfvKvfvPd8/pXbubq+V+/PX7NOTtx2zXxU/fbj2+dfP3XbxTxBYvkP16O8OPbHx9zfvNT
-XL47Qnv9+vzua/nuus9+8tvPj233r98k3XmPfkfBhQoPzc/U7X97Nz6v3zKs90yWjniuURFZFfHw
-F2XTRfyaar3HRMLv8bpFX6RJ7Ld3PG3r9zTtPbUokDEyTlBqU0wKf3zSnev3X9fzXdHnl2VMlNm/
-fmMonrQXqyR0YP4I9S2mOlZlMBB3n0S+CVgGNxVoS6owJIteaP1IvAKNMRp70UsSwQCiAjjWW1z3
-oPoWwoxnu2lBAMp2LqMcdwTwNNeqA//bhdaLg58smbB5hNYkNZdL0BLtzuOGqBptllybo8c4Zdmm
-n4xw6qU7u5WJTvSMwRjjc5lEAiM7BrKXjbqrZM2QAIOShlb6WpCoFtieodKJSiKuZRTBw1gUC4Ev
-pKA0H+QxgAakAyokAbIg1B33fgi5XC+I6z032C991CmwNb5VhORn0DY7wh+vg8FvG4e/GDtdc2Yn
-PTxuGWr0ZZZr47clxzDnaZ0df4ZhZNnugrlTActTOrbHu0k+bWStCwjOtcKLmS6nxCXc3XyS0dnr
-bZ5EKd0+Wexcx5Qu7oKyae7ioCuviRorSUABpXXCwpTfCiErXiemUl9YiL7nnHXWBIlMmlyvNGkA
-hagpHpK0KW8DgK+SlxM29kVbePETntdE3yCwNoCAwfOJXAWhrtLxAz+eqAtghKRgTiJIIn6MtUgH
-C2bJwddaK5qrRdYqc5PZs9RvSFDJsatOcXVph4KYX0+jOgAG0okht0dHpTurnO9IDExhaDn0YnqS
-mfSWwFym0QcpxhTP4asa+WnOAKPJIncMHpqqEh0OlzABU2xvjUlWP1dK6tyWUxl5U5OZIjdgMM/k
-mXqWGxEB/2E25w4WXwjYyrOarrk26YEpYIFJyQWxeeGZ3DYjoSVBD1q5bj7PTh+fBaRSkhtrZjBT
-9e48TqiAudo80JwYZYbeuVIHZ9OtMsPOPYWOtjNckrzlCOVgy9OZeZh5MLGlJzLZ7U9lGRCw1/SR
-fFnE83JVOHjKNvU4dcOxRKTHV7z5ym0u9yUI7xhkvdta3Hsee0ryOsieNM6BfpF2opYKYZ1DPd4R
-jNr+LtWpASR0MpR7Cua5QBmUeE+yfqJHjNJbddIPWoa9kLixa3O05gtLz+ezFjdP40pKml/HnaOS
-rtXlsUXGuJXUrpwrBhs3Nsg1xOx0eabfGFdrmMrSQ291w2e4XHT1Wa1IJabP+7qEGEtub2oG52Rz
-lKYrj5KK8kP8NoRIEMyK2xR5u1Uaq25gYhH24SpNnn0ieJV0qbbTZj9pFeuCVo/l90AOM8xvZDnd
-kJGjXY10fCh+OmbqRyOxZFaBEHfB5s8qcY2xqoZfbMKCn6js6Zekn5JPVJI3rPtdLZc4N+oRzpJa
-mcGxKqnzbU6axE2rDDmtQTSx3NcJaC8qV036OSG3PiPkepofWxj19QbcrP402D2NDYQM8YdtSKun
-LHVG0h0U8rkB+5ry7znNL/eOHYzLprMW5WO/GGBBaowzXizZWN81GwA8sac1EKiQozmV9KkRyeEy
-OLa2VWl0iwhF8prJJDQsgvVJYKocj1/MMSJTLmjryXJLyHiFn1cVRC3ZIoqL82g/kODg3JPq0TFx
-SWk3bbqwmu7McFRv6HYMWl+akupjnhUF8aB1EXPb9kk9bRqKkJlHWiTPb8WPfKKrKJ/8ik6Oyzxp
-SDp2sobc+iZvhM9NnwkmJsPI+jZlTTkdsaBwCFVUqnHwIr2LSRf6X+6m/0/kbmoF7qCk6gjO/g7f
-1OBmHJMffrMCOLFP1e5QkLf1ZxTOOgkLcr6GTlP/+ymcC3ztyhvmzHRfoTgrshIMj9c5WLI/QXHy
-sg8h2pEzXeygOKu4Fwiuyk4elhYO4MX/PyonCHU98q2+1cebfxKaszF42VWGnfyPRHNKitzeEpcA
-dWDlc9K4SwhJoc0jWT9aRhD4X6N0zjUmEz81pejzd1Rn3fZWeDUOXf2VBfV4rRbtUBFa8Q+Gdk7m
-CJOXpn0DAOs+tTOctKb3VeJvv/0StbMq2uIyngv7MpDbBLztX+R3WlktL5uFECtpK2EWdvyCcO0P
-eQ47Nd6Oczh9drQlyLeTqtE0F1HA/8HyHMm4azdhKwcZ2aA/hXmmi1WCNyfq6vw7zLNRzfZkjJQR
-zkU5avdLSvKetwP3tBL9aF6MSPXy3A7brQFaF9R9nY6X86zr4zYZlqX3eAv/NyA/zTgNR2KVyq5I
-rseX4E/ScMLb3mLEHfBnTNZfwmrX+N6S+7976Zd7aShv7F3/fC99jYXp8Z3HJp5mGjwQ33fo6zb8
-+6/+sZG234uOYgvrO1YwXEtsU//YSGvvUTbBDyA70qOPXvZiI228J/AOrCSIEjQ8Otj/ayOtOu81
-XDUYlER7ACqR+ksb6f1tNI2ZBrqzbGN3MsB07G6jddJs2rbvc78AV+IlhFbfmGOnHS9aOTy9OEM/
-9vAv9+yvduxiKAc9Afc9S/V9QbnrraLTI2JAkL8tb1AGw8sW5+vfGQRPPB4npH9nT8pCsA5tC9yI
-H4GJ3UQEG/ik5i4HjIyIcK/OG3tkjMucPDzDr2RWyUnlTK2IPrDFpny2ZuLziBOeP5b0UVrnBL6w
-g6/W3by27uyXdZcvdeuOv3MEVqNhGf+VZYUcaF4rNZgBvQ6mv+SquWbhzYqCJCfak+5BxyNkNzki
-W8aOt/EcTIVPJilsaEmWDODR+iRZpKsEdUZYxxDOfmVkyrMahtrvRTwOX7NQIy7ZqXLyY2szSDTi
-TfMF802Yd6GvTmRuHeM5JSCnU3XpW4ML+rzsFWoKRhTH5F+pSf9ME2cMsR2PZuL1lPmuJ5O0KEDg
-hnpb2GXA6zHNEgI/EKq8aQma2FusnFSrsiDT2s/VHi9MLCfhZ71XRxF+MRLaA0JObl2zL9TYp2/O
-zLxltih8K7LefatTveu9ALmm9BaY3XeGmhhQ+SdTfeqoH5xqEtklqNxq8sjfV+HOKz3TNMyQhvq5
-ZMVQ8Aw1Uj+UIUHqspUQA2FVlvEoJyYo80RViLCb2XcNHvtRtpPE84AESdRiOS/CAQgQGIniDKz6
-NJFq3sU6qK+F4J/Ybnr7OJbMKT2b25pED9NqWhj7oon3SqllSoVRYRoPpN9KuJ2mqbkqOjWWj2tD
-4zzLg9RqaEfLfC7XeXMXqP0IEtqekxuCEssvRVSGNjfCxCsvaYnoIdwhqxSvb42p+aCYBYbLDqFL
-/wCCD1jJZOnJc6CEwS2k2/GGuBdkgwlgZbdwwBUB4C05BbOr9mHzaSKv54EKQHJp5Es7uV1sZndk
-59QPKhRG2VPRNi7IT50DP6wU8y7FsHq+JFb3ochjW0FyK/p5E4RWfxEYszMfV1Fn32uxY35pyBwl
-0xZXXOwjZpRnRqIr50ppciX6Km1vnLBIr4fWsU7KIu/wj1dGc++E5Ff4kUVOLG84aT6WUvLG+RxR
-82C0FM1Az85FSvlAg3QVcus+DiOJTNyuVRMdET1OrsOMVhi6hrTEj2VInRE6O+0dXptnRLGbS6IN
-iM5z2XpGAwedVc0SnmCE6DE7IG+CJ4FRyvpg6qcr5OVh9hQ1K5GVFpWIosVAvPGkbMwfW3WqrobS
-Mr+mVRccs70myAAxSLqfovihhNzOQwZ/4XNg9dTt+tRcJhreTHpoVTSExp37sb3KyM7LSAHSyWWz
-A9T3zYxc1buUFDpkSylUPpjTJF9MRk+SaUIoKEGvKqnyxB5nze+tLbUBkLFkfjKlidTOoqCb2UUE
-IKC+TKXwpI3qYNr0utwS/5ZIVbAZ2coTM1THxIrBiyaKRwQyqJ7Z2enj2KHjkD2uEDU5SuCsXWOY
-pZMFszGBn0qRX3UVLPFNUFpEss8dVSNvHIssPlVrpyDippez24hENpOMzDZUXFlNSA8mgImM49Hp
-iw4zMtI28RVaPfp1n7H0s9qk649Sc0yv6yHQ/IwpyPZCkbzntmpdal5vz9QlJisKR6+KK2JSKmkx
-iTBJZkK5CCCLPqNbKZNvp7EWH4U2ePbNsiimelQmwNBcS4fSzTQ2kxgSicc/HUKZEF01tm/DrCdv
-JEackch3RnPflOlKY1eJGCNPKcWE00iT9dUIyig/M4o+vM6jYLivSJC9sPJWMzfNEpT0AjhFxFpQ
-JbivTlE6PHyiiQVJdYwTb8lK9V4jY7L4O9kmktlHkGB79U6kTx9Rvfkr+SZEMqqntjSkxDP/er5J
-lhE8bxCvy6McKerHyhbJHpR1UGKcWK6mI0cINPaq1RQjWi3iZGNJfrbqOV2mRZf6qvIo1VB9Emdk
-wHlvBGcWAts9LpFm2gSrRpStelEgpCP+12l9QwhKU6pOd2Nc9NMmWxWnxRqc+7FX7IdFCFLZqk2J
-tUvhS6tmFSdk00CSncYvXZkLVWtVuFLClkmWa4TyFVlZ9oTwhh4WZrp62qv5wttvVczMoW9z4k4I
-OfE6IaoZbaV8tFelLROim73Kb21Dm5a+qnKWEOgsQkdooVh1u0FIeO0g9fUmF8JevGp8Fobuz/Ws
-JCRuOmF+36x6IAWE4EZbRcIqlo6bVTmMFlxt8AmEopiu6qLCU3VVZXrxpXAqwoFKsAzevGqS+qpP
-poTkfRyjXkO1FALmAvz1Jg9GVM1ZCJzFUJP1sqqesdrrW11b4hOD4scnKRLSqLzKpIMiNVvs7oin
-yyqkLquoGmp9YUKjQ2ulo5Cm+FwosMiA6Y2UCFl2EArtOMXho46hLOUtLi/PwgZYuxQbEHZLuUsp
-W66CL8I403Oij/l1s0rCplCHaZBcLmqhGPOuQjymaaU6AaqZETSoyeMI9lRIzdRB1XsrNhCgU6FF
-0xY73umrQE2it3HaGuQWLnQhQbVexeyBzgS06e8it9C7A6F8k/eCCJ6vgni+auNyi0q+CuZSjXZu
-GoX01K6COjFRiOu2ViNnyUJzL1f5PVil+HCV5clwRaKPpz4x0bNR7qUQDd8Rav4kdP0+1JvPi5YO
-m0Wo/pHQ/8e2Ti+MtSig8Xq6ntZSwbSWDUJRQVjWYsIk6grjWmKAlRl5pag7ZFGsfY7XYgRaqXqd
-ryWKei1XjHEz3iWihtEkBuWMZS1tAAWnzEF2ECWPIo65LdK1ErIWRSotls6atVSSDrFGrvCgoSav
-xZRJlcNhI+lmbW4qUW8JROVlLhUe5FnUY1LNnD4QB9iTyU0IIQWmQaJ4QzDfYLqGQcohryTqO+oi
-Sj2BtNRfnLUAFItaEK/t4qFX0iTYpqJWNOUqWbaFHhrnQ9LUF4QSJtdGpVpEKIla07KWnWorKq9J
-mWvu6tAy7liK2Ne5xvES0iLKVqnTmU/TWsxKRF1LM7U28CEFyKe8YG3bG5jGuYPy2WRtJWpjxTja
-khfVxfgN49N06axltGitqFkVxbVxLbSNa9Ht7Z2K2InsFDBVWtUpshr0FOAmMPc8rOS0E6WkJ6Vv
-pFJ9lUmV44va0BFZcebnt4daDTN7Y9EeDNseXwY2o30eHFkBTVhkee0nRJHfEL1UStiYpOChtiWy
-mFprjrh040wjeKbrdbwlyG7+ls+1o21SQ63uFKuTQSu3aaV8IDeWDN4QTLnk6oWsfJimsbyBamXL
-PtdVfe6bYTF9mmerky5WrI8U9ZNvdIu0V8Ba5gfDGGdi8CajxK9eps7j1GvTgxKPJkma1WRfdbka
-3ZiNvnwpxixH7FBbogJH9kffPSP/I6WMFw6CV76A71aGH66BtSR+U/69H/qj5C7sB6//0A8Z47vR
-4KlkTSZsCyH+h5cKh6BB7igj6x9aPQ5v/YEMI0XXf8WIgIL6HnINXwJmlMH7++Mbhvaevny+8Eet
-X9+HenFuXn/o176Kv/czO5/9T10WMDGx1eKF+ytnYO+vvDgDqvFeZzkABVsnx0587Z4IDBiwJfBL
-CJ1n/VpH/AediJ/ZTf7kRvjz06DJ77Ed0QuKvrVzHyjvaQYH5qEBKBNf/7j7ABTSK4Xwlw8fvwzu
-OOQjeif/uMovT4Nuv8dqDI5d0JDFF+8I7ru/dBf8hR/64Vt6yp4fm3//XwAAAP//</cx:binary>
+                <cx:binary>1HzXktxIluWv0Pi8YDng7nB429Q8OBAyFVOQReYLLIsCWmv8zXzL/tgeJLt6IhDRgc62WbPdLGOl
+QAQurjpXevzHt/5v3+IfL+W7PonT6m/f+t/f+3Wd/+2336pv/o/kpfqQBN/KrMp+1h++Zclv2c+f
+wbcfv30vX7og9X4ziM5+++a/lPWP/v1//gfu5v3IrrNvL3WQpffNj3J4+FE1cV1duHb20ruX70mQ
+OkFVl8G3Wv/9/ceX8iX93//1/t2PtA7q4WnIf/z+/uhF79/9Nr/VCdl3MZ6sbr7jvZrBPzBKmJCE
+yV9f79/FWer9dZ3JD4bFuK5z8x/XfxG/fUlwg3/hiV6f5+X79/JHVYGj1+8Hbzx6fPz94f27b1mT
+1pPUPAjw9/eqfBmD+P27oMrsX1fsbHp4hZeC29+OBX7yB/A/e8mBTubCWrp0opLHl7R+eWe/1C9l
+kL78T2pGfOBSWozo+Pb6NdOM9YEz3TIIp+T1i/5F/Jdm/vUHO6+g+ftnenq0///S00OQvdvAe77/
+ePc9e/fYwJ7+x5yIkg+ESm5I61hFXP9g6KakuPhLRcZfRH+p6E3PdF5LZ24xU9TD4//bivonzn6o
+nKOXvBXhdPKBvn4RSP8Q2jj9YLyqRZhntfMX7PzzJzmvkr/ed/TU/7dR7J8j3D/g3wFGrV7jxgHI
+Xb76FzrO3nrkOUds/mXfu++/v6eQ9z+C0XSHv7/tl+3/JaVf0v3r9T9eqnqKStYHiwmTWaZBTMKZ
+Kd+/6368XhL0g7QoMRiXQjeFnC6lWVn7v7/nHwxTciEtS8DhdGqK9++qrJkuaZR+EIhiOiHCRKwz
+pPhHpP6YxYOXpf+QxN9/f5c2yccsSOsKd37/Lv/1qulBualLaknQZ8KgusWkjuvfXh6QDODF+v+i
+mpeGhlcOquB1TO0R2US5aZqUZXtv5GG9PpDMv0SOMWrpIGVQpusG+Dokl2vCbaKa9UqPqoF/7+NI
+H2OVuoHGHj0my/HbZXrshD3GkRNY4JAj+E9yPKRHgjQqh7joVaGR9KEW1HwqAjPcLFAhMzrCgHoF
+5YzqULOpW1DlIR38Sdd0X7+/2t2t77bOeq3U+upmvXac9Y2N328c/N9xbLXFT87N1XqndnjNzQ1+
+3TsOrm2dPa6t9vgRr17vdnfOFldv8OYdXmrbO9xtvVG4JW4/vWSd4f27p/Xdboe7KdxOrabL693a
+fsZL8AjKnv6Cn/HLSil7a29BF6/FHT9u7nD7K8fBrZ7xl91KrVa44xfnRu12T2q3svGe1Wplr2zb
+nl62wvtxv+lm9jV+uAEneKKHifxma+8/r/bTS1f7nVrZt7aDn8H1dpOBeRtPt15tr217vbtZTw+K
+Z9vgnQ/2C+66xUv3t4/b7eMkJghqerdzc5OoieyjjT9fVpmxoDFJjjWWhGXFSKjf36zvnnfrJzC1
+sl/s7d5+XKCkm8c2OLeNuYvVVRkbNWxj7dx/+fPOU3dq9fXWJmqBDp2e+MCVT+gAtA5tsCqq3BcT
+Hajoy+7hAXq2IW+oZHt141zZ9tVlEeoTNlwiiLTtkKCr10U4guCN8/wEa4GeFgjQJdFNSjxAp8rI
+hdsGoHB/tb6aDHp98/ofvt89r+Ebd7DVm+eb9fPNXaHgODfPz9Clut7AsHYPm91ms1ltNtfqFha2
+t6+2MOev19ev5nit7Nst9A3Pg1s49v2VreCfq/29fXUF69tvtwvsLHEzYfEBN4y0rRtCXs4X5wl+
+A4ktWTWfwfmJDUyPcEBiBJKnHCSu1s933gpuCXe/mxweYnvA105t8NPk1Z4Ch/uf29zu1E9nu93+
+7NT945KJ8AlgL9nIDICT2qJhMhnl3e7pbm3/3O4Ctd6sJ6HfrIFxzuPNBJNQDBSxUsBAe/rVuVs/
+OU+7hxvnSwZs26gvV3+ucQOwcrdRm6ePLcTnAEUedhvY3WoPO8/V6vYlVPtHqNpxDOXcwyCepfq0
+ugWSrB21dVb3wKH9zQQwl3XLJ1u/xCfy50PBR5nWUx2WCsC+UV+Aua3Cc3/drNXDL2QGewDRK9u5
+WuMhVsDdy09A9SnGXHqEWQwaxdAN3STqL4D3G0jhZsK1m0fnzrGvdjug9fYZ3gKwBuIjSmxWqwLw
+ul5D5gg92ykKOF+gnPWzs7u7A2DDbu4ePKX+gBWtoRNEidUeXvgFqL1Xr1i22+zudg8/dp768TDd
+9M+nu+dAPY3qT0/tAHbAobsH/PrjB6wRmL+1bx+Bsfh+v31cPW5/2oD87aN6QhTplfLUBq76x/Xt
+7R+3++3q026//f54j0hh3yMc2KvVo6NerhGItvdXziNcVK32+2tg9n4L0TuQ6quYwflPiBvBFRQR
+W7Y3iMs3V/Z2dQtXf33h50f8eQKFR+fq/ssXGKL9fUEjl/0dGfqxTViem2kCIQZR8gr/YLubGwch
+D66vbGf/K8jZC3agy8t2gJbOMdmoFaLNQBY0IY6bO/g/XG2iOkXvQsGL1J9TrAdcwi92Ci8EOqwf
+pqgMRUPx+OkBb9ipWyQEa/w0vXe329zi+/YRQnP29v1rYgOxrqeoCY+6hefuXtOF7X4Ph5xMfT3Z
+4N16glNfbWFCED/Qeu0Aj68mNTrbLzfIdJztnYP3XFbAFB3+2yFMaiGftQxdmKZhCkHEdP0ADNtx
+lB5p0kpZhtY6Q523tqCsXl2mcqzlv1OhSP/QwpCGYcw8P3Or3LVoUik3DeXKbTSuyrSPn71+LJwg
+ktrtZXqnXHGC5J9Y6NVZDAXCMVexPgoue6tUTSnZOrC6fu3Hra7eToVyIYSlo3ThZMaV3lhBWBK3
+VCHzjT9IUCS7Ou/HBWM9lR2f2g1coAhBej5Pm8siJn4tZKn6iPnC9mWfNSoqOW9UJoesUnrR+U+X
+OTsOkZO+uE44NyxioY4yplr60CpkSos8aYdSZUVq7IlWcKetovCGNJa5wN4ZUqj8UOdITqfQPBOi
+kSckS5oIpOI2V61Mx3UeNLldhUm8v8zVGUmaTDJmCIhRoDI85ornZmppaVKqNqjCXROE5tZE+XbN
+MirvujIT28v0zljhIT0xw7ahzsbMbEGvTPUx3ya6m2ursDWDBTrnRMgNXercAHvm1Jc61JabWOMQ
+ZLxQMi781g7DMRycOmjGZ+q1xQKxc0LkwrQkQV1ucWu6fgAYsihNqwqHQnmDETlNWxq3vmm6NmfW
+4Ji9xRYA6ixzFhWmAT/jpjlz5ZY1rlUHRqH0uGGKy9BYBbUhlBeM3oI/nyNlEkYFvFnnwpgFBV3j
+PNJ6UqihJLFTG7F5W4WjoWTilQsOdpzyvTqYeUhq5mDtKPKy0sEVH7M73xfexoqG4rPQKbvuWFR8
+Lq3my9ut8ZDkiSADre8iHYL0SWKz0uVrjCK8BXc+Z/OmzkzLRKFP+NwWK5n75aj5pcoD2XyMsjy0
+NSuld/8GLzB2OLPJuLBmnuVylxW+FIXKqiRQtM/MddBm5kLL4pypmxZlaErpUsh5+VtKEZRBYRZK
+KyU1bUvG0T42E/dnklf+kwRe1QvOddYCLRNwKHFHxmZ8hZofl4FJC1WjX7aJ2+YrZ+xPozDE6u0C
+FIQRY4pcliGmBznwYpMT3+s4IMN3NWF3SWU5LNbrBYeaVb+TmaOpI5lFpWlOgWSGuL5mBU3M01IV
+tKSqSmln89EPV3mee5u0y6jKTb5x3SjaUF53miratFEjYf4CipyapQnXMYlhcP01HTnmVwYJCssW
+UUZP69i8TyvmVzufNkm1oEF9cqPjhAqUTOQ6BrU41+epR195lq/3Wan8wI/2JDbadVHk9ClryxvP
+1Pp9WeXZqowyXVHQt/sh8m3ooNZruWsGrVhIhU6RRiK4wiMluqiYHs3cvhuQH2ltX6icWB1VnScT
+Uxl151GnI56Rq6BszYeqqZN+QfunMgdlw0J0tyQ9TY8Gg/ZJoyNS9DSz7DILI3ukTbqg2bP8HVCZ
+mdjQ5nL0CoA2yrrWabzYsLvC1TYJ89Qgv2ZhV7wZ4sAXFAzBmUIncobdluhSioyyUHSwSluTPbNb
+VqcL0jsFH1AxMeyzTKqjKz6Ls2lmuFEl6kJFnjQfMmsoVjSqwg1p4vDPOijH9WVEOCdHmOw0HOHw
+kzkiuFGGqSxHRDLDjuVOW1jaleESz7aspLox2kHWTu8hC1zgc4nujE+z8fqiyFih4iQtr8Iuy3a5
+34w3YaOVV43FmU2iUF+Av3PCnbJNgmEdF4zO4K/PraSIyxTCDXT+pdaavlkZsg03XSpJrvxUq/+4
+LN7pjsewIKeBBKUogRAW57lgQ70u5ZVXqNatUscsitKhSdgqLe3fnnYilUYGY1JOiMn5zCMiNo5R
+Z7JcDV0Tr0g0Nuu+5m9PpiUG0khIkAhiKs1mekuHKsuYMeRKE3m3oRFLVBSKe1JEXMUlWbDOM1hy
+RG2yooN41XmGWfUm0IoEsavbNBCRabtGOQ4LlmGd6kkILshkHQxjpen6ASH4cRD7/piruCXV3re0
+ZJOlCdlnCbdWuTDbp77TtEglaCN1b3cFTI4xrUJ+jYKczpgUUW+NUY3oP2q1fIwLbtzpxGjs3ODF
+LivNMVS57/IFjs9YpkTfBRHCECbsZhYgUJOYNdU7pKK626icyljleuirgLTa27FavtbK2C9BmfLa
+mT0QrpVXQ8W8HAmVn7VXZlM0u4TWfB8waWxrV9S+iouqWRDrGZWixYG+AxIRixuvU44DqqVfGCP2
+f4DXjWl4Kg4Cy+mCrNrzjDa3PctClVqysougDRZIn5jtFHRNRg2dGQgZr53fA9Lc7dK8KIAoXmjl
+yiApXaMX0968EVtABd0HOdVkSLfm2FK6PS27ETY7BrWeqaoJRwclbryluUivL9M6xxHQBemnJdDL
+0WcZasQCFvC8zlUk0z5XRaONz61mxGLBVE6scuKJUQqVoTNgzkEsGMPc6kiTwyqjwanygV2RuEl2
+Rd9UC9hyjpSA/RNqToFWzPCy7tw0y5IEpAqvUmh7aE4+Dl/9jAwLyeE54SEXggvonEhdzMClSCw/
+6I08VyUjwarUkOv6nV8sOPQZKlOYQWiE8IgQszK28oQviyAAhPGxV8SsfFVkibWgoHNUYNqwAdCw
+jPnEDl6kW17sZqqLBmljVK/92TYyfXNNLglFh5IzRBvMj19nCgceJIyk8DUvyhUrGnddR3VlR7QN
+bbRDFuYwZxk6oDRdP6CUZkPhjkOYK2m2ny2R0lVquPmCrU1R8SgNADtoTU7YB8zFeP+YiF73RZLp
+WqZ0MyPXRdgXjwntsp30OBtV1vX95rK/6sY5irphSMqYDqoz6x6LOIy7AhSZJyHAQvedPk0j25Wt
+ESufu/427VtvNQRcblJSGD+1QdtXPM3XPu2ih8uPc07IUKTJsd1AdKxTHPPvEwzerB5WEwn/WTSa
+tip8s13o850jIrhpMMFReQJFjomYRTcGVc4z1QelEdhDF5q1UxGZmws+cE6bQjK0jAwJ7JATshyY
+jMuilNABxpmGaW+HPjUV6bS1ztttWmvDArVzbFnYkpCWYKaAix9Ta/rK7JM2y5WouXsVtUOxy4Gg
+zts1ZKHZwZD/IIecN7VFLEo6eEDDsErK66zxk1XPafB2FUFsKKCAhlDUXHJRmmmRDPwpRxX+bdxJ
+ZusB99/aJsLuD0H3AbCBusZ6HZ0f6McaW63WJtuPAprcJENvOLmbWgt4e9rlmMhgN4gLzFFQtU2K
+OyCTmGPGSSIyFTZucK0NFl3rRbzPOi6VSdpbq+MPuUZc2Lpwr9Dr3psyzxdiy6T9GbLAv3WKEQE6
+LdY8CRgL0sjai5EEmK2hr+rer9KPrOekveZN11G772Qc7MpWGkst2jNugEoAe1gGNTlSrJkbaJnP
+SZPITA1JSCPbJ+bgdHlwTZnH7KZy8f832ygCj4H+M6XYWppH7MYQfTISoAjz/UB1FS3XIhmXPGF6
+7GOJ6lApumOwIOxDz0sB9Ju9vhRQq+kHnh1bItsN6Sh2zJX+ggmdShCkLIoUEbWHQebFFLDSJCWH
+BLOIB5ozZHFhKYK9kU+yovy73yWdu+DnE+7PuYPnTV1GwBfDhtyR0fpRwXuvoJnK00RzmCz456Lp
+xj+LRsSOrqfGn2iB9Fe5T7NtUhrV82UVnpqrTtE8MVDlIIsEqh2TT9KCeG3XZIrEpefEpvgel+KZ
+p2hOFTJNVMOWMspT+JwoomDFJA0dVjrz0qoLwsDQi0ylmoGCtWiaLVwlXdDkSbEhdcbQu4UjGFPs
+maV4RlhjAy6rM1WGWjnaVhoEX4pxSJhT5i77WETtGKjI8tEvEnFcLcWIMzbLiYlUFvkfOkfz3cFy
+zEWUYrSttNgt1tyLhtqWru4/ZVVJwwU3PAN8GJOgTBbo+E/oN2OWGlrEuprA8c3qI3AxetJdGTkt
+K2PdYZXPHyOaoEzu3a6q14brukJpVVV88kuW5gu11hnJYxaL/UwLqfW0MHpsUUaMcxVj0QHsCx/u
+2jb1n52JXD4lvVTx4EY3lfVZLzz/zaEMQsAIHV0z7Gpyc2ZXJJExL3JYMh9YnNm159JxI1s9qBbE
+fU63KLqwf0pRSupsun4YZtI0dLF1mimvatxP7RBSsRp06V7VAWvE5rJ/niMm0bJC91ES/JtJs2aG
+4Wt1lKkRXfV9rmfNbZcKzWnNrHu6TOoM+JkTCYJhosCgjx7zpbuMDyIFXyIU7vew1odPVi3aTZTG
+8RbDTP+Py/TOsIb+PDaOOboBFtYEjunFTAuSZsiA65mwHM3H8LIsPUzT8Z63q8zCuBkhEayhUzyz
+jcBMcq+qw0zJgZWeYn3TuBj5pXSnGyn6gJcZO4OpFnIqNqEcmZqNx4yFfWrGXqOlSk+S0HYzvwqV
+VmDoZ7tWZXyvh7IlmwKxZqFyOkcXrUaQpK+LJDNbaepOjw0qQLdL0b3pm4DdGgOGjGUa+J+6jGXX
+VutrC8ndGTViOQEpgEDyhR9m7tCKliW15gHqanQI3BRenkdFZgtRmQvQcsZCLeAcx1I2OsZYSD8W
+7Ei7RrRdkim3Gkc7bkZjM5ittW1KN3S61NMWmiznWENJPY1O0CtGsXhMr+iEV/SWTDHeZObO0EbD
+STyePYxWEC9Y6GSBszTAQhaFOYPAKj0C5DEpZhZG7Q1uqogXxLesROsoZNxfX7bMs1QQd7nBMQmU
+r4HkALpIkkeJyYEmRRgXq8Il1pWv+d2b+2A6Bo7oRlho4HJDTKXwAZXKx9jNHHJQiXkvbGyhx8OW
+hZipOQO3SLEAkeesAt2pqY5BUsGsmegIGc2yCYBbWl0/tvV4n2RFp0zkU0oUYbGgqHPU0N+b1qfQ
+IkZdd8xcnlahSXM4dzkU3j4NSrquIk/sSN/nV2M3NgvcnVEZEBldaEkEaPIZSkbCyLseBwJU1+Y5
+ZrI+MVrHy3R3KYs4Y+wgMTXF0J9lRE4PcqC1Pme6Xwfw475tReIk2BtwRJRZgQoCt3y8bIhnpAgh
+YiyJBQUpMZo+Jub2ep/WnpUqU/o8dfA4xbe0ZNxVroYmLrr+zH87OiJio1OKnAST4XnYHjMr6f3e
+SFXYBq4daZ7DDDdAl5ZrK+aWvep7vXMus3lOpkiq+dR+nvpMkxgOZOrXoZYnGkOOWcV7A5PEVZxQ
+T0XMWGquL1GaYsMBJTPHShg2glKVN3XQ7gDVdbxKh6jN7SDKocrLjJ0JNVJMQ9EpN0FMmTGW1KUV
++5Weqrof6804cO3jaLrSKXhVrLReDntRBO4f/wZRc4IVuAOqpRnRMpGdHlg0VVUHIQZYA/mUDOYn
+30zLNTELuu4qny3QPFOeTcdBgZgEVT367cdyrawxq0JapgqVkq48P93LvI//GFw/xJllmjzzhJQO
+10i5M7o+WQCb01x6mggBQpFR48zV3PkJy0RP4yBVjej1+8ZIBxX7pfeiuUVzM1qau6rcorrR8moh
+8k3+dxyOJnOFpyCPRkNhHo7SmsmgRn9SuQaWhjDO8FYhDY37ywo9RQFUnQJ9SKyUoY82j6+tSJsg
+MHw0bNzGf/ZGv/WdGgfC0zVz++y5brj3cpniqUCnOhctNWEiBvI57vh1ovmkRAaR1EHSqSJI+UfZ
+jJGnSoxU1pymXInUI61yczdc2lg4R/01i9f5dPabT9cPnLTVMhLoDGkoyXM/doQGx1Qdz/zOll0c
+6CpI3bFz8p7k0RbNYv3HZe5PQYIihuCMHkYS1ECn9Ji+iWkE0mSAhNFHdId/L1HOuo3hW9b6zZTQ
+IkVnCGOc1wb7MSXUDoYcY0TJ1JUiddLR6gYlI8zz12bLB38Bjk69lMKOsCw7rboBGGaCrUItCvu6
+Qjgx4uI7AogTdWHk6JGLDlydZhsvGYqveSfyTThQ9vkys6fOAupopVtIvoWOhtiM2cY0o6YCdWyN
+hVd6bhLFw9R4s0tOVCwM+THpwXrpLBGAh1jY0O6QIXaa3IcDu22tXtv9G6xYxuT12PSU852aCnt+
+GjbSIMhuzD9iId0dMIAm7dIe2BnPR3PbQKtSSKwNzsdJmJ3ypEubVHmEcUcWOOYo9cTbYdev31tW
+rb05JcUOHJmGHQKnSE+2wSrPGLJiUpGmhXQVt1Z8y9H3WiVezz5eFuE5W8TWJfnVsMRO+rE1JGFA
+UG8NiPmiq3YkLJiNZkLiGEMX7/KqJPsCs/Z7Xob5V5yByxdc4QzGII2DSNF1wjL8fC+Yx1GLtQ8k
+327vaYYq0FH8yKxYoI/Zi/LJMDTeKs6C4okF3lAuMH+aFyDDwvHVaWRsMXO+LZVpY45xcoy52piR
+r1BGYKrUgDPaje/FFdYco+jB03r+bwAOCGO3AEoG7Mx7/3UQVIXXoggY9KKyNTzhrrVG/4summgh
+d525OzxPYptHFygAgOHI7I4V7LZ+mkg2BA7pKu7oVlxt9KwNFxB03tT7OxkLeEYonH5eq+FIeUIC
+SgMnxIyilnHjtN6orTISanZhVuQW88R0H1Hto9u7/brAtPPebeo3mvPJY8zAjeWkq5HcBk5Qlonq
+uSg3SAy7TSYS6kRyXGUmrRW8GY03LDKuLjvTLGK9UsdyH7ZVdHRS0cE5lnWZBVkQiiZwLM9r9rww
+hxXxmnadBe3SmOGcWg9JTX59EJzNkYqBJ23gNFIGq5rGlmP0Vbag1hnwvTIkp8awhWwOhc90/YCK
+1voR94PQd9ygFN2eYAPWtashj8odHUJJHkVeu2/M5iai2KLHlA/ny6ez+DMp0oEVJc+k53Su793U
+vVY7KSx4IVk9w5pAP8/AEQicxRHzVLnBQRFXQ4PJkf1gJVeNHtNoW9NEGFsc1a9w/kfkQPzLBjID
+nFfWMLqctrRAG8XIsTwzV7h+MLDASXoSuhgA500w2mKsOr1UUS96adeW33Ybrykwbb9M/MRkMM+H
+7WMvAov2wNpZSC7bWjDNTZnNi9rbktIdbBNLrwtUZojOTHTRiYE0CgqkmAXPqDRxgMMrmaHbXjB4
+rT3QOLsLi16uNLPXVtWAaJ2kebqmxugtwPmJ+4G0heEzduEMjFPYDOpkmBE3ChNq6yTz9Y8Gz9vi
+c1DXhsYU9luqemEadY4e/AIxH7kcVtVnPuiPLDZcLTfsIWKtirvRcvCRD7HNm7F0LuvuDCn07iVa
++Fhugh/OWMtxmquMsE5ju6g6Vm6Rjk6PuAxIK8oFBc4ygkmB2ILAiB3/BD43aGajYWQWet904Koi
+2ZXvpvlGc8fENjThPdQtZvxu14R2mPT0uqO8W1DiiV9O5DEaQVKHzR1Y6rGLGJqUyIF9w4aRWhtt
+rA3FzBKNaaJR5AcZub8s2VOvoMiwIFYYD/LF17O/BxCXe33khi5gzYgjto3itF0VgV8vCPWUqyMq
+xswrIkmlVkTUtTHRF7ZnmZkd99i6031537aUL+DMOXLozk6L2ThEAf6OhchT9E4Dy/QcgBhJw3XO
+yiHwbZ/HNG6UlbLBSFdDHQds/XZpUpwCxAoslifRwDom7KPViP19Q7OplZlf/QhjzKx64zoQlIRP
+OkFoQEcHEyB4/DGROBti37QIswew81WSLHUwxcgXOnCnhoHDD8REBw6VDHLxmQxDfKSA14UydAwD
+Ux9uBdlKw/ra7q0CA5WpR4SRKBpT89ZUldHOzy0tdHJmIDPDcdd1QKoleziFDxOQiBIXxzMxcTWn
+6wdGjla9O9DCCh2tHTLl+wThrdPDbe9iWH+ZoZMQN200IaeiKF5wUGge4spsOmEbBJFT4JjYtzFq
+kifOvWJdhLx3KivT9h6aqAv2fo4/bEJQzG+xFoBjr8f8lSME7BWQYhj4BUbGWGOvjFSoXtO7BU8+
+RwoehfiCegV9kZlZ8NhvAxz7wgRnpPVd7meJnbWW/pVhwfDNzjSd3MMOEjrqU1tvZudkLIIhb6zI
+ybsx28gq/llSc2n14FRfsAeMI7DzP4XNOd5WVMenBuFUKwxQDJ+abBydUWP+Nc68VjfEz+ObdNTK
+pdnYqXMdU53hhGsOGY5ruYFD9XbctnlQb7KqNbaXbfE0F8FQEx00hE0cP8d889gseD8EUaGhKNGs
+JviYRM2oBtGndsJy40r3QzdRQefSLfNr9+Uy6XMMIoihsjWQA2HJ+ph0P1a5pvU96iHT7B2zMaLr
+qCZLnaSzVNDUxnQf3V4cITumwsMGG08uDxxhtO2a5lmEHTJ9qa97avKoaQCEdPrULMziZkVVJkiS
+6rUfOqQZ3WaTdXllrMewjJJtkRh1vQCJk1kfdHPBBsjhMAo+PAtVFKrJY6ZaL2VFMbLQcceCbbyo
+GO9THsROWE69Ktm0csFMzrgAun5YwZn65kiPZ7rya8a0VnShYwlkG3WtY2YltMzaolCp1y12yq9b
+UVXJ6rKJnBEr8BhLN6BqImbOlFdrU/JVtKHjIfiseRqOOzdo0NLNUMwvHZg/I1Qk/yZGcnA8ctIq
+kykZhPSK0Knq2stw9Aypn43tA8u0A1NW/jZiWZC8GZbRaMRndk0BDh8RZs1yOSa6rqqaJnFSDENt
+9JbcJ7Or6XakWfvtsjDPeAIGV3BzNIoxzp1vUNWNwBTAbxMHO/TCbvWW2/Eov/87RNCJRp8Dx8Dm
+5TDRcw/7fHXiYAG6W/kpIU7ayXEhgp7YBdonCGOY+6FnMy26Htt/j+INw8Uwc3CuvLiP0XZ3SFV2
+G3/QzT8uM3QCkLB3Pg3EkCXiKM98uy0t09JL46RwwozTJxebWe4uGAcccHUytyTSQeTuLN9mXV5E
+z2HXSLpgIhihnqgO9RNWJZEgT5sgOEh/zC/KuQgHPqNiNXAS4Qy4NtLYiD+28Vh5kW0mrEpGZQbJ
+GEuFs5NVGCtiJcSMbB2jO7dYyYDoif44JnTwX4IIuxhs18VWrn32RYoOxR/uEIVpuBVaW2nf0yTU
+XMvWAuJqoQqiNo3CFek84lLbH9K2IE7dYtwbbmoZlvSp7XOpZbbp+930en8s6NdC+En9U69J3v0x
+GqNJb8tElMn3ImJ1YxvNEOirUMuCIlShXofJvsnDYE9EaIYYjoXt8KX30xoD8rTxylCsDRakjT3o
+UdtJhQmbVd6QePqkhJD6sfUZ7R2DXZleW5HvssK5p08RCkIaqgxHovTUhmQS4bSxFjYpHj7r3X1e
+hkltY3Kbdo/6oJk4KpnVoes6CYbkkR0OtSw/9YyW4V2ZcY1uYyldNAjBS8a/FvHQ0NGhRdcLvi2L
+0Rvpqm5D9GLsmMSSiW3pV1q3qROsWikztlpDODiZEgTCTmQhEzUMuUuc7P9wdCXbcepa9Iu0Fo3o
+pkBVuY2bOI6diZad6yCQEAIkIenr3/ab3cF1qgrEaXYHZ3l4XmxM1X9SqzIbLwYpgb/XHeus6+W2
+aPIDetmF/TBjEyF2tuk+YlFxO75qCWXJW2qHBIbWPCoVf+pSQ9PaDIiNOPk9WU1nq0JOT/t3Bs3c
+k5zY5nfBQrX/0XaT3HYAmZT9uS8TQNfWqUluHKssa9IrnmfGP5ejNwJbxBDtCr5ySgidWpltNv4u
+fSWHX2NRu5WckR5wOHktrbP8qeJWO9fCMlPTp+OoFnm0Rg5HmLpvVhYz9hhKv/zeKrj1sXcp3ZjX
+GPKD+XZ0RSRP9Z4P8i9Fx86GbiakHvY+HtuU1WD8k8L+XEqeFF9ZjHQQAKX3lScdH1w18W6s3Zbu
+XbArMi/7oVmOAR+PB7l5mViYoVm3uqzjJQyFUu91IZJJtNBL8IDeIm11/EGtdFnSGktFfFxtDRnk
+hexN2PM2m9RWDJ0YTG63dqxjxr72TWUFjjIrd9gWSAhp8lbTEHf41amPm+uGiazhXfMmpjdHpmn8
+RdVmh595w4x6gbPVy75oGDk62CJi1daJYap3yxiS+xlxTjD7A4yPr5JAPWL6xZb48O1Yq7sQppK+
+mqm28VyzBRWog+xu50m/syUdyNUaJJjXVq00hHdFZzyo5zkJiGhoK5FESETURNSW3OZbNuumiwx5
+nMdFcVJUskt4DRiwjZkAF3BrCVycTZe62cb/Ck7AYvWM71ABtekSkoWeIRFSNdxyKYkhbackquMd
+CksyDS0c5UzdZdlAoFJFxg9kyW1Y6kF8FOvm9dhVQxKT55JrBCfAtRNYM7XRQCJjWxTYwv6dpzBx
+3pJsaDbbfesh9v2mSuVKzQ+xJIXcrjcjubaXzcMWvHcOS0FV9jovWXGn8qmcLXKLRq74tUG1nqCR
+Thuj2xz5NUWXUUK06EZ71Dq7jvmM8vWLySJY+6xEvormtKumOtJfG1uw+2C6q4t8+uYkSXXvTfT+
+toZoaM9Oeoj0aI8m2PS07wGRQH1Djml7nKc1rFcrsjzGCYpCs4ipRSry0fxXzxk4j7OZQvnP6PGo
+btNE7Mmfasz25WWu4MaH6g9iJQgPYSJd/sty1OQ2c5gWusOPzt0mJVILXwIWZPuamGWTFymHMrvd
+a2RRdShfyWdlZoQbjTbo641FeTkKliIg4liHtC2HY7gvWcYfGjgPzplsxAN4NQ2+Z66avXipx2IW
+J8BNm89akN4Lfyi1O2Dc1flKyVuWA/v+i9805m+mnHbAAjAjNRd8LVAOKRc2dNAhyPwCuXUib/eg
+WNGXB8b0TkxNtr7lNqtJ0pJ5XvUdKUQjnzMxyvUuRQdmjysdfbhDvdNvkaaBvw6qWdnfKo71/DQJ
+UldPZk1i8wYt0Lqc94WMVc9T7cIFs2owrfMKotHTSmb2tTR7uj1CtjrOZz+MvvnEkV1w5lgKucvT
+VmZK/dcwOpUwFW64Dqclui3/GqkDOt2SZctwqnFGEv9U5DPoKaKCKX+qENd4w8lEYeunnknxyoba
+JOqKHnu5V+ek2AafXnksCsx38ain7Z+rw5F8OUFXdbTcpNSSbjeEZp/Z5r3N4Z5Xvow9HBpulx1S
+kIbBt03DxwJejYV/q1I3nq9+78qgVvVV2TlJZLvU6w6nLB8y03ysdEr0azXSeURTWnDQeQtlWCyz
+TiwhL6BMSe1sFApp7bdLXTsJ/zl4j/V+JMWRtxDKIC6oXjzqOaQHu32foQvdWnioRovSmIq0E9CB
+QGOZLgREkl9GyIoSMdL61Q8gTl/ZQeb/BqWnGmildAJosE5fUwLErMtxFvOuWodt/rvbWD9D4IWO
+3cwJ90+lOvzVgOeL3Qmec9Wh+qxvdQrit91zJ953iHqeZVim/8qxMPOVXnz+pI+jfILpdDD/bwvv
+Q51uHj7HvbxRx8rtT0wKNSBpXjTzZY0ItrggzISZU1Ix6rt8abbiKu4JZC2Q+86vS1rhZoVIrrct
+JGkPbJQnLddIO+ggxEMUQbFKOZ2nsmB32G7C3OpZxo+RoH9fa5Ot9KT5fkCCbcx82tZUnMs6pPRM
+EzVcsHwgMUQHoROI2tjKez2rJekcROP9BvbCXg60t/ccWkzZrQw9piuEw00Zg0QqkIOq1XRhO6y4
+3kdXhZa6GtoxJMU1A9KD/OH6MZDd3wyIvAjtNKnqSsyb8YirOeq0TwjaUJt+f1Rnl0xA85FaRrst
+XUrS5z7zKUR2A39Guct+7/miXJuFZv9Fp2r4VQye/eNgdp7SDdEnuCKEJGc+LuCRkmpL8DwsU3O0
+Tb1jWEVojC7vNJu9eFqWqPZLRvdJX/sFHp2zzU3mfwm4zNeerhUZ26nYD9BAC45muTczPbFQJ0s3
+4W8evu8DkPAgFtcZxrKsw4yyVD2NmEWgSwwzmshUza4tlc0+mqOYb4d8ib6HsnnEb0i8yS8jiSsc
+5XGc/iy4NWM3HpKcc7i+C3xbBUlRUWgF2d8ssg7LznyeqMR/AobFDD6IWvE2n9LhdRPTxK7owI6s
+rTCpQIIx1c3SNanUD0KWNT9X2YQ8m2a3pTnny56A0m+iaNol7kvouIOytyVFyike/TkpTtHO+vmo
+9rn4OYthSrujJJNpZ1/pvRV89f6+qAYNm/WQN0OnhqNK+wX3U/9YY5JdLcM0F9dLLj3DHxGK6bKy
+aWxzOINcayqDYrbHkcqzmh15yCCtWj7TRYSW1KiZ7Vp6O/R8WPHP5qJqxMk1DhNfWY3FAKW4qm4b
+OVX0UkvUcNvKRokvEXN/fJUIXXmbpUY/mfg45r3am2Y7mzgk+C3prjpMSxRp3AfkHjfMb8VrVoS9
+vlEMPoCO5254jtWgklZDeX/rHcNw6Y4DQ56Lusn6cqGD7xA61SBykfvxMaxZ9menDb8b5TLT1iT5
+YFAMm2nsFHMojEdM6a8tS8IfsgjWtMTRMX3OrEFcQQGJw/wmttUBGxO7seoHHssQEbTo0flKNibk
+kWOufYmWINYlWbLxdkkL23QLUr9ju4tFDP0w8Dq/wq0q3Dlafuw4qqp5drCbTCfmR8PaARw1vxoP
+spZnAamOaB1sTNWZGQY4OBI285YvPn2jB/kWRMHNOZ0BQu6nJndQgzLP2SVmLkEGUTEM84Vgnta/
++ZQfra4rMXb7YFG7wGxUYm4PWCTnqw1+10dgb5nswR+59HqtTAqHGMHOguerHIm7INzcT1eK1pu+
+xayCrU3gtkxXABnw7ySTLfZ+9xRWeBhY+G/Q+vNXlsbhP66X4z9Ev/CPYxDyThXQ5p1zbOmPcbLi
+RTEifZ/gQL3ZXCX7JRG5etkESVAz5zTm58qXEkNBwhrSFxgo8kuZ+lRc53LeX8CzF0PssO9je4tG
+5c8bPHbhBAeS7jmbSvQCgq7VQcaLbCwmaT1iGFRYUJ3My0ew8gimiDAzNWdo9JPtTKqt8r8m1dTi
+2lCBcdi4pDpF6dCH2n1UuTlpZNWNbUkIf58GOOdbiNaS+WWy4dh7N68sv6AUL/cQUTBYfPNYwnZj
+m7KlcUJOAIQUzb9ky/y/xJDm304LbLZuYmvobGILkJb1jn4GgZ0csYfM2YkVWM+he/kOi/TpvH4c
+xwGny8DzWbR7E/O/IEuwA5kmFRiRyfarZtXyOatA8psc7vRLmpT12AHO3lbkcAAFPsO5InQ3FQza
+E87X9NUtzOFxWeLwp1T6+FFGyj4aE8iTzTP71JDmEBeNiQfySVPAVVzNIJ1O4zSt54PO+3hqUl+z
+ltsx3B+r9MlZ0sN/VogjFW1Bgvk75chIQMqLysue+ay6yGRzCYCbIX7sCXWwyuta+Ssn9vzzOKit
+4OkJy4dG8YinytbTfTZlyb/MzscPR4CDn/N1Lz/cIKcXXiAhA5ZGud/YcsCIVIBMcW2AxsddSYhw
+Q78e4/zPrwn5VLufMtS3EH6Oi0Eky75EyR+mcaWgTWenvlK5b6E7QiPEKRAqJZSb0t6S2esNC0JY
+/w0lZX9Crocnixb+WEpu3rkp6rl1uGp/q9Vst35eU8z6Cve8Rf6KTzspCOZAKfm3bZfukC0kNEi8
+h4Bz+6PZsIa3kxcGW1Xg32tCXYyPaTZ7ddbJWACRT5FmdHZ7cLad1rGoLmAu0/fSiKJENslOHuhW
+4HHPYLusAFRhh+89bO1bSytfYSuFkqAG20RCczpyDwuH8H65ieB86fnIsNifstWA9jTUmEs14Vq3
+jZlN2S02s0Nr9wqHjDlKH9ha81coL+TLkVngQFj87N7mulmTliGBoWznsvbPQg7Fl1saeX/s4z7c
+eE5yempqDDHnzc+16YT9ZlQSlg7X6VpJc/a+aV7Q05exd8Wobic4vM31tsjyz+Jycu8nEotzWnP+
+e8DAam+qYWueecOCh/dRwGOw575gXeDreqpTX4mrNaVq6gaq6X/1mnuIgBSTtzRu8ZUeVptuK/ZS
+Ie4okKMNuDOXGVTkcXaOxzc2+ODvUC2K+dxkIjvNtDZHt0IygXFWD1juGH48rk5owhuW7vylEPnw
+U2ww+rajWYusHQhmgD4TIfknx2m+hd3vu4QDvSrPmxt11cFFYx4rExyCe5HtgAsQj7KLsGU9INMt
+9x3XsVStq0m5ngaM7UVHJE2uC3fgZzYwQSAHcj6qqsXzTP+C4WO/Ek333xRy+j+gCcLtIO3kO8Nl
+87s+3PIfkED5uFk9f05FzK8X/MytA0uO9deDJUJaBjT/0MEdDbvO1S5rfK4NOFGEmePEktxlbUrZ
+iiuLmgEcJCv2Z4lwDyz7GVQRqJ7V+uiwpR4tQnyn9FYHUvxxYS/uq3LaPuQo6O+8AoXW7lSaT7Ej
+dar1Evhnt89LOaPsTTJrN7vXH2CYMSRb3gx3sVj91gZcxHu8yCMZYa3y9k7bAUNKktq0D6ySC2xd
+KynbgL3jnUCa9V6PJcX3zjQsIRBuLBeqJyba4DaPFQi2Uiz/cVzWC5vJcc/q75eClKBiTbvyrBq6
+nS+1PWFqCqqje5zeINNnj5ktD9fO2I9iNw/fU9tK3XKlSuQRtk6X1dINOQz7N/UWto/MBfpSxoai
+dpOonhZl6t/FkKfhuhGDeNFmWv4aSKzvER+xhPNYjo1vF6RgvCUeQGqboQPD/D+u6bN0Ci2AccRm
+osSW1ZNXSfXb5hqrHFTE9JU7h9ZxLAGun3ITXt6YZMpv5Y4lGbNvvtg+Vyl5G+sFsXTYGRgW0poi
+yGnH1HI3R7zMpdVUrq7FI15+EnLI4cTXA8FHEzbiTg5CPKgc+wRwIHDKF7my6W6LCEq4MNKk1/Uu
+qq9hpuoG+nVMMdJhxEhN7V+ALFdrDxkyOzpfk5r3daEhoJcAxBCVCd/8/Qiy6e8hTVOejVmyc1E6
+TPTKTHHssm3b35P1aB5LiPugtVeIJGlFMcuta5D9eAsqcylaEG/jz2EWRnfaqEwikNVh9qoRGpW3
+Jh/mn7Yh1dHNh85jZ2jq72g9hAat0IzPNVJ4q3bWZqzOeW3TM+6xjpjcYHWes528Q1wEuztM79ne
+F7LY7yTccceVAEv0UpFj4zdIjURz5BireYtaRK4annh3SQZdVf1W1HCpFwOKDAVYdsNSGR92I9fm
+FD0Xt0GFrcACVoS8bUjYH8ajRFdT1QAaU9pNXY0ViKJThPLwrWA6fqyNT9Ye91DcWW+ytG+OHYdb
+Cjb/NkToz2aWdOhKTCh/QTKE+6k6DO+xM6sfxgciHxNEMZjhudEAgXu/5AZv5WF23N7TPMwYO0ZL
+7Q/KsqHsa1Wv4VNEkuytEgZPAakN7kKCUR2b4Z6L/PItAIDFedyav2Uxbuq0bns83g9m0581iMOr
+4BKOByc6+7bMR/N3tovk5zpV6hXB6fS3Xci0dUdO5vdkRNdtE2zcvyKZGoQulc1yTrcSp7Qp7SFP
+ZLdNffKW6fFqA9a9t5miabwbZIOZJWIt/lnSHfBi6jMkA+QAsGU/alH7FlGliz/V9bQIwBz5/FN4
+BCcgOj0q0vqN+3dDJ4yhWZWq6jRLfJl+cSs+2tdrtfdJDP4ew/OKXTbIsHYzEL3xBHf+PANT0+sH
+Ca6sh78yfkMKIVnXp3oidX3KaihOuuNYw9HFsVBApiprko4EHxc0Fb3pbgGn/S8LVYLYX9yHMbsq
+mkP/WZlFyimr7Jp3wJix1oQqt0B6SLnom51mRCKiM8+BDiFYDyjxpvncqRiLRzsd4s4l5FC9NwdW
+oSFCttdxvyFEnm9GH+csw4wBBcwAGfCs502AoPHqedpsluB/d8uPNJ8wt4UpJvM5AvWlXanG8mmW
+UA20PlgNxE3M1Q9E0uVVa3Rp/4Mh3tsWYEii+xK3WffzRjgAK90Mjy4gGKcFUCKSi4Nq9+gLj3TO
+rpibesPRyei9ZGx/BqkyY7cPi0q/y7f8GD21KNPIb8Ofj5imW8JS95JF2jzo2Rt/gVx/etzVkGZ9
+gYyIJ9MgvBF53gaJ76o8MtBVKbeYBJI9S8nZNoCMXmc+DdB4TINLu2VRY7wXVGBVK9AG57Y2tvAn
+HQmCO4mMh7wdtzq92rQ2rtXg/184TpWBskbWHFgFXQYU4xEP1AitzNB6yL2wiJbFcLFDXscewcQa
+VCabzNDWCB1nXWmZ/6BKmuTCsaVeA1PNH5bqKP/xvKEWdWswodtxgKq2kDImZxEHEfuNZe7lKMhM
+2jQdw45sDCorkDBjNXd61hB8B2Rj+RqiizwegHmhhxU/DuSnFR142mPFtH/U9yCJtl8MErkEhD+g
+EGTZHhGoX2pABIzHGkkX2A79aDqiN8mUyk/CxwhQkjbihYGh16e5Ik3oCPaDx8ZPmJzgLtp4myR7
+BM4cpLhmeQZfr/GgZdoCyQyqrzC5bp0FxzfjTsYFC4CnxdYVk6Y/my3FXp3CdPkMyicFhLGmFoOQ
+taI1ogYnFSqjH+2IkbdHHre4ngXHjOEG4tbeHdx9ZiwkEvPeoe8mMcv0OjOMvGyR5k/Q/sa5LQxr
+gLAmattOM9i++7gUAMD4UJhf/ycZ2sY1+iuzm38giplXwpZVnpptnb6KXKCdaufj5xHI9pAHxb/W
+BREeWA5y9qCDKlGC2JK9OkmR1+uAPl1V2ZL9ZRYlDz8VZwy8aLS99Wr7UykCYD5Gh8QtW3MJSzKi
+XJDXNhUn9Dn6AAZtf8aqGnWXD0V4g0ia/FFgJtDIGu73VtqUTPdIKwWfNJjV/dSh5gF6/4jXHuis
+2r62BJktmNbLL4IQx6TDMlr/yLJjAtK7+f0X8TMma25sci+n70rjOWdPCu3TdIdJ3S3IEbhvIWSu
+SMvGPS3vfRFpCWpmlk8+DZh38ZHqIfOkRKyhQ7+rK4diteF9gs9rrab1dmdV5kEwza7oh0oCpkSE
+dp1d2ZUiKqtAwkrRm1SFf7hC38UKo6boNODU1/TgAEsF8vGOtqCAPQZEkxRXaIIpcO2ZgQjP4rw8
+ie+kgXOjsnCHspcrrB8Y79uyJss/RmZKO+X5ilXY5cvz5Jv96MCXj/u5oQqhL5kf06cNI0jSlVD5
+PO4Y/zeUg5qDfIJ9xMIZ75MNQ/bgkf7OZu1agVoHe5Ibq3BN4Qj8qotpou2cWjp3OCThzdmJvAzp
+tI2ggje8dFMwoLUOL5ITrfVOP5aIJv27ofM8AGlOH5HXu2SPK7TwDJDdLPDqjW+G2E8q3X4zIH/J
+ZcqDfZyTdJ9vWWlibFc8XuUZZkTwfxP5Djz+zho+zfuOWT6vx2aEmmcnYweJLf9UAtgsTJQbFlqy
+CQGaSAv+mMENa0+bcdtpYDsofg8pH65vyDBUbDIpn0QqxIpLPWBWWKAG/UwEiOmT2lGKuzB5nNh6
+Sap/Jk/CMw3W7be6LtFyAjw3aVe5wn8AB69ot0OEfCkRe8uvRwp5/HebQx6m1kuO8W8ZgNshhiZj
+HWDd+DZ5l74HIeu0dZkgtzC9L19ldQB4RsgzwlYnUMC/raxc1cpkBodfDNV6Pe8E//K8uRUjLa1k
+0a2iLv6B9yjAdkBF8E0Wz/BcKbpjzUJofPIX2AlgcYWi5joB+jC7C9uc/JKErtmJ4H2FY3eMYPmB
+IzOQ8RUH/tsjS255FkcePj2UXO/4QXhDC5YNqU4V3CFlR1e3m8uB7PQbAD7J0S44Qj8xLSnZDzkj
+SbfUkeSXkJr8PSnU+AqVKv9jgc2+I8oz5Rfw1PPrOo3F1xYX7lsMPQkwf3Bzn3pZ6b1v6vXYToVr
+0r8QjuvYZmxCCADeREHFdSLk8Vvh1V3FTcYV23oDNQgOMoyd//A8+hXo4QqeeHQyYMSD8mY9lYJw
+fdq3kd7uSJsA3eQV/WL5DCQgXWrW8+0oj3M1RqgJR1skBBvDQvbhfiimGb8ZzADpPM5rOC/W5rKb
+ce9uVLok4JJhyPwS+jBPWkUMtYTtrOgC4Or8VKjCT51OZJ7cRiY31iKYqHgnmQcjpIY6M+cJC+xz
+JUiqu6YgJFyPG89eIIdFMkCScswG1YIMl8WkQGeG7zmgHRjTD1LlWqK4H+on2UCPoUvjbR9tTHX1
+lOylG84HMfOfSmM66kYFsLqVZCjQzzKpX8zqi//guQA+o4RdqnYz8OPQN4okw/Q+DyGLd2KjI2lz
+wYA2uaGoHqDV1aKv0Ydjz029oiiRwsJe55AOcR7w8hZ5YXKtptsM5QPIM19NesJ7KseXSQwBcE9x
+kPG0QJdEAedlgJW1KWOXBQv1cCqieIWvq5zbGXkWA/58i32psmhatEhwHBad5mtHgC7twfikN+Ux
+M4EMy6a8KUVNPAD9w//kuJSvOkaYjP3UjEtHBGpf53jGETesllWfAQkNjzv/zueQR5m+koTb3/B7
+4PFTlkGAEmbt957TeqfdQDSkGJTV2fU+4fn7gE4ABZJWCkRXlqPYCoxZeDhVtuk2HQExINwE4kjk
+Ju5YYsdyNXgv0JzmF2mQ+4ZuULET9VgiWorE1LNyhkx3RThY2dY+8WM7OCQTdVIBUL2qQ1l86WLl
+vxVKCsdFqOz1kmIk6mtooOhzFNLeBZos4x2ms/Lu0EmlLoVTbuyKYoaoBpMD0Jo0denWzy4jAGDi
+gMPDi2J5d8Hih6z5ODzNWLp+e+wEsPiQBQEHsdbsl6gHHeCmjBVkQGgd0wlU73arNcaU8wxMXXRS
+h83CPptvP1J7LH+JJMV467OyuIL72v4tnSxOScbt+gPQPTgvA1NkQFFay3+Nm8f/ArjVLwn09ZXq
+EtIJppHo0+ViwPRmVozm/eg0fTCQe0AhBg4WOUoueFAOjoouZIggR+jmsX1U04IiaDnQcnQSU23d
+JMYdt+KocPRNrRVtFd/pawPp0QeXqX9N1qq27Zwp/6EQEJ32E3fkCfNEhEJlxZev6vkXpXZ7FX5J
+mha1Op3ggYLuBMoxumFoCYMeEXlUqojdLe6mHREAA6gB6fGAuXS11W1qPf0oUkN/5UllnyjBgtru
+tdv/ZsmgMI9gCdI9A615PeMHYqRjNr8dMZKWnRzdvkCzgsxqhH3mCKZ1GiILPPqzvqAX8s+KHoVB
+tHSIOXKe1rHsKZQwY89wAdMOstwKzyrDOejGLB8hW0ZmGPhzDcFW+12TYVrBDabthldK3akacCcY
+OaFfETAl/xPebQtU+FE+KInJ8xTcoEFrgd6d+2Zy1J/9BFp79eW8dqESFL+MwSV6igwNBtx47f9o
+kYgPLATwcY8ziS9ZGhK4Vsh6vNAhTM9ZcClAo/QAC4f2segOeg0w07I2y4MzbP0x0yz/tSls+k+A
+nXLarVBe/Qlw1r0PS5h/7qXAiA0F+ARN2MjyV16EBQ78MOY/CGhufrWoYf3gbvlWIGIHEe2BGDdz
+sYkSpHW2Qb8gwU6gk0AmvpQlRC0TR8xle6zKfDkYLv6UWEEHzBs5ns8cQwKmCXBczWkpj9F06x6H
+X6lJISbSYHS+36jBQVcUy4HrPM6Inm6tzdInnx/+acaLyTSgSzp9QFGHJSQY95+Hsnhu+f59ived
+jstV1EK9LSCEcaAb6ceOABhIWnAHvGkBOgGKiqXg99xoVXUbzTb04QN/dF45tRyv9uAAx2VCgryi
+M4NwaB+8eRp2BonF9C20byk9eIAezZI37ObyIS8AdePKT+RBb2Z4hJ0G4bksVfQ6Sw0w4O1booQH
+rigQECkWW/cVQLVXgIr6PRmOrDhViQQu67Yx/QHNpCo7+EoAXGFfK8FKT2kVOtRZiDcweqmnYPF6
+mJ6sOW44N6CSezwCcHkMUOy9EZ5r3+c8JFcHAf2OGj74j1oX7KXAFIPrVBL7meYRLD8SPEe8YiYt
+AhZ1cvDXlI0Fu0Ek6/GgViTGnPEooLBBmodeuRR4DzIYWLcOmNzzDXjTrEu0irBsd4SitrSVGYzo
+jaRrbEkZ2AP8Fu7ZZbX5dNTQ7SpFZsitkqDiMbktDLQkLT6A4x0of9U2XC05HPbAYsflkhwrlD2e
+En2Ln7pD2lBlnHcBlquvEecHn4D89vOezOU/TbksT2Rz6uO7PGBLA+eBHG9MEtcV8zNiDcGXvq/1
+kcLvwPNBoUORGvAMMIofcoO5APKYkv2IlcTb/CKAOGgReFxc37Bl+B9nZ5YbOZKt6a0k8p11OQ+N
+W/VA0gcpNIekkOKFUCiUnOeZu+m19Mb6o7K6W045nK1CXVwgERlpbkazY8fO+YeClEgNzycto4Jd
+eODUKWCA/tiWwhhfxVbO5ZmWaS+zfSrlPNboOaF5I+YJbyg9vhObIXrt88n4GYAHB5AZKOKPeip5
+FGkJqjvqEIC28WURjqHfih5pud4pP9iF0QVQ/NfBq5PSUbKCbM8Iyc+NyZRRhMwScR/JBXimYaLJ
+ScCOymATmaTsdifwErUj2nWAjaxePgOUE5gblO7wZdIzQXnJAMMRrRSu4SjrxH1QlxwJCv/WTS0X
+yk1BBTpzvV7pn0uZW5PNp/a/5AyrITuKI/1bV4P9sjMrDx/7kXYZNaleu4SD3bPDAVcGmxZgX4U2
+VKHymjdiuhh6JYnnfLgKrEY8CPexNfgA2WYAYq7hNrTryi4k4HrZcwWJ9KlX6vwqE8NB2UdJIW4z
+YWjUHcG1jB2jyZtABTVBSRArIOoJSXceZ/Q/pbmTCKbOtA0Ypd1+sLSUfkMa6jURSKbYi0kKRAd0
+8mlvd0rMeeIjeBU4pkbTaXx05mXch7iZ1Qrl8UtIZVQPsiHWDXxlKvC5lCWoVnBvBM2mK4xE2eIS
+REk7apXqKY/k/q3PuINQ5KLj7EbNWH43LElILgD6ht8iokXqGP38qqLHzI8ALhP6tkHu9YQOqfAN
+1iJtbGPqoxc1UPs3enyMWsV1bLnUrRLzulJTCsK4G068B9C/peuamVr1Ax5coX0LtDx8AHTQNCRc
+XdECmQkFMCMDVJbYqQoQWHufklp9AZ22vuwAmreOSblr2uOOWITBNb3WQb4HYTH9IvHqwMMPhurV
+j40fQwXZVEhwGWcCrfwXVL77p8FXhnZHT97MXYtXMRiLVkAdkvc1xW3fmIRnC0k0ZLtM3boK2tgK
+QIMFJsl1nn+vaeMDrBJD8ZcAPCJzpzDWvA3gEAtoFE/T1FVrMEJ0uucDoLYjYoVyZnalY3Kn6GTY
+BkgzOn3WfZOX5u3UKr1Is3JimjCUyx1I2/5y6uqJ8ttEZHBpjLR3PqDplv6QFJfUNM34MUQeQXHb
+PK9Q/QEFSJIZpyO14loj5FRSzKPfBBgiARlrmgZcihDEtBgEtg39W2Qc42IyvH1JbTlEpIgE18lF
+mZYhLbhM3yI7VqDNhJSauaVyH3M3KTKtORUYOZpx1cRzOas6maaVIvjfSR77bhOgoHqOmIxEhUXM
+BIHHcc327QcRVYUySkfPjkfCO31ECj5nqILzmAZwYoDtmiLpRYvlGP5whowmaqtdPLip0qm/gykj
+BgohTjS2oKTUaK0IDLDdEqzvqqRMHgAmKsWGV/3w2PlBGpwJJN70NsJCuTV8GYWtQSrYkY2eNRJd
+Q0m67EluXsqoM78jF2wBPsKpyNsk1gSlc1Lk5qoyQ/lnkMuG5kbRIJ5Nmp8X15WVV7f9mGki2A0T
+BHs+p/app8SVo4otqDAycgHmdabXP7Ig4Z0bIQtKkAfE6blUxtVbwgE9JDhmQHKVLBEEwG9Ce0OY
+mjpHiWIwjkWEolFfvt8DamN1di7mzSWhkT4xOCLvCSZGsh9RVh1cAA+0B4H5lM8j/LjaLQG8led4
+poh/+UNmKjtRoMbnUCaQuEpEHfdIgotgbqRe4fmJ+nnzO/Xluiehjv1HNHa72zGoOm6YQvdfymYc
+//INYHbbuLLiXxaXdLXROVh0IsrILJGgiQxwoSMpp8OOp9mtBgLnBhYDiR9P7/iVGn32khdG2NsS
+0vCPdHGp0fR1M17meW+9oP0CmoeOsVbSBZgiIMuKYP5OonT6FfK2YlZSAqatTY1OdaIw0pq5nad1
+jhgayc8QbVdMe6QJur1KpY6uZzhzOurOAiya5VMK+EQU+fg+bbvzuh/lxhYNudc4B6oQgDKK/Gpj
+Fhawa+4W7JRMX518h4ZseYXrmDi6hqiLF5qfYTYQSn2S78gf4x9lTlQmiQN61MoFoR/AY/oK3DS6
+gdfagDMM5VTYgAj3bhriU+CQ5ks808K8/S6DFX8o6N3cazp9BJXb8SLNE+UuShQ1uy2jvkVqxwq7
+cS+b3fC9DuoaGdSpUpABKpLG2425Et21hVJTeepHSCujOFFtJHdBNHWSzdjc8EoS9E2o5jwXh7rU
+K1duODUbvwkH4qPVV9lZpg5yCx23V02L2qpGfNCUhj8OoPO8FuFUCA5aazmKBpE0Rr/MHODEDomM
+zrvseOMA6MKl/m4AN/em8jTgU0uzmEvmU2v31AA42QgCBnhDIya/+mrw7j0y/d+IQs1l1nHoVQIB
+OeAGKo7yDB8EpEcKPei5DAcu8qqRrF2Z9DFdVhhC6X4A33nHW6XA1DiSa+DzGuSgXppKyakTmIh2
+LMtJAsKEIonredBkyCMN44baNNmmBivgW1QBv3ND7CVNmgct1xPgGuVRHsvw12CC7HWSxCDLhf1X
+lU4pmt5NFqngjMj8SXJpuwbxNldS/buQygB5WkRDbmpBaianNL22t6G/gWYqDDG/j41w/Gm2uvRd
+p6ElbiRvEgU3sCyaE/hC+aETVympaSIo2a1kNuYdzo35syjUGoClPPdlh3hI+RBnuOwCSpqQwWuu
+lBf05AF8AsdNzyqIV91GQve9cfg94r0H5/l8mvocjAgF1N91HPrPMtU0ELXlkIZ0YtlitqykwghS
+sJtxlwDcAAcAgf/hZWOguiCSJtrwhlnsQNjzNxWwdTn3Ht03kmMg+XaroJO28avGuGoiTRgI1Ymk
+UfuLoqeqiMN7y4utG9qGVFx6z5uEucA15LapC1BbhlAl3R+JbC8kDTw1ZFCWdpNDdrAhVnm/9IBS
+xba2ykh1R7AQFjivZjxXJz1F60Kcb5hILJNwo3YBZdkERIeykVLTuJ7fnRpBpZ3O6rz2K8drO2p7
+6DfJF3U3qQ9+TBSzEbgMcR/iWbI1q4J0BvHm6q8ewt9FWKaN7HaVSL88NGEVsNJsSEdrSj+xu2kU
+niAg8o2HEUl0M5yke2UwkGopwV3KlMZI0XDQyWWIN3Fm3TaxN2k2j/WApMGTJA6EKAsPfahMD17Y
+tRKA8LnOjBhc+6JGtVI6U08dxplwoPBmXcGRhhs1o5t0LHwB+CzPantUDOkSulh1ZVo+gGNDSsns
+fdVoMIqyin4g0tOel+uRVu80xL23BSiq+vtEqq1bIQtQ0bAsOvbflK6nm0E7vHY9wn4NxYK7/kyO
+VEuw6wYf5SarBN6iDW33DY/VLIKGGOX5rTxKwALAjNWQaDyRfhccuXZTDsFYuJU4SKpjTlCgnUFs
+25dO6YV+07eVFG2twIo5U4Glk2kBQJ2Az/l+5EqUBMPfg09hZtNOgtQ5aQ4BnsRsjIFcWKUcnqM/
+ZqWXfReaN1oYJ6WrdFMCTSsHY3cN5YemdgtPgcUolfS3FGdSvR2DyRvccaBktfUDEmNXYhUrdyKI
+k1tEdKlY2KQQJKpCsncXlga5RIn1hQDQsyMJGTmrb0k2YKYewvu4y5sRhZfZBuASQ4TmCcysShMy
+r/XLUqPv7CjTWAAtNosILUbVk0DeErlsgUbKleRJQF4GKqkg8Xpg2W4Cf+h37hXjQ55I0bUKKl2c
+AYPUjqnGGjxE8+Iv0+t4/FHXpVZI9ZCMK9Jo2DRGIv4k4+sbhydKRgraVea1VCiltPNUc/rpC714
+CcW0E79BJlN+95qkzMWZBHgmXkL+GYXhYKI/KmbXkAsUCQy/0ga02TE4cAABcaKMIRJvA0wPYidX
+RT5YJ4rafVtXtJXLVqe9G4u1dTYKftPver7394kbfNirVDPOIqont43SUUNC46y9ABDBLZmDPrki
+O+C6SMQ67+yppoixM8OyooAlwyb4Tk0yIQXJOxm8VBabt3qaA4bluvGvywQksd2xyj9AqHfX80MP
+KI6YwAcThLy+gSfpvcYFFWSnUwZeGOpgJsBEsFR5toKRw+wXwWiAz0ooV6QRwrob1PDU14RiG8qw
+chHcB2rW8PIVrfIZnSE9ociWJa++VFagILyYkhJs7qQAk54V91IOAoAgC/5C1dA8tsMaQ3KXUzz+
+tEZ96sjjFbAgPaVaDRQOaSM4aTW5U0O4DA5dKP2XZlbGLXdQrWxzz6fPzdatNmLjV6T4VaEUzhyd
+x60cUdzZRENDGVszJ4CRgZlezxjU0Q2Gcrgkc8lqfe/T0R43gSqZJdJypXBZd9ya+zjPlTOTmohs
+mwjM84TPh0K6riED/q48cbrWQzNp7B5gRbtvJupvN3DPPLRNBSNnbQJVyze4eDXGxdToSfHIu0B4
+FCwKo7SBChF8vh6R5TZ9IT0n2aSK5IA8j14tP+oEm+cXGEVPgjS1K0pQ4z8MHEMtWi5WphEkFEpj
+4Gx9ivAAgMLxAXRph9+GBXVpqxRweey8HfGhPc24nrUEPoobYB6A9CdyDSIiZ1QhF+TuRBo1qwT4
+Q0NYlX8Kbe7ZbVy2OyPuhxtBSBB7FTyfT9e0bhK30u708EvC9zw8Pq3Q8U1kbOmCHXKt4bBWDbCV
+1IZ6xXMoAcrc7kVQggrszuKaHoVlT5rqf6uGBFjw6cGXrmKYyzG6LIp0HRV91k85HB2fMF2jdZfZ
+sceVu6kkj4OUYgm4iXlVhMCaqKL5MLPpn4e8qOCIbuIMtAlJDAXvUm+eVn7Rknu+/EULiRUAz15Z
+pXwOP1eJw7Qw3ci3ZIdU6bEkFSbw0AuvYKNtkqbX0Pcyx12WUQGQex9o+EjJATyJtbJSSwmA95+F
+geGseispn5TFyoEI3ao8ibPUp9wKd84H2JFQjYzrXM/d06uw1IaYR5sVPoxZ3RRMzEImpejVDIt3
+kCDAgc1famgowOOgS5EWDtrwC5NfeUVE59g2RHJP0rV5D0raQvoCgGSdxzV9eOiA8o0OzIQ0VwKL
+24jDGeg5a1dkcLdzRf+a/cNsb6iDNNbnHcj40mIHmjkMRPAvtPsQwoNyRfk3LB5SlbvgjEoQre3T
+S/t5oofjLfbXqAsQU4oC4mEm9rOo6ng5Mu438BgKWPGycUuzLO8sLfG3p0f+vLMZGfEZDVFjAz+q
++Zd9kHyqRy2XQpWdjUOSeO6DbeXiLfIvarW8rycmgWwbGBkUcQ5HYehQsUpOtNJLzbk2Q9/MVDqn
+Kd9/N8Bbr+ybz+cC9W3CB91jGoJ8zcPhTNXyrFRgp1YNt1lDadih4vgDco20P718n8+Eis6GgRM5
+7R70fefl/bB8ULmqagi5G7xSLs/IYOBiQR8OHQCesJIryrkrlutHR1QQYoIBDzVhqV4o8cIu05Yz
+XwRC/+qNFLqsJporiVUQ36DWaK7ojBzbIVgnmBAhTOSfluriPY4QKp1bonHV8l6xpqIu3MKou+w/
+2IpYEKEJL6kqX22xliFgcjIK1nIqjRKsc2OBORrKlVGOrR9y5RLgKVxQwMQffrHeAKcbB4zSgBDQ
+oRZa0z4K5GozUGOlg08t7PQWObYZLdECPUBaRjRbnDA9rzR/NOctInXWbZ8hDOIMvm8ImzYhqVmJ
+JEuRovmkWYohsooqqhFLm5LcahNyYJjHleSnLyENPfChMdCVqbgw62y2Ixaa7vH0FI+ELy4GRMgk
+YiUuz/Lhmk6eOSkaIFEbTQEYnZLh7eqRequSRtsy8UyqEIq6UxUAjyvTPfI1EYGl24wmE8FFXSQq
+nRzmgVly0muvNZ9liNcRd7HU7TEra7c+/OjN6akeOQ1zQoY1iyJxJS1DS91bDRi7hF4W8FBXQ9ly
+2wrKmiP5ka9oyCi66RIqRUg/L6aFXI0fZfOZ8+RYGkC9x3W0U+paErdSM78lpBpKVCC1kbUyv6Mj
+cxFAYcMsEL30w0/pgfsfmhSPhDzuxCfYVjH1ndgLr0ecMX4R2sG69jA5vZVAeuSUMJxIcoHWNfC2
++Xd9CKQVjHcDginrGhfDeZ2J3QYhWOHWooCyEtCOTBH1PwX/Ek7K7BR+OFSZiPLUaylThPrnChXI
+skGr4N2G9I9uC1DKT7FkrckVH5mgNUvDYx+kUUARF58UvjQSzB1nJOTbuWIFGglmi7fzRUgKX96j
+FpAPC5MNXG/QwDycYATnnHISE/TQA3KtBhhTX2prcm+fT8JsuCDisaoh+KYvFQHFzsTEo8QGRkA/
+4DruY+B8QdStZGJHRpml8fgfwRMF/UX0bKGrpJlm0Ys2gIgWUqYB1gn0lV1/ZBTsDJGWR0JRFhE/
+O1yxQQy6gewdjAWYkfS6Qlsnd/NKaIKVbX5sIBJKxOxF7jh2wuFANJRUP6N8ak89wqRhKlcOeMUV
+weHPQfHdURS5LNzhyX4Ws5HJV/oho8bJdONzYmc4bsIa+EcxQPrfQLAuxuevbjm0ePFqBKGuzc4q
+i7ARguqmfEDCrCgFL7bALLbFOAzu6VGOTMwwCYuqyN2m88w7XL0e+Va/ikte4lZJxzAJjAu8ZOqt
+abSBUwz+mjfP8fF4AeBjSnq3FMXvZLE1DMo6IBCEmvYfbqI0Vz0fok0kRvltO1TK6+kpHtkgTBEX
+My4ZJP8/vbyRx4e0wkKOQRZC3M1pLuTN9PX9jiQPdTFNmaOutdAZtmodijucA7tNRO/GHOA71VE8
+rphXfk4LqERp3CQGVyWM+MXZ9fQAtalZPVPB2Q6gNqIskGb67yD2rZ3Vm1BwY3+gg1c36e70Mh75
+cmRbyAVqWBVKlFIOd0oXimFZ4ldi57rqP8EA0p5g5qn1NslR7bD1GETR9vSQn68VfClYyrmRw+W5
+vLODXs6sHhNt21OyaacByvqZCDQkLwSZ1/mNB4FXsvMyoJx7euAjW8ZE1dPkAJqcv6XULLaX5K/I
+Ddpd0AhXkaamdl0U/ZfTWKZnIXspw7dC8Xtxf+XFAJXfBPdlJWa2g9boofEmZAZHIUlSbWWDHts6
+XM0UA+cVBTN3+P1aBUcsYKo8S80h3CHtBbQuCQVE6T0jukSOcLzUqNntFHLr+68vp8EyYjZisn20
+eWt9yESMkNK1r2uA/8Ey3UhIPm1yJBVXnqjHNqgh8yQmhdR4qS5SZiSfCgXBeYDJemzYNXiFn8qA
+qCfw23IPTaTen57V5/SDuMxLGp1bXj2E6sNZTaip5DAEYfekgQY0UvVpSep0Z4F6IZS1siWPzo6X
+/pyB8P/NxXsfdSqgoag0oOLiwSPAHZimSZ1bQ7KPU02s7ybYP2vVsCODzkYpvH1YUe7xxe0wyUCV
+iwmuzYhrG30qaFwjWPgcbRs/Td0vryfQBORKeatyNSiLAJP2MUxbpHWgRTUQjJxwGsrkCf6XUQ6w
+xMdeXnvZvXujHNaEZ9sUXlcm60oKsfiEQ2oFvk57wrY4e+km7Brxsh9QEbPCJtt7Ju0jKSzrXQA6
+Eh9AgRaV7Y8GTcEUnbyV/Xsk6FiInxDXFZ0Av8wxgx50Jg5ROfiayt9gpguMz0ct/vQqH5/zh2Hm
+bf3hMEZ6k3SihwOON02DblftLLCFXaSqOaliNdfsZuFM7OmxmQmqtUVCOxrxchNnnkhc8ao6tr/4
+4n+bKxAeFkc2R1DOM1Sm7IMfd1QQq29KVcbAwkT/vKt5p52e/LElpgDOhcL1ORu7Hc5d1Sf8KZBm
+tA1NKdFeg0VkjGm/MqsjgYG0jXYIAvkK33Ke9YcVBh2sJkPLYwEZvfLZi3x6iaXsv2C+vZYPHJ0Q
+D69ZpRx8r7hYQBSSAQlIZB0VRuKuV4EKpFkTrGQdR0eBWELgof5BED+cENwmr5CxTsUq2A/NLVJF
+auvy3IIFffr7HFs5LHy4Xym+U4BY5PIVGb4JsZWBhEbcCqDTXSPvjNsC1vD3/2QoxJ+tObvGB/xw
+Tmk91I0l8JGKoSmuTa8J6HKaQHlBFPXRw38wGI5XlOHIs6XlUxxJmwCFaLLejibMtm0bzC9Bibtd
+k6Tb00Md+1bkadyCSDJzzS/mBY5J1euU8o2iaOktchbmlW525kqsmv8ry8CJULIxl4i4IZZ6zFnS
+6WM4se+yGuyk3YIXPSM49o8BVapt0cL4OT2tYzuDgh8wRRBL9LEW15/SQBxPddpnaGplTjRBkasi
+jMJI7oOVj/V5bpRMVDYFFx/ljOXcelWykhpc9cyornaBV97mZnUOXE7fi1XYrUzsyGgm2stYKOD7
+MkPODvdh3yoCjuO02LVe0M/91BLusXeCviO10w0yfd5K0vl5f1BdlzDPIY+QYbsuznIo6oD2hRxi
+O33250KaRupucn93+nMdHQWnQ44x9Qz6noezEoROHyYUmkC1ocKqdn51BYxzzVfpyNrNuRDNFl4I
+FJ7nP/8QaCnZw5AywdZn3djdSJI3wyZg/p6raa//kEsv+evL02ILUmmSUayny7OYlqInVegHvAtQ
+GSNjT+XfYWZ80aea6gKPApWwREDn8ljmlbKA4EQ2dbzxcgUl3Rr9GCrMauYAx4CkJvLNVk7z569F
+XNew4ORhSYq5bAqWXQELp7PA9CVle2FMkXcptr3Sfzm6Q6sQDdzLDaK7bC6iu5mC+QEEEqOO0eSb
+NE7fphluVunRmhXWpwnpisQz3BB5J8s4mC8OFWq/ldCKkBGlcgyf01woNnETfLlGzyi8T0knZsME
+JnS4/QCDgvg2kByu4l4p7TgzkcPpxz5WLru2ALoX1RZAOrjyHH7ULsvVXtmxec5hg2c5EYSu4+Ev
+SHjuzKRfEExVAl4mrJTgQg219Kv3P9fJ7LPFxczNTGg8HEZEIr5V51oe1DDTtZT+LQNovD99tuZc
+++BKoew5W4bM/XBr/r/DQaowq6um1n+28ISLXLjVw30qGttckm1cb0hwIH7h2bCyJz+VGOZRIRxR
+21Vn0aDFNwRPiGLvoP8c2nMrMC/SbiPnnpPokTtNT6cnuByKArJIBwKjHMqusKAXwSNEW2ICHgoz
+WB/8KxRPPKft0+6bgOb6xkw9AGXcpu7pQZc75H1Q+vz0NWVSjGV9L0J5SOvzIbDR8Ihv4Qgkm8kc
+zZVRlrfz36OY5LyKMpvrLc4bjWgfSWCmFkB16gGWCHM9FiUlB275GmjiyGCzYQhcNLre2GQson6V
+51iVaTMiMfAYqy/MOy40bsyh8b648ZnXwVCLja/pnmdMJUPBT+whMqTeDoGVr6Zs8yiUf/DHoLhG
+JFnExbaVAtD3KDQSZLRdT+eYhttkbL+6E+jQwoQgTlFyokhyeL5gHUyRpkNQ9MKi4BVbB6gsJl+N
+vLR/DkZZnGIeJOgCDDweEQX1bLSznsVYej49k88bgHIE8qwm0i4UlYzFVxkSoZH9CTk1jIv039KA
+pkMCSXfWljDW7JLet+7HsESCwWCUCGiZ0GRautT16CSoY0cri046SjLkjAKEbaO+qIS0vAKAm28b
+vW33CMDKzhBG8hlKuclKbPx0inkj43sigeAyZx7nYsZpicp6GhhPVggLoERq0Rn0eC2bOjoIKA/W
+lLaNLi4HQfoFKWH/OR7L1NoopaKdZ/jVWbsvfb0ZFaPyEKKPwkB4oCxiRZskgxXoQ29jiBeAXi7M
+B7RToJGqUbDyxlvM6O+hyHKxa6WPjaXh4ZZXPCOMM5JbW08hgNdM0G0TQfpakHgfhf7P+2SwwVyi
+EaY8R0oqC2DbBFhxVLCiLxRxWuvaLSF8fw9Di2E24OO5qi3WDe2cjiaaAJS+06p9NJTjBUpy7ZXW
++tou4MEMu2vQIGPC4epjjFQgS7f+mYZ2i8MnXTvoi0P4/nN0+gHzESQh/lSPNDMZGT3kIvJxSOxa
+jZNvA5IG2xB+24op9zs27MMZfB8LqJzMxqGBT258+B1VNUX+eeQ7BlF130LwQT5L2U1evEe2eK/l
+1c827H+2EhY6qvc909qngTb0SNZXNvEZ2vRrdYo5Vi5+EBe5yYVuyUDploghaBYwc01k8kWpspS3
+FA3Y+DyraXXeoJ+Zxds4nFL5Dl248HUKUaReQSwdWfzZylYErgRoAgG+wwXxqklukQDtbOBh6Pjq
+ee6CIS7cMogS9/RxPXKGDoaaf8qHN1YpjXIwztsuaHThLGZDXJCMtl8/qYxicUZBs8134eEoFdRW
+L0s4Q+3kB1vZGoRtIaM39R/MhWeVRB+QToS+2EcWTgsJ8mvsozyKfsKMrq+ETtDvTo9ybHMA9+BI
+UB+hgbuIOqAu/KJLYVbHoRTtsG0NDFghkr/xVb+5EAuUHeS2KM6VLuoevj40dxTIMgAfnw8K9OpM
+6lPohQrFuctB0voXvBGEM+je2k2Kshzyabp+Q+xfwwd+3iaA53lvAVkimSYkHH5Aoae/I1QRGh6m
+Wl5GcZbvA6tea7l8XlqTNiCfTjRFHnjLen0glp0uFuloQ827E3XtpVPNe2/SzztUXNBtbfaGWn0N
+20LwoSIpoxhAmVUGpru4FuEg9Ty7sxH2KYIFT1aBOPi+kJRQd5CZLQJ0G2ufJgwyndHj6c8575TD
+MGNK3FuAGmi/gKtZDA2CBkJZzNCmDihbGbxokxdBucHvCMJDU61VHo4sL+OptELAJQNgXezcUZo8
+1ZfRxEEIOXaGLNf3VtoK7lDExR7C5z2Cf8UeTeI1H8DP8WzuC4JVAl7K7llWzAM8ByFIo7OIsJHg
+xGIuuLFaW9sCna2VeHZ0KN7tkEHRNOTWPtyoyAn1RiqglZMl9OedAI2D+DosOnTSmlnw4/QX/HQs
+sN4DVKGr7Nq5Z7+4tIUBCrWpQcTQBiQ8hAqZqyLGP+30KJ/2yQxYZwgCKGBFHpeHc7I8cGcTUlTo
+5aVmvRn7IMrcRA+031DETCTRimjNbvjTMi6GXCyjksADNDE2cGB8Fq6kxm+RITVuWibdyuQ+LeE7
+Gh+oAwkW/Wt9cTUE0xiIKCMhKTqW7RmSJakDRShb2RafR6G0QTeeXie3KhLuh0uIuGgXGSVkZSuu
+tU0ZdBPCTfq0kvvO/5WPB5r0hYPF0WKTyyaCpIejQNCSsH4C8dJ6nng3WB3eSX57NipGZ+NDNNx1
++VqH6NOQrBhvlxm9PYO3l8++RDKUQanhU4R1JbkDMuaaY+WNcCMhsHRtmc0sWzc2m9M7cv78BxPl
+bUamNsMPGRTM5eFEk6FvOzHGD6rZhnbr9Jt8p1zKbrAyzLKZScw4HGdx7ZAwtnqZME7h/nzMXCw4
+7N/nNy+nJ/P+JDk1G+VwNoNeBxAAGUXeASywsfTYSFeovbjYoDjahu6b/a2yz1HRt8cfp8devj8/
+zXDeuB/yL17QiVrNzlrCXnV6Byy8/WpcGudfvVqXKzkf+A/jDEmGLETGOOqttyth1z+Caz73Vj7Y
+8oZZjrK4YWDlR4kwz2baYhHioB/oZE6xcpY/PZWWo8xn4sNclLCS1Gj+Xpfl5lfs3L9pu5fH72sG
+mu8ev6e2xSLsgmdORilkmHID/NRBhsB+RHPzenKMB2Q8z1Z2wryXTw23CLkWxpWED4brnV9ov9qv
+mX3+l/P9cWWYIwHj49Fdvs/TOqsNFEHnWSGE5VAvcrAOckxXd192z7X7gGTQ2gdbCRdLHlRjKoUV
+zGN2Lm87Dli4+THZrw9XgX1Tuy88C2w0N1culrXvt8TYK2h1yMn8/Ubn17QVdxhjbeptcBWeeXay
+a+2VhZ3v+hPfT15EkViFSgnLcJ5k4KT8T7UR/nTQaFtZzvmonhpoETJUAUeigOalLWUofHcejIi8
+as+72Fib09peWQQN04hqM5sPmqk9td4+RDK5kPE8y2IUSdZ6zu+ltlPzWgSPyBRkDd2xvxcwucau
+wTW2WME5D6Ebun/BvScQi/Zfa7N8Tz9PDbyIJ72fYilQMrDyXT6vH/Or8lz55d1QcUR9u3gZ77Pz
+8Fq50e5Xdsza8i4CjN8MoZ7PO0ZhzyDAwP7s9mR5jmcbTrHJNr5rOqazBt3+VG9ZxE95EWlGOYuT
+ej4Y9CC34V5y71Nnst88u2B5861sr97jxwIAPUHA/DNpDp7NYcSuYzPNxHnL4kW8kTgfimuROaiO
+9S11cPK7rW8Qtt5VO/XCOltZ5WNx9ePYi1VGVmZM6JGQq7j9Rn9MtsG2345uvK3P5P1a2ezYJ6Wl
+QN8CXB198cWDIEKvOhqrorYrROBFCRIuKlXq+NZmlRtNt6entgwEpP2UPql3KApgf3ALh6uqN6Hs
+BYk6OYLSKFtkkhBXlqoQq7VxWok5c0z5eEQYCoQnvX6oSKaBPNbhUIkp64PcYaDlQVb/lltZBi5Y
+SVZi6HL15lFUmli8BmbS7LK0omJWjS0kqkcN5NxrtCeN86pLakcc5fQ6KtL0AUaTdPPlVaSIw7OK
+pJ0+qD7vnw/ZRI5eQlUXWDbiO1lskGclpqpNeotqfbK2F5cvOSbIG47aDYB8DRbW4hxgylNNliGM
+jpF1meUggVE/oAGHlFKl5Up8n0hdg+5raiBfS3G7FmwkEtObJBq9R63Jmhwdga7rzspUl28BlJRY
+DVVhYdqFiH3S6XX5lHzTdqU9pktUm4CG0b46XBgVL42sMQy8LKWuw3pESPyRaIh0beAONXavqEFr
+3RBtMTrtXiqaj69+bfmmK9EgnLZRoehrRPdlfjn/JIX9QYcLxVfsjA5/koBWU4hZ/ODgtBCjN6zI
+Np4U6TO1fzQJ+qIzz8dC5toNu2Eltf182BQ+Ggg1SsIU6ZXF7YSgq9CPsEScqjF/luA3Hho0iK4R
+3lwDih4ZaWbU6HTiqSoA5zmcpF/PzneWPKGqF+mgKeA8ufkYIRpKq+rt9Ef+fK6pYlL2Qj0Azoa4
+7Mr7hjikOYpWjoEizqapBnyeSn+lg/LpkcNng1ypgMqkh8wVMM/4wxHz6U8o0dR2jicEnj1gLGpH
+qa/YbKj0PGynfGMkXrKRxUi9pKGfvGnpKK1EsM9Hj98A9GZmLYE0Wxbbxqnr/bzkdJlIOusbP/eE
+72osAgu0GiRxzlAxRtHly6s7xzGIPqB9JIr1h/NOtSBV8sSDb1/nCOGMarxNU0PZf30U8M1zvwDY
+AYTZw1H8vqM9NUYdai/YeiKIhNgwntpfXj9VVJiIRGGNduX7N/7wDeNRiY0GbIgT9kV2mai15IYC
+IjQ9IqJu2g7e9quzmmEbgCppgrBz1MWekUexTrCkRSZ+Cv3zKBemMw9rlpVHwueAYsoa1E0mRdft
+E+4Q8i9dvdGsHWxiM1cUkcFJ0Grfi6YmANrQegRih7o784T636is/3od/of/lt/8fXvW//pv/vk1
+R/NpRo4t/vFfl+Frxbf/q/nv+a/933/t8C/967p7q5q2evvj8qWo/9i22e+XJsyz5d85+E8w0r9/
+ifvSvBz8wyZrwma8bd+q8e6tbpPmfTh+8/xv/v/+4R9v7/+V+7F4++efL79TViesmyp8bf789x+d
+/f7nn7A1SPiI0v/1cYx//wtXLyl/9+aF0uv/+p9H/9bbS9388090of9BPAQXqvCF+Fbz2e3f3v9I
+U/+hz+1S8gVkXzjfHLEsr5qAvybL/wB0wX0LooItxMXx5x+cs7//TP8HPRTk2gCkEZVUQAb/5xce
+fLn/9yX/yNr0Jg8xMfvnn9jKcMY+5EeqLtKzIKjoOnU/KrSLix0yUSCJpdC6Qo49L2DPskPyXcrS
+W0GuZIzKBLprqj7kg13mGVo0Q9MOMcrGJvBJFMhkR+gHH6XtMkRfdzAw+LaxPq+8TaeKqBSbeE8M
+GySy/TMu3lZ0QP6UsyFO3WBCQn7wivZQ4zkilmbPlYzRE6puNdpAvdZiOoBQuniNkqf0ze/rltq/
+p85OljRhmg061ZiSx8hmJw7+W/WtEsp0Hb2mrgoU2SdxcLBR4LKvwG//sHSAfa5IvyLwUv1pEhsR
+satc8vYRviO/G3kobpGfSV9GrcHmAyuOnh9RhaxBhLjQ5MShPtyqPZICuD6IvLFCPH97u8OI5Eyv
+EINCNYEE2qHKjdNwlSZ4Vg0VPXFES7qacCBM4csYFCqSLZ6HdF6AZU2wa3vEcO0gnawXs/nf7J3Z
+ctRYuoVfpV9AhObh5lyklGkDHvGA8Y0CY9A8D3tLT3++Lahu21BQVaejo05E+6qiACtTqZT2Xmv9
+67MYPTSrtFb0TAnkY3Lm/j4uwEWFeA/LceIB/9j5CQWFEa91uKvrakSFGALvtZ/UxVVsieFab9ys
+j0qK8E5tUusnLbIqA4YALKhzSgbvoUlH/24Dch0HiTedA1XjU+9dGlX3VGyOb3Uh6tNEZN7t6mG+
+RFNlludD2QOE6TAq7j27hSlZrYPcwXPNMZeb5p7m4+4dFZL6AvJjhn1gBKD86CV1Curlg6IR1xoY
+6EeO6OivIfo4N2Wdi+wwx+vsR2KiCona8bHM951uZQ8eczafG9kpnjp996MJojao6MBmCI6HMaVJ
+aWgSPBlCqTXTNSEzx0NQCBwR0T2d34IUtYfXWR6MbyDNJB+8xc7fdnKJP/YUFkJXib2hYzfgje/c
+ul4/1kTfP6QNdeLU4unzWdYu1Rm0a54VFA/EJsCyNc535K0bC6HcophqrRvBFCAr0YfUccYS0AZd
+pBHLhlLj4vP9E5164STM6cc/jyE9nHWGa95VfuPeqwmAZOeKqT/Ra6t4SzqqDZesdMD8gkN5R+Wh
+oG2oag0vNGVAW6NLnI0Wq8rke5GNzhXrsK2aLZgP+SqMJNLtZjjQJhq8yzA9j313kJdG3waExWmI
+iGNq0ELuVjUbk7lPIYgKWI9HzNnO73iKAKUGyTLcD7ro3T2gcKbVtV5ReCePxnxypKzmD3Zj9KfC
+SsQnv/Mh88w5Z3XsSW/v4SGI5UBbeAzd0y5tsOHNupq71qa79GhygNpD75lXk0bxzHmnYzHcr35n
+OqHeCgrgvBg4Bg11hQ17yyob6K2FPj7WPm0WB5sgwWk78SEe625S5AdHn+moiqe1mI8wD8DrLcti
+nUiqwi7zgq4/BQyLH6E5AOogYGl/tPiIQAR1tN0RkMhBxBmtUYW9mHyHCmhBnS5rwUpGfaMupZ4x
+2QkCscidqNACnbboukvcMGDa9YPWBMM9sPfyRMx5/UA41HF31G6a1gHeTw33nJZRZ5/knjteVtng
+XTFHSZ85B+jf5gbNvDvIEGCGjHEy553f8UJoYKeNeSgs50MOQD6L6C7Q+v3ixuNhpm2Syu5UN7tj
+1xPGDc208IT0lUpA4ifCva2cUr+g1qxw9kxv9qexK/Ms6klWvmclrXErn/zhS59QrkbrIP2Le/Y5
+c9TkY5ftu34eqwiIafoJMnOvH4DqMV+1dLL4rPFWhtAsZd2FTPMsXmQlC2Rnmk06Sn37zmPEPbXf
+wcpNlr2TNc0jbMLgaqaeCvoB6dl3cVXBh5jwsfOQWx3XhG5akIKTVdivea+JA9M244ZH/3hOpWqm
+55B+zcl6L6m9YtHtdPoUyikF3eEZMr9rReWN1F7X9RtB8e26b9JGfNZrw75pclcj9FwYdQ/eS3RX
+kJioX00WZ2b1TGE6xFepk53Ug2Qx4MhTaxYNdSfX46S3QWCoWWo8dLYwAM0h0/F6mOaQUWKn8iGx
+NPOD7zbdlT1Y9JmrPkE7nGnQ0/a6xz16VzkzfXTaNLbvhxGLkL6SkULzoSBku28oqafGEfQ6/B8I
+TUfJYnFtUz98FkhIGVFCrPpDLpE0DtnkUXlot3HWHZXTWPP5jF3+mJWde2+1EGX23QSMl6L8wNYO
+TFyaxZu8XowbSEC6/XaFJxccc324VmQEWWtGqncLxvGyMI0FWy0rXw9+bzq7gSrt9XLggXuT6DmD
+jvQKZtPrQndoPy9GIw6AiJp9RM+AW0QNjD24VST/cP1HTy9oKgSzEa216I6T1pMdU3pFZ79jWqUo
+jlK6t7Vjmg96AV6qKeQVAIn4XczNiagd033i3JyCwghTSEX38Uzrb7SMjUZFbdUl+UHPIFnssnh0
+j0mW0PGkL4GkjmWMV/QOA5YaFSKGZkIepw3n39tTTGnLGuwMzauIHBr5DHhypIht/9PiYggrqc+l
+aS1XnjeT3/7aYZzpPKP6yurjY6agiKbJLtev/09FxrYUQF2tYOne/mfajJvWit80GsXt0UhXM1QS
+MmVoosOi3+h6vDyUdLY239qMSzxfmnB72fy8zXgcTO8ijVGTwu/ajCWQAxrnE9eg4WIgbBe2cMNp
+07B0Zm9NuiCo3iMFs4etZrn7sl+98zKN5zu7npIrGwB8ddJp0nukNx0PYDChHewaSo01opfFOO7T
+XvK4t1cx6bTKz/5NPic6twNtpeLaThcIRzlFokBH6IJg2pin91HCBIex94rMyo68zDPBixQyfe/H
+oKIitnsuN5ispYOaRs1EhKO/sBnsza6xQmDBIISKfq38sJ1jK8pdUVy5Qz5OR+1U5jA3gduJKNfZ
+t+wSMuosBoDnrTyqTW735TQkVIvzoHAPRpFWN0YX1Ijwoi4zJsEQH36xzVRb8OfbA7QHtXUmSqk7
+bGaeb9FjiE1VYC9ZpAuqbOhRHSj0nPNfbJlfKnbsQtRhVJICKcBk9f78MOzYuMNaFpjOtj0eg3KK
+kGy1PXOWWti5g37W2VN1SDuv3ccyloeO4PplPI32LyRVpQZ//3b/9TpeKBJ2q4uRtg5sm57JN+l4
+/RHCHv3iXmVF3CQh9VgYO5Vo2Cnpyf7J/vHb7uzpbuxHJxtdHJ1VDd6RUXh+FtzVAvJMLVpEfRDw
+dqv0I+ghzS9OtvrIXr7Hp0dhc/lU0+qbrMlyb8oiP0mmN07nLns9meZDkwFP+Pkb2lyDF8dS6RUi
+oRQSMIDx4h01FJWn2WJnUSV1Lu5Jsnil6r0vwDc0VndPLxu4V+rE9PuYvvBIjIDFgJpXxlEhDPsU
+VrftAfCDsJTNeXFsrKb2eQKGdt82BWtfjbWYE3FfCC7ok61/lV/67gNhSU2wF6eCYRy13X5+qvJ5
+BseeB3kEZ4hP3M+avZZlxi/E9R8exWe6jupLGhNfjg0MjSXS1tcYabdNvl6+VR2oaXB+Iel997Hz
+XkjbEEshtEdrj3oVT2SwBP4UKEU/j5iZp8qAufpDJoz8WMa6/HPJRJR3N9gEb6JlmDzOC/WQ1bOu
+61lWRB21x59W+oGvHSfpDjRHy2jwG+1NEoDs+/m19qP3R/IZIyRgnjl4Wc/Yr5zghKYCUGNpB2EA
+NPMAGIGJbVBQf/5QjNihqFNYi/+iFNsnp9IpU8X75rIQqzWet5Tfh83sGx+ghM6/+LJ+f20wksjt
+kTWnCtG99B/1tcuWdvKLqBVrcwQ460tvub+qXnjhXvF5cT0wAU4wlTgp18jz9zNYRjHaU6YuQG+5
+mdizRatmpye+Vg+netqWpzW95b+aYPnRW3t61BfKU+wujW6ncRbh0qzHwsZcStvqV5WWL3TS7b2p
+6T10NIoHeZA9f2+OXLKiQ2uINH/KLqoCROfiyToE3W2+BfcWo+OI2DoGaBJ//Pll8qM3uAnoqtWM
+SYQXdw+5Dq2mSabpac+QkTuZkPOAsUR/4SgB1zsN0lQDbZmjpxdjPrHOiqnE98x5pqa6KQ6G2kz+
+/CjfP6G5RmjrRNf2McOpenl+HhswSTW71hxGBCvZSLVVQa9iEwZek+q5kaHgzDpZ0kKzwqHXa27Q
+Ha2o9pKDJ0j8tu1+8YrURfns0aJeEHN9aJdqSv3lnMec1HbXkc+N4rWzjxJIHJe1k5UR9fGuvgum
++VdZ4B98SxhzolyAuLVuMxLw/Ayko21rsyfyyPfIzY6AyObI0xr/GO+Z/Xne+iczIKjqF4uC7+9r
+KnuAg8FRXSYY1VX25PMdNcxtg/nSKEFlOsBaw07III4z88qY9i8uppfRI/V1UZlMMtbcEnDVXiwO
+glpfvCChXqXxJvcMJkqwG8pBu+qYn47moowTJDdjZjvbmPKUhtrgjCufWLTFHvZopDb2gFYVH21X
+338dhyeOA2ODanX9+37Du6z5xxGWw+Pnfzw2/7iayqfOw7d//ZvvELwiMcyIBzMl3PW4dv7lO3iv
+kAUD5SSy2sZ54Hv1T9/Be8XYKv+OZzaJZha6//IdLOsV0y+U1Ot0TzANg5XxZ3yHrUr42deXwhGC
+7h56F0sEqEvPL2v+kCp75rdZ5jL30SXtuTXxiEup4rJIv13M5QqCDaSiPaBDAQdC+90tfj8AHdL9
+SierPhrZ0l+ZAcTRHXxAOoOg1yf9R/gQWn+xxoNeDBh8xLjT/VpZS/oxKwiK2K8FZFzt1kfnBCHn
+zI7ITnUYyE7J+hL2j70zyn7OwU9o86A91lWuxX7omHRfzmjATh3fC/RiEPNw13u08hi9x26twY+6
+Wp/Q+PoEVqpd17V36pDQOrMZ6ekjr04gdlPUKSCedvEcDT23KWYaxv7EzycIoDqcyouyssSXtWJE
+P7RGP3sPNcHzdyt1EgYggCbwQ763+ptet0aU5sFLzhd61TBC8sD9pJPs7w5Vnhb0i5VZcJUxLHEb
+N31/i4TSXC0VtFPeRKm/JgrDv0pgOV3lrtGde8TMTznrpBByfTZeT0ZfxDxQ+vo+L/rmJgYxh6jt
+ZP2DtRI12DV1n36B+daDHgQIpEjOKs9NxxjEWuDa4I8KKaVCV2cfMwtXZKd5evzYWXV/uepWy4bd
+X7RpD7O9oiBDZu2FnyhGbycFmmiJ13NS+CIw6YNrlltWjwXUjoD2x1Bz88lTYK0ifatl1PDw9k3r
+zI6DGSqE51OkawymGcW8tascMKJ/cKRuvm+NIrhpZJOGsi9dRSqe3RN9YYJml0o5vV3cZYT+k4DS
+CL1+7K9cWrdq6CNafp7hC53ow6ZjxRMwx65/vwRTdhIX1PAnqVtCabPH0yxn5mZnLTNri7R0eDZq
+I2SvXVs6fhUadOid0MuArw4GnJDV6FYJBlZqaZ+SvvLfNU3coJ9PqX5RZwtPtQDZf98JOc7HGhDx
+R9qAjJtKn7DkwOoyaj54XHvoQD6EcN2onFMwI/DVTcwtGHyduC3LdPigdYWDdiAd444RvUqVJzdM
+u5bYeR4yrtO+nmarpNCgWewrV3jLuWdXy8nA/HC/04yiusrGwEwwAKvM29mNl3c7vTIcomJE8joY
+ncX6GZ2PHo2k0LX7yRvn95BA6BH0sO6ukfHdqwZGHRJu4can0MAbd6cLzSRrisyA4Af00dj1dTUc
+jN7relwf8OI7Ay/tnQuR+sEcRmuJ8sHwzimXWj/EelIybj/J+rok8H8p6JgyokKU5pmTezq5Exh/
+gHoX029DzMHkwV/z4ROzRPZF7uoSTqSmwZ4aO71hVrQTkB3M1o2PTc1cbir41deDMVeUkVGbddfl
+wERwRPriPdtSWYZ1LJePA1Tcbg/gzv40+xNVSnXB/975sN3eEK5AKZgMi/MccMAPFXVbd4Efi3U/
+eqtxNq0OReQdo7phpvlIDpYPcnYX+x3YiYR380az8RB3yKwAYIbBxPtMJz8Ne+lmOa3Q2ioAhmXi
+wRVpl+3ioZN4YPbc11HVtvgjuifaE86jfw8zOrhj6zxy49KKUe7HpJW3biLMa/oV4yHSZN6eVSWW
+Ioi0OlMadt7Jfc/YUxmWyG6AY/gr7+gxwyNp6Y66qPIerSYoe1fD8ezVZL1a8fE6NO+LLPtGHilb
+PItKoxVzmNpjVmJpzf8lff0NSV9WzTxy3o4td6YN92UZmnVc68P1hvxiYLvbzbUGGP53uF9dzqI8
+BEhvmf9+7tcK0bMN56V0d9/Bv1rozJiIYgCE4v8Y/sXDHpPJkTzOnsG/MDoU9KP18/t1gDx0/p/j
+gNkTGM3ImwZbXP+dYGC9w8Oudfz8/yUMTDP04QZAMz3HQhHBqAoFe15bizgzJqvsd3+QC4b1GedR
+4Woo+xscrBsmL7kU89g9sqAWV2Y9zC2Y7L8xJky6AgogNcEOyLeXnLBEWv0UmdoyfPlTnLCWoMBF
+ttT+RawPiLp/lBjmlZ2+7te2rrSDRj1JENVr47+tKmht2UEsiXwfWGtcHaRpUdOXImt8o4cJc7WH
+fTLoMdmXH+PDitVrAKqSHzj9ig/rTXd4LVJDEHxphHW3FkWTh89wYl5uHy2rk5phVfnJcHCA+QHX
+7QpxsSy2LQ5EFdYp5Cn8b4CMuVmRCJ9PYazzK/EUNbbiM9+oXMNz1BimdpKz2nW+loD+dy/9dC+N
+UsXe9ff30lcMTX/8R0hskPouZL2vmUAV/KOVTf3T3zbS/ivVYepRtsPwubc5AL8F+KxXZKkpPCbo
+jC5Lgu/JRtp5FSCyu6RnUW2QRtjd/jPAF7yymONFzVWFROiD5p/aSLNNfraNpgrSIemu4x8wAvAy
+vmd7QgzDNFVRTUF6mHd2fO2K0TperWb+9OQMXXz9pT91p9ShAvQE+n5Yqr/0csbJq0c7BTxO4N4L
+Z2N2wnINHv/KQTAQ8OAYNgiUGvZE7SIin/heQxQlBUy3T0EpRzXU7F8YFMR+vztv7JGpSuHk0VKC
+JfL8OFpQ6KXZAlv21aZ88RY5UOVcLmcNzY3eKYh5dvDttpu3tp39uu3ytXHb8Y+BKvLuWcY/sqzQ
+YyRPrad+ICRKIzUSfJbHNHga51V6YdJXGISSCdMjaPZ+dsiWWNbIlIpGqemaA67SlpoHzz3uyh2R
+nGSJWqc0PptJYn2oMzE/lomVrFHQVib5OzfOrXCWBAZ3WlKNCR7h2hbHJIVWIH6mrX3p6V05bSaD
+KQYnzTIP8zmfPlMbmcGIpRUiDycGi66k643JzhOOeVP7TczjsShzEOMIVaFc4z4LV6/CPGnqKSdS
+Z05M3xLMSd7bkykUblv4WQS0Rh927lRjmtLU55bhuniM2iFkjl+6wh6nMEauacIVSuitY+YOHGDp
+mp9GJhbeWBq0dHL1Zv6R329CujUmbtPYXz0Te5pHjJGSzdR82yRzfaZ7Oa6813rOR/JBwFNz06jR
+89l3zSH7UbaTfTHMFB6Z9XpaJzPYAYqr6xNArpL8KnNHNnCRVavCzO8n/zjTXFmcLEMHQ9z1+gGq
+r6oNvTQ6neGktHad+5QIKfPVUvaX9Whm+nHnWJxnfdYGC+1oXU71rupvibYS1kv8Jb+WuMMPddok
+PheC5JGXDxKGZ1GUrRFOgyP7t4ZbU/GAwWvab4H+UI8uPTv/HBtJfANbT1wDmEc2kHjBBNa8tl0I
+3Hg+5RDmlPTvpEpbMnOQXzhbBHPM3PI2Lfzu3iQpp5MW7Mvzmnh4HCWt4d4WaPenq8p11hUhKyS3
+elr2sUp+xs4SLMetyoNaWeA+9FtItNsCo4gZzYmT28apsQVKp7YYrgOVMp1V3pQ0MNHTtHX6u2AL
+pKZbONVQOVVti6yaMu3vnYExHWB3C6HWYAu4JirrOm+x19Fs+/So3OKwC1phsnNUSrZJmGyCB6vC
+s8MWpHXX3JqJuS/NEDq9Ctvmzpq8ZvSSCO5CrJpCdKhorA/kJC8JtM9LaJhlg6y0mjNw4y3Uq5Wi
++jiopO/ceO5j0Y7xMdtr0MmIQdqdTLP7howDXzKVGI69ifDwVLirpGLPpbXT3ALGyySGy3KLHdur
+vebs9cn775ctmswQw4hsqRLLrpT6udxizLm5jl3I9p14s6GSzoOvDTFYE/LPribJyta13sLs1fxR
+DxuVlh7SLpb7aQtRa7nWxnvCPoSriy1oDaGStKK1BbBdlcUWWyx7AV5PT7sGQHPnzIv2eqXehDyX
+ynOPLfTSfbzFvJctKkLIl9iIuUVI0kkvb9ItWFJtIRPdzFW+cAufiGCqR+pPVChlxLcXUbeFVbwt
+uFKoDEun0izkbwi2JLEKuQxb4GXawi/SSwnCtJkKxbRbQKbIF8IytsrNoFsZMvK3OE3iA4Tdr1vM
+ptkiN54NF5TbGEkcPVVf/2IL6PBV9G8SUnH6PtsiPMtCyn/fFBv/dYv5aFvkp1fpH2cLAjkqE1Sp
+dFA7Nd65t0WG+jVuaB8K6pS1oNnKqNsCRjRTEDaSRKDzcC0b886q/LH+KzR1zZ1S2HOTeYsw5B0x
+L/JHiOqG35hvfG0u5r9CVC9LMz138pUoZZca5lnrK5Y4gyQoMUGmtxInGYHG37SaWqDVIk72nkaS
+Quk5Y2mlF5jSqDxGO7fv1Bkhouo68YmHwHbHXGov9/GmEZWbXhQr6Yj/DIbIUYKSLEx5K7J6koSC
+leK0enNwJybDv1+VIFVu2pRau9SRtmlWWb6gXzH9Jh7GplKq1qZwFUnJvVnrlfKVemX5CeENPSwp
+bfPNZFYrT79NMXPnaagArINVD0clqjlDa5z5m9JWKtHN3+S3oacYzt5UOU8JdB6Yc0qbNt1uVhLe
+MGtTt6+UsJdtGp9Hhcz7bjFybTcHSXXXb3ogBkJ8TRIUkbAl3dhvymG6MkdPI7JSFItNXTT4Vl22
+BKEf6qAtHwR5GCLemyZpb/pkoc3mmUgnC9VSCZgruLnrKhaomosSOOu5gy6/qZ6ZOdkH21qz1w7m
+xzuNIYFpp28y6Wxo/YGCHcTTdRNS101UTaypduHfoLXSYUgNb6UUWGTA4lrLlSw7K4VWyCz5SJDZ
+LHiK6+tnVTzQ7TAbEHYbfSwYlNoEX4Rxbs+5LaqrfpOEXaUOU8m4nndKMeZZhXhMTVb7GoxXiTls
+6UIAWlNSM5NX5p2XkTTbFUqLpohT3NqbQJ2VvvNmcIRzSl6VPHm/idkzXUho019FbqV3E+DXH9tN
+BK82QbzatHF9QCXfBHOtQzt3nVr7NGyCermJ677VIWfpSnNvNvk93qT4ZJPlzU2iz+RE2JhBifFU
+S9DwA6XmS6XrT4ndv1+tYt6vSvXHAU5OxNAV585mClg8nq7kZhXIzTZIlIOwbmaCVL6C2CwGUrNp
+2CjfoUwz6322mRFopeZVtVkU3WZXiKwXt7nyMPrcwc5YN2uDjnFsjmKzPOos47IoNidkM0VagrUn
+/WaVFHNmFWj9FmryZqZIU0/mvWa7nUvMG78lVs7L0hh8kRflxxSWK98GYp7KXZCR3N6ts4Z5425G
+juMUQ8EjCX/HXJXVE2tr9xBsBlCmvCAe2/X9ZBR5fCiUVyQr02B41U6c0znvu3NN4io5renlzA7g
+Na2b7dR5aXMVKC+qSzznlqWIf0UgFqdt3WyrIhjdT3Izs3Lla1muNcQRsWn9DQ9Y3w9n8pxcQdXi
+srZS3lgthK+FaVeLL4xay4tgs9HSzVHzWsw1sRltYjPdfr5TUTuEZzsvYor44/RPk40k4/YiECEZ
+f617O28ip9C6y1Jrg0h5Q0cpAKH3Pz/UNqL74lgUkpINYxKUweaXBBroxH1SE4eO8saxrk0nabRd
+q2vxfedrxCsGj0Q3kyQL1bOlbXfZIWid5Uu1dIG1LxyzvTW8UQfmOBSt8dbqkxywCWBUgq+1bryV
+UjTXrTn5esTnan6e+nl1I+o629djZnhncpjzL/RTDZfUwy/3jiOWHKy909CQ0xTBRzlZ8t7IhNuh
+Hkv/cqzM9NolSv9Qi7JC7DAHhoAE+6Pddl7+X0oZT2YWv5tE/Do8+W1OcRvFu27+2l/6zXJXA4/f
+/6JvMsbX0cZPDWuynkHJhInLpwqHGgF8poxsv2ibqvzZLygZ3RynRwYfUVBf0ZXPj8InlBCGfvsD
+x3pFRIYfJrK3n6+HenJuvn/R309y/rW/8+y1/8m5zt85Ay9+y5MzYDqvbJYDcDcJAm0/z0+EHbyi
+zZq8hNJ5vv055/xvdCJ+FDf506fB0l8RCCM0iL717DowXlE/S324RXxW/fztroNvMt8f+R785Crw
+XhE2RT5Sw7rfPuWnp4HxX8pNyLMr/qL64RnxR6+CP3CpfJuU/lR+/tj/z/8CAAD//w==</cx:binary>
               </cx:geoCache>
             </cx:geography>
           </cx:layoutPr>
@@ -7594,7 +10371,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>204106</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>87475</xdr:rowOff>
+      <xdr:rowOff>73269</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7609,8 +10386,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="114299" y="750145"/>
-          <a:ext cx="1994807" cy="6004830"/>
+          <a:off x="114299" y="743865"/>
+          <a:ext cx="1994807" cy="5923635"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7694,8 +10471,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2195827" y="732924"/>
-          <a:ext cx="2763909" cy="904466"/>
+          <a:off x="2185244" y="732924"/>
+          <a:ext cx="2737450" cy="904466"/>
           <a:chOff x="1865697" y="746064"/>
           <a:chExt cx="1996342" cy="823333"/>
         </a:xfrm>
@@ -7780,8 +10557,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="2587433" y="1214813"/>
-            <a:ext cx="1042492" cy="269467"/>
+            <a:off x="2518635" y="1195545"/>
+            <a:ext cx="1185654" cy="269467"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7811,7 +10588,7 @@
           <a:p>
             <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="75000"/>
@@ -7825,7 +10602,7 @@
               <a:t>Faturamento do </a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="75000"/>
@@ -7838,7 +10615,7 @@
               </a:rPr>
               <a:t>Mês</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="75000"/>
@@ -7908,7 +10685,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="ctr"/>
-              <a:t> R$ 26.467,80 </a:t>
+              <a:t> R$ 3.661,80 </a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2200" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -8157,8 +10934,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2177701" y="1714500"/>
-          <a:ext cx="2783715" cy="945777"/>
+          <a:off x="2167118" y="1714500"/>
+          <a:ext cx="2757256" cy="945777"/>
           <a:chOff x="3839768" y="744141"/>
           <a:chExt cx="1297599" cy="838827"/>
         </a:xfrm>
@@ -8274,7 +11051,7 @@
           <a:p>
             <a:pPr marL="0" indent="0" algn="ctr"/>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="75000"/>
@@ -8285,33 +11062,8 @@
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
-              <a:t>Total de </a:t>
+              <a:t>Total de Assinantes</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Aptos Narrow"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:rPr>
-              <a:t>Assinantes</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -8371,7 +11123,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="ctr"/>
-              <a:t>802</a:t>
+              <a:t>168</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="2200" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -8401,7 +11153,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>1392</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>70184</xdr:rowOff>
+      <xdr:rowOff>52336</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8416,8 +11168,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2177261" y="2714771"/>
-          <a:ext cx="2808881" cy="4213413"/>
+          <a:off x="2166678" y="2714771"/>
+          <a:ext cx="2775808" cy="4195565"/>
           <a:chOff x="1851489" y="1172640"/>
           <a:chExt cx="2579627" cy="4079083"/>
         </a:xfrm>
@@ -8823,7 +11575,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>44%</a:t>
+              <a:t>39%</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -8955,7 +11707,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>56%</a:t>
+              <a:t>61%</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -9000,8 +11752,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5029190" y="742950"/>
-          <a:ext cx="5267781" cy="2449154"/>
+          <a:off x="4985534" y="742950"/>
+          <a:ext cx="5214864" cy="2449154"/>
           <a:chOff x="5605859" y="121841"/>
           <a:chExt cx="4017567" cy="1941909"/>
         </a:xfrm>
@@ -9253,13 +12005,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>45614</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66816</xdr:rowOff>
+      <xdr:rowOff>35415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>234924</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>176353</xdr:rowOff>
+      <xdr:rowOff>144952</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9274,8 +12026,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="45614" y="66816"/>
-          <a:ext cx="3223483" cy="301573"/>
+          <a:off x="45614" y="35415"/>
+          <a:ext cx="3308486" cy="297944"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9305,7 +12057,7 @@
         <a:p>
           <a:pPr marL="0" indent="0" algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
@@ -9318,7 +12070,7 @@
             <a:t>Análise</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="95000"/>
@@ -9330,7 +12082,7 @@
             </a:rPr>
             <a:t> de Assinaturas</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="bg1">
                 <a:lumMod val="95000"/>
@@ -9402,7 +12154,7 @@
         <a:p>
           <a:pPr marL="0" indent="0" algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1100" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="85000"/>
@@ -9415,7 +12167,7 @@
             <a:t>Análise</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1100" b="0" i="1" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1">
                   <a:lumMod val="85000"/>
@@ -9427,7 +12179,7 @@
             </a:rPr>
             <a:t> quantitativa de produtos por assinatura</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="1" u="none" strike="noStrike">
             <a:solidFill>
               <a:schemeClr val="bg1">
                 <a:lumMod val="85000"/>
@@ -9468,8 +12220,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8124330" y="3271376"/>
-          <a:ext cx="2177353" cy="3472323"/>
+          <a:off x="8047601" y="3271376"/>
+          <a:ext cx="2157509" cy="3472323"/>
           <a:chOff x="5592187" y="2252263"/>
           <a:chExt cx="1951327" cy="3461122"/>
         </a:xfrm>
@@ -9694,8 +12446,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8242930" y="3855015"/>
-          <a:ext cx="1904655" cy="2645611"/>
+          <a:off x="8166201" y="3855015"/>
+          <a:ext cx="1884811" cy="2645611"/>
           <a:chOff x="5653536" y="3229449"/>
           <a:chExt cx="1887859" cy="2566299"/>
         </a:xfrm>
@@ -9888,7 +12640,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="l"/>
-              <a:t>Faltando Item</a:t>
+              <a:t>Suporte Ruim</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10026,7 +12778,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="l"/>
-              <a:t>Suporte Ruim</a:t>
+              <a:t>Faltando Item</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10164,7 +12916,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="l"/>
-              <a:t>Produto com defeito</a:t>
+              <a:t>Boa qualidade</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10233,7 +12985,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="l"/>
-              <a:t>Boa qualidade</a:t>
+              <a:t>Produto com defeito</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10302,7 +13054,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>333</a:t>
+              <a:t>39</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10368,7 +13120,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>190</a:t>
+              <a:t>27</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10437,7 +13189,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>70</a:t>
+              <a:t>12</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10506,7 +13258,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>69</a:t>
+              <a:t>9</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10575,7 +13327,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>47</a:t>
+              <a:t>7</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10644,7 +13396,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>47</a:t>
+              <a:t>5</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10713,7 +13465,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>23</a:t>
+              <a:t>2</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -10782,7 +13534,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:rPr>
               <a:pPr marL="0" indent="0" algn="r"/>
-              <a:t>23</a:t>
+              <a:t>1</a:t>
             </a:fld>
             <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
@@ -11372,7 +14124,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>2437</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>82904</xdr:rowOff>
+      <xdr:rowOff>62802</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11387,8 +14139,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4943475" y="3267076"/>
-          <a:ext cx="2983762" cy="3483328"/>
+          <a:off x="5007115" y="3231488"/>
+          <a:ext cx="2971201" cy="3425545"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11396,9 +14148,9 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="14902"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
@@ -11517,9 +14269,8 @@
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
@@ -11592,9 +14343,8 @@
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
@@ -11605,9 +14355,8 @@
           </a:r>
           <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="85000"/>
-                <a:lumOff val="15000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:latin typeface="Aptos Narrow"/>
@@ -11678,9 +14427,8 @@
           <a:r>
             <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
@@ -11696,8 +14444,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38099</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>582083</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>61451</xdr:rowOff>
     </xdr:from>
@@ -11741,8 +14489,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5600699" y="3871451"/>
-              <a:ext cx="2346392" cy="2847808"/>
+              <a:off x="5535083" y="3871451"/>
+              <a:ext cx="2412008" cy="2847808"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11798,8 +14546,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5189428" y="3313693"/>
-          <a:ext cx="1883718" cy="301733"/>
+          <a:off x="5145772" y="3313693"/>
+          <a:ext cx="1863874" cy="301733"/>
           <a:chOff x="5014789" y="870368"/>
           <a:chExt cx="1872314" cy="294325"/>
         </a:xfrm>
@@ -11850,9 +14598,8 @@
             <a:r>
               <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
@@ -11885,19 +14632,17 @@
           </a:prstGeom>
           <a:ln>
             <a:solidFill>
-              <a:schemeClr val="tx2">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
               </a:schemeClr>
             </a:solidFill>
           </a:ln>
           <a:effectLst>
             <a:outerShdw blurRad="25400" dist="12700" dir="10800000" algn="r" rotWithShape="0">
-              <a:schemeClr val="tx2">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
+              <a:srgbClr val="B69BEF">
                 <a:alpha val="65000"/>
-              </a:schemeClr>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </xdr:spPr>
@@ -12598,7 +15343,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>27%</a:t>
+            <a:t>22%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2200" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -12682,7 +15427,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>22%</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2200" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -12763,7 +15508,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="ctr"/>
-            <a:t>51%</a:t>
+            <a:t>54%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2200" b="0" i="0" u="none" strike="noStrike">
             <a:solidFill>
@@ -24096,6 +26841,282 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C758786B-7270-48CA-A786-2DBAB7A9FDFC}" name="avaliacoes" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A28:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="9">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Avaliacao" fld="9" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="13">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA08B2AE-AD38-492D-B332-C6CBD99EF920}" name="faixa_etaria_genero" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Faixa Etaria e Genero">
+  <location ref="A20:D25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Genero" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="7">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAFAF6D5-9043-4AD7-AF3A-3AA97C31611B}" name="mensalidade" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A8:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="12">
@@ -24103,7 +27124,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -24133,9 +27154,9 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24151,7 +27172,7 @@
     <dataField name="Sum of Mesalidades" fld="11" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -24167,7 +27188,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15E09DCB-79C2-4C1B-A7EF-2EBD8DF06589}" name="genero" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -24205,9 +27226,9 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24231,16 +27252,16 @@
     <dataField name="Count of Genero" fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="4">
+    <format dxfId="19">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="21">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -24256,7 +27277,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE305C93-4919-483D-AB80-C61F0512F508}" name="regiao" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A41:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -24264,7 +27285,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -24294,9 +27315,9 @@
     <pivotField showAll="0">
       <items count="5">
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -24323,7 +27344,7 @@
     <dataField name="Count of Regiao" fld="5" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="6">
+    <format dxfId="4">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="5">
@@ -24342,7 +27363,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9D695B4-D49E-4D30-9A84-E288D804DCB2}" name="produtos" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -24350,7 +27371,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -24421,295 +27442,19 @@
     <dataField name="Count of Assinatura" fld="10" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="10">
+    <format dxfId="0">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="2">
       <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C758786B-7270-48CA-A786-2DBAB7A9FDFC}" name="avaliacoes" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A28:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="9">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Avaliacao" fld="9" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="16">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" grandRow="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA08B2AE-AD38-492D-B332-C6CBD99EF920}" name="faixa_etaria_genero" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Faixa Etaria e Genero">
-  <location ref="A20:D25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Genero" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="22">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight17" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -24778,9 +27523,9 @@
     <tabular pivotCacheId="1259103837">
       <items count="4">
         <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="3" s="1"/>
-        <i x="0" s="1"/>
+        <i x="2"/>
+        <i x="3"/>
+        <i x="0"/>
       </items>
     </tabular>
   </data>
@@ -24798,7 +27543,7 @@
   <data>
     <tabular pivotCacheId="1259103837">
       <items count="2">
-        <i x="1" s="1"/>
+        <i x="1"/>
         <i x="0" s="1"/>
       </items>
     </tabular>
@@ -24816,25 +27561,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C184AD73-03A1-4143-98BD-3271CF2BD15B}" name="assinantes" displayName="assinantes" ref="A1:L803" totalsRowShown="0" headerRowDxfId="35" headerRowCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C184AD73-03A1-4143-98BD-3271CF2BD15B}" name="assinantes" displayName="assinantes" ref="A1:L803" totalsRowShown="0" headerRowDxfId="373" headerRowCellStyle="Normal">
   <autoFilter ref="A1:L803" xr:uid="{C184AD73-03A1-4143-98BD-3271CF2BD15B}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{516E62C9-DC1D-40FD-9E5B-FAA921878FAC}" name="CPF" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{72375F92-40DA-42A6-AA48-6359F6595083}" name="Nome" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{AF52DEA4-2281-4A96-AF35-3A8EC26DF5E1}" name="Genero" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{11EC0B7D-87C5-40A0-BF7F-4FF836D055BA}" name="Nivel_Estudos" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{D40E2EF7-022D-4139-BE41-911573806B65}" name="Interesse/Hobby" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{438FF73C-8563-49C2-84AF-0B893F21B784}" name="Regiao" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7F70924D-8105-4BC2-93FE-5DBE5ACADE03}" name="Data_Nasc" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{A9374651-A9BE-4CCE-8EC6-9348A627FC2C}" name="Idade" dataDxfId="27">
+    <tableColumn id="1" xr3:uid="{516E62C9-DC1D-40FD-9E5B-FAA921878FAC}" name="CPF" dataDxfId="372"/>
+    <tableColumn id="2" xr3:uid="{72375F92-40DA-42A6-AA48-6359F6595083}" name="Nome" dataDxfId="371"/>
+    <tableColumn id="3" xr3:uid="{AF52DEA4-2281-4A96-AF35-3A8EC26DF5E1}" name="Genero" dataDxfId="370"/>
+    <tableColumn id="4" xr3:uid="{11EC0B7D-87C5-40A0-BF7F-4FF836D055BA}" name="Nivel_Estudos" dataDxfId="369"/>
+    <tableColumn id="5" xr3:uid="{D40E2EF7-022D-4139-BE41-911573806B65}" name="Interesse/Hobby" dataDxfId="368"/>
+    <tableColumn id="6" xr3:uid="{438FF73C-8563-49C2-84AF-0B893F21B784}" name="Regiao" dataDxfId="367"/>
+    <tableColumn id="7" xr3:uid="{7F70924D-8105-4BC2-93FE-5DBE5ACADE03}" name="Data_Nasc" dataDxfId="366"/>
+    <tableColumn id="11" xr3:uid="{A9374651-A9BE-4CCE-8EC6-9348A627FC2C}" name="Idade" dataDxfId="365">
       <calculatedColumnFormula>TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8BC2F83C-1480-4EA4-8ABF-292A5A7EA90A}" name="Faixa_Etaria" dataDxfId="26">
+    <tableColumn id="12" xr3:uid="{8BC2F83C-1480-4EA4-8ABF-292A5A7EA90A}" name="Faixa_Etaria" dataDxfId="364">
       <calculatedColumnFormula>HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{068B1B6C-B8F0-416C-B51C-5765F1B7BAF2}" name="Avaliacao" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{3A91DDCF-3F84-4D1F-ABA1-DD14DE1FE4A5}" name="Assinatura" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{529DE6FB-0438-4C90-8241-3B7EDE321EA0}" name="Mesalidade" dataDxfId="23" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{068B1B6C-B8F0-416C-B51C-5765F1B7BAF2}" name="Avaliacao" dataDxfId="363"/>
+    <tableColumn id="9" xr3:uid="{3A91DDCF-3F84-4D1F-ABA1-DD14DE1FE4A5}" name="Assinatura" dataDxfId="362"/>
+    <tableColumn id="10" xr3:uid="{529DE6FB-0438-4C90-8241-3B7EDE321EA0}" name="Mesalidade" dataDxfId="361" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -48618,7 +51363,7 @@
       </c>
       <c r="H3" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -48658,7 +51403,7 @@
       </c>
       <c r="H4" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -48778,7 +51523,7 @@
       </c>
       <c r="H7" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -48858,7 +51603,7 @@
       </c>
       <c r="H9" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49018,7 +51763,7 @@
       </c>
       <c r="H13" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49058,7 +51803,7 @@
       </c>
       <c r="H14" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I14" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49138,7 +51883,7 @@
       </c>
       <c r="H16" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I16" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49338,7 +52083,7 @@
       </c>
       <c r="H21" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49498,11 +52243,11 @@
       </c>
       <c r="H25" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I25" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>45-54</v>
+        <v>54-70</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>430</v>
@@ -49858,7 +52603,7 @@
       </c>
       <c r="H34" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I34" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -49938,7 +52683,7 @@
       </c>
       <c r="H36" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I36" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50138,7 +52883,7 @@
       </c>
       <c r="H41" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I41" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50298,7 +53043,7 @@
       </c>
       <c r="H45" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I45" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50538,7 +53283,7 @@
       </c>
       <c r="H51" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I51" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50618,7 +53363,7 @@
       </c>
       <c r="H53" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I53" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50738,7 +53483,7 @@
       </c>
       <c r="H56" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I56" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -50938,7 +53683,7 @@
       </c>
       <c r="H61" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I61" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -51178,7 +53923,7 @@
       </c>
       <c r="H67" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I67" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -51218,7 +53963,7 @@
       </c>
       <c r="H68" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I68" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -51298,7 +54043,7 @@
       </c>
       <c r="H70" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I70" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -51698,7 +54443,7 @@
       </c>
       <c r="H80" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I80" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -51778,7 +54523,7 @@
       </c>
       <c r="H82" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I82" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52018,7 +54763,7 @@
       </c>
       <c r="H88" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I88" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52258,7 +55003,7 @@
       </c>
       <c r="H94" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I94" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52298,7 +55043,7 @@
       </c>
       <c r="H95" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I95" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52418,7 +55163,7 @@
       </c>
       <c r="H98" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I98" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52458,7 +55203,7 @@
       </c>
       <c r="H99" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I99" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52498,7 +55243,7 @@
       </c>
       <c r="H100" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I100" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52538,7 +55283,7 @@
       </c>
       <c r="H101" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I101" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52618,7 +55363,7 @@
       </c>
       <c r="H103" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I103" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -52898,11 +55643,11 @@
       </c>
       <c r="H110" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I110" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J110" s="15" t="s">
         <v>433</v>
@@ -53018,7 +55763,7 @@
       </c>
       <c r="H113" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I113" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -53098,7 +55843,7 @@
       </c>
       <c r="H115" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I115" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -53338,7 +56083,7 @@
       </c>
       <c r="H121" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I121" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -53378,11 +56123,11 @@
       </c>
       <c r="H122" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I122" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>24-34</v>
+        <v>35-44</v>
       </c>
       <c r="J122" s="15" t="s">
         <v>433</v>
@@ -53618,7 +56363,7 @@
       </c>
       <c r="H128" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I128" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -53858,7 +56603,7 @@
       </c>
       <c r="H134" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I134" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -54418,7 +57163,7 @@
       </c>
       <c r="H148" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I148" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -54458,7 +57203,7 @@
       </c>
       <c r="H149" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I149" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -54698,7 +57443,7 @@
       </c>
       <c r="H155" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I155" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -54818,7 +57563,7 @@
       </c>
       <c r="H158" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I158" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -54898,7 +57643,7 @@
       </c>
       <c r="H160" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I160" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55018,7 +57763,7 @@
       </c>
       <c r="H163" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I163" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55058,7 +57803,7 @@
       </c>
       <c r="H164" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I164" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55138,7 +57883,7 @@
       </c>
       <c r="H166" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I166" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55178,7 +57923,7 @@
       </c>
       <c r="H167" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I167" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55218,7 +57963,7 @@
       </c>
       <c r="H168" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I168" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55258,7 +58003,7 @@
       </c>
       <c r="H169" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I169" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55298,7 +58043,7 @@
       </c>
       <c r="H170" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I170" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55618,7 +58363,7 @@
       </c>
       <c r="H178" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I178" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55658,7 +58403,7 @@
       </c>
       <c r="H179" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I179" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -55858,7 +58603,7 @@
       </c>
       <c r="H184" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I184" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56098,7 +58843,7 @@
       </c>
       <c r="H190" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I190" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56138,7 +58883,7 @@
       </c>
       <c r="H191" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I191" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56378,7 +59123,7 @@
       </c>
       <c r="H197" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I197" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56658,7 +59403,7 @@
       </c>
       <c r="H204" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I204" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56738,7 +59483,7 @@
       </c>
       <c r="H206" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I206" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -56938,7 +59683,7 @@
       </c>
       <c r="H211" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I211" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57018,7 +59763,7 @@
       </c>
       <c r="H213" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I213" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57258,7 +60003,7 @@
       </c>
       <c r="H219" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I219" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57338,7 +60083,7 @@
       </c>
       <c r="H221" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I221" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57618,7 +60363,7 @@
       </c>
       <c r="H228" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I228" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57738,7 +60483,7 @@
       </c>
       <c r="H231" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I231" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -57978,7 +60723,7 @@
       </c>
       <c r="H237" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I237" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58218,7 +60963,7 @@
       </c>
       <c r="H243" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I243" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58258,7 +61003,7 @@
       </c>
       <c r="H244" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I244" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58298,7 +61043,7 @@
       </c>
       <c r="H245" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I245" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58378,7 +61123,7 @@
       </c>
       <c r="H247" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I247" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58458,7 +61203,7 @@
       </c>
       <c r="H249" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I249" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58658,7 +61403,7 @@
       </c>
       <c r="H254" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I254" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58778,7 +61523,7 @@
       </c>
       <c r="H257" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I257" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58858,7 +61603,7 @@
       </c>
       <c r="H259" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I259" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -58938,7 +61683,7 @@
       </c>
       <c r="H261" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I261" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59018,7 +61763,7 @@
       </c>
       <c r="H263" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I263" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59058,7 +61803,7 @@
       </c>
       <c r="H264" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I264" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59378,7 +62123,7 @@
       </c>
       <c r="H272" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I272" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59578,7 +62323,7 @@
       </c>
       <c r="H277" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I277" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59698,7 +62443,7 @@
       </c>
       <c r="H280" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I280" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59738,7 +62483,7 @@
       </c>
       <c r="H281" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I281" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -59898,7 +62643,7 @@
       </c>
       <c r="H285" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I285" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60018,11 +62763,11 @@
       </c>
       <c r="H288" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I288" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>24-34</v>
+        <v>35-44</v>
       </c>
       <c r="J288" s="15" t="s">
         <v>436</v>
@@ -60058,7 +62803,7 @@
       </c>
       <c r="H289" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I289" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60098,7 +62843,7 @@
       </c>
       <c r="H290" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I290" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60138,11 +62883,11 @@
       </c>
       <c r="H291" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I291" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J291" s="15" t="s">
         <v>435</v>
@@ -60178,7 +62923,7 @@
       </c>
       <c r="H292" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I292" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60258,7 +63003,7 @@
       </c>
       <c r="H294" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I294" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60298,7 +63043,7 @@
       </c>
       <c r="H295" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I295" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60538,7 +63283,7 @@
       </c>
       <c r="H301" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I301" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -60938,7 +63683,7 @@
       </c>
       <c r="H311" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I311" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -61258,7 +64003,7 @@
       </c>
       <c r="H319" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I319" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -61338,7 +64083,7 @@
       </c>
       <c r="H321" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I321" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -61578,7 +64323,7 @@
       </c>
       <c r="H327" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I327" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -61658,7 +64403,7 @@
       </c>
       <c r="H329" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I329" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -61818,11 +64563,11 @@
       </c>
       <c r="H333" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I333" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>24-34</v>
+        <v>35-44</v>
       </c>
       <c r="J333" s="15" t="s">
         <v>431</v>
@@ -61858,7 +64603,7 @@
       </c>
       <c r="H334" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I334" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62138,7 +64883,7 @@
       </c>
       <c r="H341" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I341" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62178,7 +64923,7 @@
       </c>
       <c r="H342" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I342" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62458,7 +65203,7 @@
       </c>
       <c r="H349" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I349" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62618,7 +65363,7 @@
       </c>
       <c r="H353" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I353" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62698,7 +65443,7 @@
       </c>
       <c r="H355" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I355" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62858,7 +65603,7 @@
       </c>
       <c r="H359" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I359" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -62898,7 +65643,7 @@
       </c>
       <c r="H360" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I360" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63098,7 +65843,7 @@
       </c>
       <c r="H365" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I365" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63298,11 +66043,11 @@
       </c>
       <c r="H370" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I370" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J370" s="15" t="s">
         <v>430</v>
@@ -63378,7 +66123,7 @@
       </c>
       <c r="H372" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I372" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63778,7 +66523,7 @@
       </c>
       <c r="H382" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I382" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63818,7 +66563,7 @@
       </c>
       <c r="H383" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I383" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63858,7 +66603,7 @@
       </c>
       <c r="H384" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I384" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -63938,7 +66683,7 @@
       </c>
       <c r="H386" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I386" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64058,7 +66803,7 @@
       </c>
       <c r="H389" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I389" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64138,7 +66883,7 @@
       </c>
       <c r="H391" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I391" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64218,7 +66963,7 @@
       </c>
       <c r="H393" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I393" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64418,7 +67163,7 @@
       </c>
       <c r="H398" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I398" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64538,11 +67283,11 @@
       </c>
       <c r="H401" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I401" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J401" s="15" t="s">
         <v>431</v>
@@ -64658,7 +67403,7 @@
       </c>
       <c r="H404" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I404" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64698,7 +67443,7 @@
       </c>
       <c r="H405" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I405" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64738,7 +67483,7 @@
       </c>
       <c r="H406" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I406" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64818,7 +67563,7 @@
       </c>
       <c r="H408" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I408" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -64938,7 +67683,7 @@
       </c>
       <c r="H411" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I411" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65018,7 +67763,7 @@
       </c>
       <c r="H413" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I413" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65178,7 +67923,7 @@
       </c>
       <c r="H417" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I417" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65258,7 +68003,7 @@
       </c>
       <c r="H419" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I419" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65498,7 +68243,7 @@
       </c>
       <c r="H425" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I425" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65738,7 +68483,7 @@
       </c>
       <c r="H431" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I431" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -65898,7 +68643,7 @@
       </c>
       <c r="H435" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I435" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66058,7 +68803,7 @@
       </c>
       <c r="H439" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I439" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66098,7 +68843,7 @@
       </c>
       <c r="H440" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I440" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66258,7 +69003,7 @@
       </c>
       <c r="H444" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I444" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66298,11 +69043,11 @@
       </c>
       <c r="H445" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I445" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J445" s="15" t="s">
         <v>433</v>
@@ -66338,7 +69083,7 @@
       </c>
       <c r="H446" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I446" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66658,7 +69403,7 @@
       </c>
       <c r="H454" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I454" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66738,7 +69483,7 @@
       </c>
       <c r="H456" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I456" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66778,7 +69523,7 @@
       </c>
       <c r="H457" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I457" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -66978,7 +69723,7 @@
       </c>
       <c r="H462" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I462" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67018,7 +69763,7 @@
       </c>
       <c r="H463" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I463" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67258,7 +70003,7 @@
       </c>
       <c r="H469" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I469" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67378,7 +70123,7 @@
       </c>
       <c r="H472" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I472" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67418,7 +70163,7 @@
       </c>
       <c r="H473" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I473" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67578,7 +70323,7 @@
       </c>
       <c r="H477" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I477" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67738,7 +70483,7 @@
       </c>
       <c r="H481" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I481" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -67778,7 +70523,7 @@
       </c>
       <c r="H482" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I482" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68138,7 +70883,7 @@
       </c>
       <c r="H491" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I491" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68258,7 +71003,7 @@
       </c>
       <c r="H494" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I494" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68298,7 +71043,7 @@
       </c>
       <c r="H495" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I495" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68378,11 +71123,11 @@
       </c>
       <c r="H497" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I497" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J497" s="15" t="s">
         <v>433</v>
@@ -68418,7 +71163,7 @@
       </c>
       <c r="H498" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I498" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68498,7 +71243,7 @@
       </c>
       <c r="H500" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I500" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68738,7 +71483,7 @@
       </c>
       <c r="H506" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I506" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -68778,7 +71523,7 @@
       </c>
       <c r="H507" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I507" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -69178,7 +71923,7 @@
       </c>
       <c r="H517" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I517" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -69258,7 +72003,7 @@
       </c>
       <c r="H519" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I519" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -69458,11 +72203,11 @@
       </c>
       <c r="H524" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I524" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J524" s="15" t="s">
         <v>436</v>
@@ -69498,7 +72243,7 @@
       </c>
       <c r="H525" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I525" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -69818,7 +72563,7 @@
       </c>
       <c r="H533" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I533" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -70018,7 +72763,7 @@
       </c>
       <c r="H538" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I538" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -70138,7 +72883,7 @@
       </c>
       <c r="H541" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I541" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -70178,7 +72923,7 @@
       </c>
       <c r="H542" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I542" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -70498,7 +73243,7 @@
       </c>
       <c r="H550" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I550" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -70698,7 +73443,7 @@
       </c>
       <c r="H555" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I555" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71178,7 +73923,7 @@
       </c>
       <c r="H567" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I567" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71258,7 +74003,7 @@
       </c>
       <c r="H569" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I569" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71338,7 +74083,7 @@
       </c>
       <c r="H571" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I571" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71498,11 +74243,11 @@
       </c>
       <c r="H575" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I575" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>45-54</v>
+        <v>54-70</v>
       </c>
       <c r="J575" s="15" t="s">
         <v>435</v>
@@ -71578,7 +74323,7 @@
       </c>
       <c r="H577" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I577" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71618,7 +74363,7 @@
       </c>
       <c r="H578" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I578" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71698,7 +74443,7 @@
       </c>
       <c r="H580" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I580" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71818,7 +74563,7 @@
       </c>
       <c r="H583" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I583" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -71938,7 +74683,7 @@
       </c>
       <c r="H586" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I586" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72178,7 +74923,7 @@
       </c>
       <c r="H592" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I592" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72218,7 +74963,7 @@
       </c>
       <c r="H593" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I593" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72258,7 +75003,7 @@
       </c>
       <c r="H594" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I594" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72658,7 +75403,7 @@
       </c>
       <c r="H604" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I604" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72858,7 +75603,7 @@
       </c>
       <c r="H609" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I609" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72938,7 +75683,7 @@
       </c>
       <c r="H611" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I611" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -72978,7 +75723,7 @@
       </c>
       <c r="H612" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I612" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73338,7 +76083,7 @@
       </c>
       <c r="H621" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I621" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73378,7 +76123,7 @@
       </c>
       <c r="H622" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I622" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73578,7 +76323,7 @@
       </c>
       <c r="H627" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I627" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73618,7 +76363,7 @@
       </c>
       <c r="H628" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I628" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73738,7 +76483,7 @@
       </c>
       <c r="H631" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I631" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73898,7 +76643,7 @@
       </c>
       <c r="H635" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I635" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -73978,7 +76723,7 @@
       </c>
       <c r="H637" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I637" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -74218,7 +76963,7 @@
       </c>
       <c r="H643" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I643" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -74338,7 +77083,7 @@
       </c>
       <c r="H646" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I646" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -74378,7 +77123,7 @@
       </c>
       <c r="H647" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I647" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -74618,7 +77363,7 @@
       </c>
       <c r="H653" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I653" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -74978,7 +77723,7 @@
       </c>
       <c r="H662" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I662" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -75018,7 +77763,7 @@
       </c>
       <c r="H663" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I663" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -75178,7 +77923,7 @@
       </c>
       <c r="H667" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I667" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -75418,7 +78163,7 @@
       </c>
       <c r="H673" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I673" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -75458,7 +78203,7 @@
       </c>
       <c r="H674" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I674" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -75578,7 +78323,7 @@
       </c>
       <c r="H677" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I677" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76138,11 +78883,11 @@
       </c>
       <c r="H691" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I691" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J691" s="15" t="s">
         <v>429</v>
@@ -76178,7 +78923,7 @@
       </c>
       <c r="H692" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I692" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76298,7 +79043,7 @@
       </c>
       <c r="H695" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I695" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76378,7 +79123,7 @@
       </c>
       <c r="H697" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I697" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76578,7 +79323,7 @@
       </c>
       <c r="H702" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I702" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76618,7 +79363,7 @@
       </c>
       <c r="H703" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I703" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76658,7 +79403,7 @@
       </c>
       <c r="H704" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I704" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -76698,7 +79443,7 @@
       </c>
       <c r="H705" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I705" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -77018,7 +79763,7 @@
       </c>
       <c r="H713" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I713" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -77058,11 +79803,11 @@
       </c>
       <c r="H714" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I714" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J714" s="15" t="s">
         <v>435</v>
@@ -77138,7 +79883,7 @@
       </c>
       <c r="H716" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I716" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -77258,7 +80003,7 @@
       </c>
       <c r="H719" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I719" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -77978,7 +80723,7 @@
       </c>
       <c r="H737" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I737" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78058,7 +80803,7 @@
       </c>
       <c r="H739" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I739" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78178,7 +80923,7 @@
       </c>
       <c r="H742" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I742" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78258,7 +81003,7 @@
       </c>
       <c r="H744" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I744" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78418,7 +81163,7 @@
       </c>
       <c r="H748" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I748" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78738,7 +81483,7 @@
       </c>
       <c r="H756" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I756" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78858,7 +81603,7 @@
       </c>
       <c r="H759" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I759" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -78898,7 +81643,7 @@
       </c>
       <c r="H760" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I760" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79018,11 +81763,11 @@
       </c>
       <c r="H763" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I763" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
-        <v>35-44</v>
+        <v>45-54</v>
       </c>
       <c r="J763" s="15" t="s">
         <v>436</v>
@@ -79058,7 +81803,7 @@
       </c>
       <c r="H764" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I764" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79138,7 +81883,7 @@
       </c>
       <c r="H766" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I766" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79378,7 +82123,7 @@
       </c>
       <c r="H772" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I772" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79658,7 +82403,7 @@
       </c>
       <c r="H779" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I779" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79738,7 +82483,7 @@
       </c>
       <c r="H781" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I781" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79818,7 +82563,7 @@
       </c>
       <c r="H783" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I783" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -79938,7 +82683,7 @@
       </c>
       <c r="H786" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I786" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80018,7 +82763,7 @@
       </c>
       <c r="H788" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I788" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80138,7 +82883,7 @@
       </c>
       <c r="H791" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I791" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80498,7 +83243,7 @@
       </c>
       <c r="H800" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I800" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80578,7 +83323,7 @@
       </c>
       <c r="H802" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I802" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80618,7 +83363,7 @@
       </c>
       <c r="H803" s="13">
         <f ca="1">TRUNC((TODAY()-assinantes[[#This Row],[Data_Nasc]])/365)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I803" s="13" t="str">
         <f ca="1">HLOOKUP(assinantes[[#This Row],[Idade]],informacoes!$A$3:$D$4,2,TRUE)</f>
@@ -80697,10 +83442,10 @@
   <dimension ref="A2:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -80725,15 +83470,15 @@
       </c>
       <c r="E2" s="2">
         <f>GETPIVOTDATA("Genero",$A$3,"Genero",D2)</f>
-        <v>352</v>
+        <v>66</v>
       </c>
       <c r="F2" s="24">
         <f>E2/E4</f>
-        <v>0.43890274314214461</v>
+        <v>0.39285714285714285</v>
       </c>
       <c r="G2" s="25">
         <f>1-F2</f>
-        <v>0.56109725685785539</v>
+        <v>0.60714285714285721</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -80749,30 +83494,30 @@
       </c>
       <c r="E3" s="2">
         <f>GETPIVOTDATA("Genero",$A$3,"Genero",D3)</f>
-        <v>450</v>
+        <v>102</v>
       </c>
       <c r="F3" s="24">
         <f>E3/E4</f>
-        <v>0.56109725685785539</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="G3" s="25">
         <f>1-F3</f>
-        <v>0.43890274314214461</v>
+        <v>0.3928571428571429</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>352</v>
+      <c r="B4" s="29">
+        <v>66</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>468</v>
       </c>
       <c r="E4" s="2">
         <f>E2+E3</f>
-        <v>802</v>
+        <v>168</v>
       </c>
       <c r="F4" s="24"/>
     </row>
@@ -80780,8 +83525,8 @@
       <c r="A5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>450</v>
+      <c r="B5" s="29">
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -80799,12 +83544,12 @@
       </c>
       <c r="E8" s="27">
         <f>A9</f>
-        <v>26467.800000000334</v>
+        <v>3661.8000000000061</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
-        <v>26467.800000000334</v>
+        <v>3661.8000000000061</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -80829,8 +83574,8 @@
       <c r="A13" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B13">
-        <v>136</v>
+      <c r="B13" s="29">
+        <v>80</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" ref="D13:E16" si="0">A13</f>
@@ -80838,19 +83583,19 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="F13" s="26">
         <f>E13/SUM($E$13:$E$16)</f>
-        <v>0.16957605985037408</v>
+        <v>0.17777777777777778</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="B14">
-        <v>168</v>
+      <c r="B14" s="29">
+        <v>102</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -80858,19 +83603,19 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="F14" s="26">
         <f>E14/SUM($E$13:$E$16)</f>
-        <v>0.20947630922693267</v>
+        <v>0.22666666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="B15">
-        <v>232</v>
+      <c r="B15" s="29">
+        <v>126</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -80878,19 +83623,19 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="F15" s="26">
         <f>E15/SUM($E$13:$E$16)</f>
-        <v>0.2892768079800499</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="B16">
-        <v>266</v>
+      <c r="B16" s="29">
+        <v>142</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
@@ -80898,11 +83643,11 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="F16" s="26">
         <f>E16/SUM($E$13:$E$16)</f>
-        <v>0.33167082294264338</v>
+        <v>0.31555555555555553</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -80941,56 +83686,56 @@
       <c r="A22" s="16" t="s">
         <v>420</v>
       </c>
-      <c r="B22">
-        <v>50</v>
-      </c>
-      <c r="C22">
-        <v>65</v>
-      </c>
-      <c r="D22">
-        <v>115</v>
+      <c r="B22" s="29">
+        <v>8</v>
+      </c>
+      <c r="C22" s="29">
+        <v>16</v>
+      </c>
+      <c r="D22" s="29">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="B23">
-        <v>102</v>
-      </c>
-      <c r="C23">
-        <v>132</v>
-      </c>
-      <c r="D23">
-        <v>234</v>
+      <c r="B23" s="29">
+        <v>15</v>
+      </c>
+      <c r="C23" s="29">
+        <v>25</v>
+      </c>
+      <c r="D23" s="29">
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="B24">
-        <v>91</v>
-      </c>
-      <c r="C24">
-        <v>107</v>
-      </c>
-      <c r="D24">
-        <v>198</v>
+      <c r="B24" s="29">
+        <v>26</v>
+      </c>
+      <c r="C24" s="29">
+        <v>24</v>
+      </c>
+      <c r="D24" s="29">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="B25">
-        <v>109</v>
-      </c>
-      <c r="C25">
-        <v>146</v>
-      </c>
-      <c r="D25">
-        <v>255</v>
+      <c r="B25" s="29">
+        <v>17</v>
+      </c>
+      <c r="C25" s="29">
+        <v>37</v>
+      </c>
+      <c r="D25" s="29">
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -81011,64 +83756,64 @@
       <c r="A29" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="B29">
-        <v>333</v>
+      <c r="B29" s="29">
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>436</v>
       </c>
-      <c r="B30">
-        <v>190</v>
+      <c r="B30" s="29">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="B31">
-        <v>70</v>
+        <v>429</v>
+      </c>
+      <c r="B31" s="29">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="B32">
-        <v>69</v>
+      <c r="B32" s="29">
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="B33">
-        <v>47</v>
+        <v>435</v>
+      </c>
+      <c r="B33" s="29">
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>432</v>
       </c>
-      <c r="B34">
-        <v>47</v>
+      <c r="B34" s="29">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="B35">
-        <v>23</v>
+        <v>434</v>
+      </c>
+      <c r="B35" s="29">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="B36">
-        <v>23</v>
+        <v>431</v>
+      </c>
+      <c r="B36" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -81089,57 +83834,57 @@
       <c r="A42" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="B42">
-        <v>216</v>
+      <c r="B42" s="29">
+        <v>22</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>426</v>
       </c>
       <c r="E42" s="2">
         <f>GETPIVOTDATA("Regiao",$A$41,"Regiao",D42)</f>
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="F42" s="26">
         <f>E42/SUM($E$42:$E$44)</f>
-        <v>0.26932668329177056</v>
+        <v>0.21568627450980393</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
         <v>425</v>
       </c>
-      <c r="B43">
-        <v>409</v>
+      <c r="B43" s="29">
+        <v>55</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>425</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" ref="E43:E44" si="1">GETPIVOTDATA("Regiao",$A$41,"Regiao",D43)</f>
-        <v>409</v>
+        <v>55</v>
       </c>
       <c r="F43" s="26">
         <f t="shared" ref="F43:F44" si="2">E43/SUM($E$42:$E$44)</f>
-        <v>0.5099750623441397</v>
+        <v>0.53921568627450978</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="B44">
-        <v>177</v>
+      <c r="B44" s="29">
+        <v>25</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>424</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="1"/>
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="F44" s="26">
         <f t="shared" si="2"/>
-        <v>0.22069825436408977</v>
+        <v>0.24509803921568626</v>
       </c>
     </row>
   </sheetData>
@@ -81845,11 +84590,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
